--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="15">
   <si>
     <t>user_id</t>
   </si>
@@ -25,41 +25,48 @@
     <t>country</t>
   </si>
   <si>
-    <t>Qatar</t>
+    <t>درعا</t>
   </si>
   <si>
-    <t>Jordan</t>
+    <t>حلب</t>
   </si>
   <si>
-    <t>Morocco</t>
+    <t>دمشق</t>
   </si>
   <si>
-    <t>Egypt</t>
+    <t>القنيطرة</t>
   </si>
   <si>
-    <t>UAE</t>
+    <t>اللاذقية</t>
   </si>
   <si>
-    <t>Kuwait</t>
+    <t>حماة</t>
   </si>
   <si>
-    <t>Saudi Arabia</t>
+    <t>حمص</t>
+  </si>
+  <si>
+    <t>إدلب</t>
+  </si>
+  <si>
+    <t>السويداء</t>
+  </si>
+  <si>
+    <t>دير الزور</t>
+  </si>
+  <si>
+    <t>الرقة</t>
+  </si>
+  <si>
+    <t>طرطوس</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -75,7 +82,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -83,30 +90,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -405,13 +394,13 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -489,7 +478,7 @@
         <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -500,7 +489,7 @@
         <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -511,7 +500,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -522,7 +511,7 @@
         <v>54</v>
       </c>
       <c r="C11" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -533,7 +522,7 @@
         <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -555,7 +544,7 @@
         <v>51</v>
       </c>
       <c r="C14" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -566,7 +555,7 @@
         <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -577,7 +566,7 @@
         <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -588,7 +577,7 @@
         <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -599,7 +588,7 @@
         <v>40</v>
       </c>
       <c r="C18" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -610,7 +599,7 @@
         <v>49</v>
       </c>
       <c r="C19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -621,7 +610,7 @@
         <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -632,7 +621,7 @@
         <v>53</v>
       </c>
       <c r="C21" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -643,7 +632,7 @@
         <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -654,7 +643,7 @@
         <v>30</v>
       </c>
       <c r="C23" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -665,7 +654,7 @@
         <v>50</v>
       </c>
       <c r="C24" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -676,7 +665,7 @@
         <v>63</v>
       </c>
       <c r="C25" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -687,7 +676,7 @@
         <v>53</v>
       </c>
       <c r="C26" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -698,7 +687,7 @@
         <v>18</v>
       </c>
       <c r="C27" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -709,7 +698,7 @@
         <v>51</v>
       </c>
       <c r="C28" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -720,7 +709,7 @@
         <v>42</v>
       </c>
       <c r="C29" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -731,7 +720,7 @@
         <v>59</v>
       </c>
       <c r="C30" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -742,7 +731,7 @@
         <v>24</v>
       </c>
       <c r="C31" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -753,7 +742,7 @@
         <v>43</v>
       </c>
       <c r="C32" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -764,7 +753,7 @@
         <v>65</v>
       </c>
       <c r="C33" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -775,7 +764,7 @@
         <v>41</v>
       </c>
       <c r="C34" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -786,7 +775,7 @@
         <v>31</v>
       </c>
       <c r="C35" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -797,7 +786,7 @@
         <v>33</v>
       </c>
       <c r="C36" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -808,7 +797,7 @@
         <v>25</v>
       </c>
       <c r="C37" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -830,7 +819,7 @@
         <v>29</v>
       </c>
       <c r="C39" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -841,7 +830,7 @@
         <v>47</v>
       </c>
       <c r="C40" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -852,7 +841,7 @@
         <v>32</v>
       </c>
       <c r="C41" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -863,7 +852,7 @@
         <v>54</v>
       </c>
       <c r="C42" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -896,7 +885,7 @@
         <v>56</v>
       </c>
       <c r="C45" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -907,7 +896,7 @@
         <v>57</v>
       </c>
       <c r="C46" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -918,7 +907,7 @@
         <v>31</v>
       </c>
       <c r="C47" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -929,7 +918,7 @@
         <v>25</v>
       </c>
       <c r="C48" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -940,7 +929,7 @@
         <v>32</v>
       </c>
       <c r="C49" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -951,7 +940,7 @@
         <v>55</v>
       </c>
       <c r="C50" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -962,7 +951,7 @@
         <v>49</v>
       </c>
       <c r="C51" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -973,7 +962,7 @@
         <v>23</v>
       </c>
       <c r="C52" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -984,7 +973,7 @@
         <v>24</v>
       </c>
       <c r="C53" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -995,7 +984,7 @@
         <v>39</v>
       </c>
       <c r="C54" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1017,7 +1006,7 @@
         <v>19</v>
       </c>
       <c r="C56" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1028,7 +1017,7 @@
         <v>50</v>
       </c>
       <c r="C57" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1039,7 +1028,7 @@
         <v>40</v>
       </c>
       <c r="C58" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1050,7 +1039,7 @@
         <v>54</v>
       </c>
       <c r="C59" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1061,7 +1050,7 @@
         <v>21</v>
       </c>
       <c r="C60" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1072,7 +1061,7 @@
         <v>24</v>
       </c>
       <c r="C61" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1094,7 +1083,7 @@
         <v>23</v>
       </c>
       <c r="C63" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1105,7 +1094,7 @@
         <v>64</v>
       </c>
       <c r="C64" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1116,7 +1105,7 @@
         <v>20</v>
       </c>
       <c r="C65" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1127,7 +1116,7 @@
         <v>63</v>
       </c>
       <c r="C66" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1138,7 +1127,7 @@
         <v>50</v>
       </c>
       <c r="C67" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1160,7 +1149,7 @@
         <v>18</v>
       </c>
       <c r="C69" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1193,7 +1182,7 @@
         <v>28</v>
       </c>
       <c r="C72" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1204,7 +1193,7 @@
         <v>23</v>
       </c>
       <c r="C73" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1237,7 +1226,7 @@
         <v>58</v>
       </c>
       <c r="C76" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1248,7 +1237,7 @@
         <v>27</v>
       </c>
       <c r="C77" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1259,7 +1248,7 @@
         <v>52</v>
       </c>
       <c r="C78" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1270,7 +1259,7 @@
         <v>51</v>
       </c>
       <c r="C79" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1281,7 +1270,7 @@
         <v>54</v>
       </c>
       <c r="C80" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1292,7 +1281,7 @@
         <v>29</v>
       </c>
       <c r="C81" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1303,7 +1292,7 @@
         <v>57</v>
       </c>
       <c r="C82" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1314,7 +1303,7 @@
         <v>21</v>
       </c>
       <c r="C83" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1325,7 +1314,7 @@
         <v>54</v>
       </c>
       <c r="C84" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1336,7 +1325,7 @@
         <v>40</v>
       </c>
       <c r="C85" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1347,7 +1336,7 @@
         <v>31</v>
       </c>
       <c r="C86" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1358,7 +1347,7 @@
         <v>64</v>
       </c>
       <c r="C87" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1369,7 +1358,7 @@
         <v>47</v>
       </c>
       <c r="C88" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1391,7 +1380,7 @@
         <v>28</v>
       </c>
       <c r="C90" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1413,7 +1402,7 @@
         <v>64</v>
       </c>
       <c r="C92" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1424,7 +1413,7 @@
         <v>42</v>
       </c>
       <c r="C93" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1435,7 +1424,7 @@
         <v>53</v>
       </c>
       <c r="C94" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1446,7 +1435,7 @@
         <v>23</v>
       </c>
       <c r="C95" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1457,7 +1446,7 @@
         <v>63</v>
       </c>
       <c r="C96" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1468,7 +1457,7 @@
         <v>52</v>
       </c>
       <c r="C97" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1479,7 +1468,7 @@
         <v>63</v>
       </c>
       <c r="C98" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -1490,7 +1479,7 @@
         <v>35</v>
       </c>
       <c r="C99" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -1501,7 +1490,7 @@
         <v>52</v>
       </c>
       <c r="C100" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -1512,7 +1501,7 @@
         <v>37</v>
       </c>
       <c r="C101" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -1523,7 +1512,7 @@
         <v>46</v>
       </c>
       <c r="C102" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -1534,7 +1523,7 @@
         <v>20</v>
       </c>
       <c r="C103" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -1545,7 +1534,7 @@
         <v>20</v>
       </c>
       <c r="C104" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -1556,7 +1545,7 @@
         <v>61</v>
       </c>
       <c r="C105" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -1567,7 +1556,7 @@
         <v>40</v>
       </c>
       <c r="C106" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -1578,7 +1567,7 @@
         <v>31</v>
       </c>
       <c r="C107" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -1589,7 +1578,7 @@
         <v>56</v>
       </c>
       <c r="C108" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -1600,7 +1589,7 @@
         <v>57</v>
       </c>
       <c r="C109" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -1611,7 +1600,7 @@
         <v>24</v>
       </c>
       <c r="C110" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -1622,7 +1611,7 @@
         <v>26</v>
       </c>
       <c r="C111" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -1633,7 +1622,7 @@
         <v>64</v>
       </c>
       <c r="C112" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -1644,7 +1633,7 @@
         <v>62</v>
       </c>
       <c r="C113" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -1655,7 +1644,7 @@
         <v>29</v>
       </c>
       <c r="C114" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -1666,7 +1655,7 @@
         <v>18</v>
       </c>
       <c r="C115" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -1677,7 +1666,7 @@
         <v>42</v>
       </c>
       <c r="C116" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -1688,7 +1677,7 @@
         <v>23</v>
       </c>
       <c r="C117" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -1699,7 +1688,7 @@
         <v>45</v>
       </c>
       <c r="C118" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -1710,7 +1699,7 @@
         <v>62</v>
       </c>
       <c r="C119" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -1721,7 +1710,7 @@
         <v>26</v>
       </c>
       <c r="C120" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -1732,7 +1721,7 @@
         <v>33</v>
       </c>
       <c r="C121" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -1743,7 +1732,7 @@
         <v>58</v>
       </c>
       <c r="C122" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -1754,7 +1743,7 @@
         <v>44</v>
       </c>
       <c r="C123" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -1765,7 +1754,7 @@
         <v>33</v>
       </c>
       <c r="C124" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -1787,7 +1776,7 @@
         <v>32</v>
       </c>
       <c r="C126" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -1798,7 +1787,7 @@
         <v>51</v>
       </c>
       <c r="C127" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -1809,7 +1798,7 @@
         <v>45</v>
       </c>
       <c r="C128" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -1820,7 +1809,7 @@
         <v>65</v>
       </c>
       <c r="C129" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -1831,7 +1820,7 @@
         <v>18</v>
       </c>
       <c r="C130" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -1842,7 +1831,7 @@
         <v>36</v>
       </c>
       <c r="C131" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -1853,7 +1842,7 @@
         <v>62</v>
       </c>
       <c r="C132" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -1864,7 +1853,7 @@
         <v>18</v>
       </c>
       <c r="C133" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -1875,7 +1864,7 @@
         <v>23</v>
       </c>
       <c r="C134" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -1886,7 +1875,7 @@
         <v>19</v>
       </c>
       <c r="C135" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -1897,7 +1886,7 @@
         <v>39</v>
       </c>
       <c r="C136" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -1908,7 +1897,7 @@
         <v>18</v>
       </c>
       <c r="C137" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -1919,7 +1908,7 @@
         <v>22</v>
       </c>
       <c r="C138" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -1930,7 +1919,7 @@
         <v>28</v>
       </c>
       <c r="C139" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -1941,7 +1930,7 @@
         <v>27</v>
       </c>
       <c r="C140" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -1952,7 +1941,7 @@
         <v>42</v>
       </c>
       <c r="C141" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -1963,7 +1952,7 @@
         <v>26</v>
       </c>
       <c r="C142" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -1974,7 +1963,7 @@
         <v>46</v>
       </c>
       <c r="C143" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -1985,7 +1974,7 @@
         <v>46</v>
       </c>
       <c r="C144" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -1996,7 +1985,7 @@
         <v>58</v>
       </c>
       <c r="C145" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -2007,7 +1996,7 @@
         <v>22</v>
       </c>
       <c r="C146" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -2018,7 +2007,7 @@
         <v>43</v>
       </c>
       <c r="C147" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -2029,7 +2018,7 @@
         <v>54</v>
       </c>
       <c r="C148" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -2040,7 +2029,7 @@
         <v>37</v>
       </c>
       <c r="C149" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -2051,7 +2040,7 @@
         <v>37</v>
       </c>
       <c r="C150" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -2062,7 +2051,7 @@
         <v>61</v>
       </c>
       <c r="C151" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -2073,7 +2062,7 @@
         <v>18</v>
       </c>
       <c r="C152" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -2084,7 +2073,7 @@
         <v>37</v>
       </c>
       <c r="C153" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -2095,7 +2084,7 @@
         <v>40</v>
       </c>
       <c r="C154" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -2106,7 +2095,7 @@
         <v>56</v>
       </c>
       <c r="C155" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -2117,7 +2106,7 @@
         <v>63</v>
       </c>
       <c r="C156" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -2128,7 +2117,7 @@
         <v>18</v>
       </c>
       <c r="C157" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -2139,7 +2128,7 @@
         <v>17</v>
       </c>
       <c r="C158" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -2150,7 +2139,7 @@
         <v>59</v>
       </c>
       <c r="C159" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -2161,7 +2150,7 @@
         <v>60</v>
       </c>
       <c r="C160" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -2172,7 +2161,7 @@
         <v>62</v>
       </c>
       <c r="C161" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -2183,7 +2172,7 @@
         <v>28</v>
       </c>
       <c r="C162" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -2194,7 +2183,7 @@
         <v>62</v>
       </c>
       <c r="C163" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -2205,7 +2194,7 @@
         <v>55</v>
       </c>
       <c r="C164" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -2216,7 +2205,7 @@
         <v>49</v>
       </c>
       <c r="C165" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -2238,7 +2227,7 @@
         <v>54</v>
       </c>
       <c r="C167" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -2249,7 +2238,7 @@
         <v>19</v>
       </c>
       <c r="C168" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="169" spans="1:3">
@@ -2260,7 +2249,7 @@
         <v>46</v>
       </c>
       <c r="C169" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="170" spans="1:3">
@@ -2282,7 +2271,7 @@
         <v>23</v>
       </c>
       <c r="C171" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -2293,7 +2282,7 @@
         <v>16</v>
       </c>
       <c r="C172" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="173" spans="1:3">
@@ -2304,7 +2293,7 @@
         <v>54</v>
       </c>
       <c r="C173" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -2315,7 +2304,7 @@
         <v>64</v>
       </c>
       <c r="C174" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="175" spans="1:3">
@@ -2326,7 +2315,7 @@
         <v>39</v>
       </c>
       <c r="C175" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="176" spans="1:3">
@@ -2337,7 +2326,7 @@
         <v>38</v>
       </c>
       <c r="C176" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="177" spans="1:3">
@@ -2348,7 +2337,7 @@
         <v>23</v>
       </c>
       <c r="C177" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -2359,7 +2348,7 @@
         <v>20</v>
       </c>
       <c r="C178" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -2370,7 +2359,7 @@
         <v>38</v>
       </c>
       <c r="C179" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -2381,7 +2370,7 @@
         <v>31</v>
       </c>
       <c r="C180" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -2392,7 +2381,7 @@
         <v>65</v>
       </c>
       <c r="C181" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -2403,7 +2392,7 @@
         <v>50</v>
       </c>
       <c r="C182" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -2425,7 +2414,7 @@
         <v>27</v>
       </c>
       <c r="C184" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -2436,7 +2425,7 @@
         <v>49</v>
       </c>
       <c r="C185" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -2447,7 +2436,7 @@
         <v>16</v>
       </c>
       <c r="C186" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -2458,7 +2447,7 @@
         <v>20</v>
       </c>
       <c r="C187" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -2480,7 +2469,7 @@
         <v>41</v>
       </c>
       <c r="C189" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -2491,7 +2480,7 @@
         <v>45</v>
       </c>
       <c r="C190" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -2502,7 +2491,7 @@
         <v>48</v>
       </c>
       <c r="C191" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="192" spans="1:3">
@@ -2513,7 +2502,7 @@
         <v>41</v>
       </c>
       <c r="C192" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -2524,7 +2513,7 @@
         <v>31</v>
       </c>
       <c r="C193" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -2535,7 +2524,7 @@
         <v>28</v>
       </c>
       <c r="C194" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -2546,7 +2535,7 @@
         <v>31</v>
       </c>
       <c r="C195" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -2557,7 +2546,7 @@
         <v>57</v>
       </c>
       <c r="C196" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -2568,7 +2557,7 @@
         <v>44</v>
       </c>
       <c r="C197" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -2579,7 +2568,7 @@
         <v>28</v>
       </c>
       <c r="C198" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -2590,7 +2579,7 @@
         <v>55</v>
       </c>
       <c r="C199" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -2612,7 +2601,7 @@
         <v>47</v>
       </c>
       <c r="C201" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -2623,7 +2612,7 @@
         <v>59</v>
       </c>
       <c r="C202" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -2645,7 +2634,7 @@
         <v>23</v>
       </c>
       <c r="C204" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -2656,7 +2645,7 @@
         <v>40</v>
       </c>
       <c r="C205" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="206" spans="1:3">
@@ -2667,7 +2656,7 @@
         <v>47</v>
       </c>
       <c r="C206" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -2678,7 +2667,7 @@
         <v>48</v>
       </c>
       <c r="C207" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -2689,7 +2678,7 @@
         <v>61</v>
       </c>
       <c r="C208" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -2700,7 +2689,7 @@
         <v>41</v>
       </c>
       <c r="C209" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="210" spans="1:3">
@@ -2711,7 +2700,7 @@
         <v>56</v>
       </c>
       <c r="C210" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -2722,7 +2711,7 @@
         <v>63</v>
       </c>
       <c r="C211" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -2733,7 +2722,7 @@
         <v>50</v>
       </c>
       <c r="C212" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -2744,7 +2733,7 @@
         <v>28</v>
       </c>
       <c r="C213" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -2755,7 +2744,7 @@
         <v>32</v>
       </c>
       <c r="C214" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -2766,7 +2755,7 @@
         <v>52</v>
       </c>
       <c r="C215" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -2777,7 +2766,7 @@
         <v>32</v>
       </c>
       <c r="C216" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -2788,7 +2777,7 @@
         <v>20</v>
       </c>
       <c r="C217" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -2799,7 +2788,7 @@
         <v>58</v>
       </c>
       <c r="C218" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -2810,7 +2799,7 @@
         <v>62</v>
       </c>
       <c r="C219" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -2821,7 +2810,7 @@
         <v>45</v>
       </c>
       <c r="C220" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -2832,7 +2821,7 @@
         <v>37</v>
       </c>
       <c r="C221" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -2843,7 +2832,7 @@
         <v>27</v>
       </c>
       <c r="C222" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -2854,7 +2843,7 @@
         <v>50</v>
       </c>
       <c r="C223" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -2865,7 +2854,7 @@
         <v>21</v>
       </c>
       <c r="C224" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -2876,7 +2865,7 @@
         <v>20</v>
       </c>
       <c r="C225" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -2898,7 +2887,7 @@
         <v>19</v>
       </c>
       <c r="C227" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="228" spans="1:3">
@@ -2909,7 +2898,7 @@
         <v>64</v>
       </c>
       <c r="C228" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -2920,7 +2909,7 @@
         <v>20</v>
       </c>
       <c r="C229" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="230" spans="1:3">
@@ -2931,7 +2920,7 @@
         <v>26</v>
       </c>
       <c r="C230" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -2942,7 +2931,7 @@
         <v>56</v>
       </c>
       <c r="C231" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="232" spans="1:3">
@@ -2953,7 +2942,7 @@
         <v>58</v>
       </c>
       <c r="C232" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -2964,7 +2953,7 @@
         <v>42</v>
       </c>
       <c r="C233" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -2975,7 +2964,7 @@
         <v>59</v>
       </c>
       <c r="C234" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -2986,7 +2975,7 @@
         <v>17</v>
       </c>
       <c r="C235" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -2997,7 +2986,7 @@
         <v>29</v>
       </c>
       <c r="C236" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -3008,7 +2997,7 @@
         <v>37</v>
       </c>
       <c r="C237" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -3019,7 +3008,7 @@
         <v>18</v>
       </c>
       <c r="C238" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="239" spans="1:3">
@@ -3030,7 +3019,7 @@
         <v>58</v>
       </c>
       <c r="C239" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -3052,7 +3041,7 @@
         <v>53</v>
       </c>
       <c r="C241" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -3063,7 +3052,7 @@
         <v>31</v>
       </c>
       <c r="C242" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -3074,7 +3063,7 @@
         <v>28</v>
       </c>
       <c r="C243" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -3085,7 +3074,7 @@
         <v>55</v>
       </c>
       <c r="C244" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="245" spans="1:3">
@@ -3096,7 +3085,7 @@
         <v>52</v>
       </c>
       <c r="C245" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="246" spans="1:3">
@@ -3107,7 +3096,7 @@
         <v>65</v>
       </c>
       <c r="C246" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="247" spans="1:3">
@@ -3118,7 +3107,7 @@
         <v>55</v>
       </c>
       <c r="C247" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="248" spans="1:3">
@@ -3129,7 +3118,7 @@
         <v>23</v>
       </c>
       <c r="C248" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="249" spans="1:3">
@@ -3140,7 +3129,7 @@
         <v>22</v>
       </c>
       <c r="C249" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="250" spans="1:3">
@@ -3151,7 +3140,7 @@
         <v>34</v>
       </c>
       <c r="C250" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="251" spans="1:3">
@@ -3162,7 +3151,7 @@
         <v>52</v>
       </c>
       <c r="C251" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="252" spans="1:3">
@@ -3173,7 +3162,7 @@
         <v>60</v>
       </c>
       <c r="C252" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="253" spans="1:3">
@@ -3184,7 +3173,7 @@
         <v>42</v>
       </c>
       <c r="C253" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="254" spans="1:3">
@@ -3195,7 +3184,7 @@
         <v>20</v>
       </c>
       <c r="C254" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="255" spans="1:3">
@@ -3206,7 +3195,7 @@
         <v>45</v>
       </c>
       <c r="C255" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="256" spans="1:3">
@@ -3217,7 +3206,7 @@
         <v>51</v>
       </c>
       <c r="C256" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="257" spans="1:3">
@@ -3228,7 +3217,7 @@
         <v>19</v>
       </c>
       <c r="C257" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -3239,7 +3228,7 @@
         <v>34</v>
       </c>
       <c r="C258" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="259" spans="1:3">
@@ -3250,7 +3239,7 @@
         <v>65</v>
       </c>
       <c r="C259" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="260" spans="1:3">
@@ -3261,7 +3250,7 @@
         <v>28</v>
       </c>
       <c r="C260" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="261" spans="1:3">
@@ -3272,7 +3261,7 @@
         <v>44</v>
       </c>
       <c r="C261" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="262" spans="1:3">
@@ -3283,7 +3272,7 @@
         <v>19</v>
       </c>
       <c r="C262" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="263" spans="1:3">
@@ -3305,7 +3294,7 @@
         <v>18</v>
       </c>
       <c r="C264" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="265" spans="1:3">
@@ -3316,7 +3305,7 @@
         <v>52</v>
       </c>
       <c r="C265" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="266" spans="1:3">
@@ -3327,7 +3316,7 @@
         <v>55</v>
       </c>
       <c r="C266" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="267" spans="1:3">
@@ -3338,7 +3327,7 @@
         <v>55</v>
       </c>
       <c r="C267" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="268" spans="1:3">
@@ -3349,7 +3338,7 @@
         <v>20</v>
       </c>
       <c r="C268" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="269" spans="1:3">
@@ -3360,7 +3349,7 @@
         <v>54</v>
       </c>
       <c r="C269" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="270" spans="1:3">
@@ -3371,7 +3360,7 @@
         <v>55</v>
       </c>
       <c r="C270" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="271" spans="1:3">
@@ -3382,7 +3371,7 @@
         <v>24</v>
       </c>
       <c r="C271" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="272" spans="1:3">
@@ -3393,7 +3382,7 @@
         <v>62</v>
       </c>
       <c r="C272" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="273" spans="1:3">
@@ -3415,7 +3404,7 @@
         <v>53</v>
       </c>
       <c r="C274" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="275" spans="1:3">
@@ -3426,7 +3415,7 @@
         <v>32</v>
       </c>
       <c r="C275" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="276" spans="1:3">
@@ -3437,7 +3426,7 @@
         <v>21</v>
       </c>
       <c r="C276" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="277" spans="1:3">
@@ -3448,7 +3437,7 @@
         <v>25</v>
       </c>
       <c r="C277" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="278" spans="1:3">
@@ -3459,7 +3448,7 @@
         <v>47</v>
       </c>
       <c r="C278" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="279" spans="1:3">
@@ -3470,7 +3459,7 @@
         <v>42</v>
       </c>
       <c r="C279" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="280" spans="1:3">
@@ -3481,7 +3470,7 @@
         <v>55</v>
       </c>
       <c r="C280" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="281" spans="1:3">
@@ -3492,7 +3481,7 @@
         <v>21</v>
       </c>
       <c r="C281" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="282" spans="1:3">
@@ -3503,7 +3492,7 @@
         <v>32</v>
       </c>
       <c r="C282" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="283" spans="1:3">
@@ -3525,7 +3514,7 @@
         <v>40</v>
       </c>
       <c r="C284" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="285" spans="1:3">
@@ -3536,7 +3525,7 @@
         <v>35</v>
       </c>
       <c r="C285" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="286" spans="1:3">
@@ -3547,7 +3536,7 @@
         <v>52</v>
       </c>
       <c r="C286" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="287" spans="1:3">
@@ -3558,7 +3547,7 @@
         <v>57</v>
       </c>
       <c r="C287" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="288" spans="1:3">
@@ -3569,7 +3558,7 @@
         <v>16</v>
       </c>
       <c r="C288" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="289" spans="1:3">
@@ -3580,7 +3569,7 @@
         <v>41</v>
       </c>
       <c r="C289" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="290" spans="1:3">
@@ -3591,7 +3580,7 @@
         <v>38</v>
       </c>
       <c r="C290" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="291" spans="1:3">
@@ -3602,7 +3591,7 @@
         <v>56</v>
       </c>
       <c r="C291" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="292" spans="1:3">
@@ -3613,7 +3602,7 @@
         <v>36</v>
       </c>
       <c r="C292" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="293" spans="1:3">
@@ -3624,7 +3613,7 @@
         <v>39</v>
       </c>
       <c r="C293" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="294" spans="1:3">
@@ -3635,7 +3624,7 @@
         <v>56</v>
       </c>
       <c r="C294" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="295" spans="1:3">
@@ -3646,7 +3635,7 @@
         <v>37</v>
       </c>
       <c r="C295" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="296" spans="1:3">
@@ -3657,7 +3646,7 @@
         <v>33</v>
       </c>
       <c r="C296" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="297" spans="1:3">
@@ -3668,7 +3657,7 @@
         <v>16</v>
       </c>
       <c r="C297" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="298" spans="1:3">
@@ -3690,7 +3679,7 @@
         <v>41</v>
       </c>
       <c r="C299" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="300" spans="1:3">
@@ -3701,7 +3690,7 @@
         <v>45</v>
       </c>
       <c r="C300" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="301" spans="1:3">
@@ -3712,7 +3701,7 @@
         <v>51</v>
       </c>
       <c r="C301" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="302" spans="1:3">
@@ -3723,7 +3712,7 @@
         <v>19</v>
       </c>
       <c r="C302" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="303" spans="1:3">
@@ -3734,7 +3723,7 @@
         <v>47</v>
       </c>
       <c r="C303" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="304" spans="1:3">
@@ -3745,7 +3734,7 @@
         <v>27</v>
       </c>
       <c r="C304" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="305" spans="1:3">
@@ -3756,7 +3745,7 @@
         <v>59</v>
       </c>
       <c r="C305" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="306" spans="1:3">
@@ -3767,7 +3756,7 @@
         <v>17</v>
       </c>
       <c r="C306" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="307" spans="1:3">
@@ -3778,7 +3767,7 @@
         <v>45</v>
       </c>
       <c r="C307" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="308" spans="1:3">
@@ -3789,7 +3778,7 @@
         <v>30</v>
       </c>
       <c r="C308" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="309" spans="1:3">
@@ -3800,7 +3789,7 @@
         <v>26</v>
       </c>
       <c r="C309" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="310" spans="1:3">
@@ -3811,7 +3800,7 @@
         <v>20</v>
       </c>
       <c r="C310" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="311" spans="1:3">
@@ -3822,7 +3811,7 @@
         <v>58</v>
       </c>
       <c r="C311" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="312" spans="1:3">
@@ -3833,7 +3822,7 @@
         <v>30</v>
       </c>
       <c r="C312" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="313" spans="1:3">
@@ -3844,7 +3833,7 @@
         <v>54</v>
       </c>
       <c r="C313" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="314" spans="1:3">
@@ -3855,7 +3844,7 @@
         <v>36</v>
       </c>
       <c r="C314" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="315" spans="1:3">
@@ -3866,7 +3855,7 @@
         <v>64</v>
       </c>
       <c r="C315" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="316" spans="1:3">
@@ -3888,7 +3877,7 @@
         <v>58</v>
       </c>
       <c r="C317" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="318" spans="1:3">
@@ -3899,7 +3888,7 @@
         <v>63</v>
       </c>
       <c r="C318" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="319" spans="1:3">
@@ -3910,7 +3899,7 @@
         <v>22</v>
       </c>
       <c r="C319" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="320" spans="1:3">
@@ -3921,7 +3910,7 @@
         <v>52</v>
       </c>
       <c r="C320" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="321" spans="1:3">
@@ -3932,7 +3921,7 @@
         <v>19</v>
       </c>
       <c r="C321" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="322" spans="1:3">
@@ -3943,7 +3932,7 @@
         <v>42</v>
       </c>
       <c r="C322" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="323" spans="1:3">
@@ -3954,7 +3943,7 @@
         <v>20</v>
       </c>
       <c r="C323" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="324" spans="1:3">
@@ -3965,7 +3954,7 @@
         <v>63</v>
       </c>
       <c r="C324" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="325" spans="1:3">
@@ -3987,7 +3976,7 @@
         <v>34</v>
       </c>
       <c r="C326" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="327" spans="1:3">
@@ -4009,7 +3998,7 @@
         <v>64</v>
       </c>
       <c r="C328" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="329" spans="1:3">
@@ -4020,7 +4009,7 @@
         <v>63</v>
       </c>
       <c r="C329" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="330" spans="1:3">
@@ -4031,7 +4020,7 @@
         <v>53</v>
       </c>
       <c r="C330" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="331" spans="1:3">
@@ -4042,7 +4031,7 @@
         <v>21</v>
       </c>
       <c r="C331" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="332" spans="1:3">
@@ -4053,7 +4042,7 @@
         <v>62</v>
       </c>
       <c r="C332" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="333" spans="1:3">
@@ -4064,7 +4053,7 @@
         <v>36</v>
       </c>
       <c r="C333" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="334" spans="1:3">
@@ -4075,7 +4064,7 @@
         <v>53</v>
       </c>
       <c r="C334" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="335" spans="1:3">
@@ -4086,7 +4075,7 @@
         <v>64</v>
       </c>
       <c r="C335" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="336" spans="1:3">
@@ -4097,7 +4086,7 @@
         <v>38</v>
       </c>
       <c r="C336" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="337" spans="1:3">
@@ -4108,7 +4097,7 @@
         <v>22</v>
       </c>
       <c r="C337" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="338" spans="1:3">
@@ -4119,7 +4108,7 @@
         <v>21</v>
       </c>
       <c r="C338" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="339" spans="1:3">
@@ -4130,7 +4119,7 @@
         <v>52</v>
       </c>
       <c r="C339" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="340" spans="1:3">
@@ -4141,7 +4130,7 @@
         <v>30</v>
       </c>
       <c r="C340" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="341" spans="1:3">
@@ -4152,7 +4141,7 @@
         <v>37</v>
       </c>
       <c r="C341" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="342" spans="1:3">
@@ -4163,7 +4152,7 @@
         <v>55</v>
       </c>
       <c r="C342" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="343" spans="1:3">
@@ -4174,7 +4163,7 @@
         <v>23</v>
       </c>
       <c r="C343" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="344" spans="1:3">
@@ -4185,7 +4174,7 @@
         <v>30</v>
       </c>
       <c r="C344" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="345" spans="1:3">
@@ -4196,7 +4185,7 @@
         <v>60</v>
       </c>
       <c r="C345" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="346" spans="1:3">
@@ -4207,7 +4196,7 @@
         <v>48</v>
       </c>
       <c r="C346" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="347" spans="1:3">
@@ -4218,7 +4207,7 @@
         <v>24</v>
       </c>
       <c r="C347" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="348" spans="1:3">
@@ -4229,7 +4218,7 @@
         <v>22</v>
       </c>
       <c r="C348" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="349" spans="1:3">
@@ -4240,7 +4229,7 @@
         <v>39</v>
       </c>
       <c r="C349" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="350" spans="1:3">
@@ -4251,7 +4240,7 @@
         <v>57</v>
       </c>
       <c r="C350" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="351" spans="1:3">
@@ -4262,7 +4251,7 @@
         <v>58</v>
       </c>
       <c r="C351" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="352" spans="1:3">
@@ -4273,7 +4262,7 @@
         <v>26</v>
       </c>
       <c r="C352" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="353" spans="1:3">
@@ -4284,7 +4273,7 @@
         <v>34</v>
       </c>
       <c r="C353" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="354" spans="1:3">
@@ -4295,7 +4284,7 @@
         <v>57</v>
       </c>
       <c r="C354" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="355" spans="1:3">
@@ -4306,7 +4295,7 @@
         <v>57</v>
       </c>
       <c r="C355" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="356" spans="1:3">
@@ -4317,7 +4306,7 @@
         <v>16</v>
       </c>
       <c r="C356" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="357" spans="1:3">
@@ -4328,7 +4317,7 @@
         <v>60</v>
       </c>
       <c r="C357" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="358" spans="1:3">
@@ -4339,7 +4328,7 @@
         <v>56</v>
       </c>
       <c r="C358" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="359" spans="1:3">
@@ -4350,7 +4339,7 @@
         <v>32</v>
       </c>
       <c r="C359" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="360" spans="1:3">
@@ -4361,7 +4350,7 @@
         <v>38</v>
       </c>
       <c r="C360" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="361" spans="1:3">
@@ -4372,7 +4361,7 @@
         <v>25</v>
       </c>
       <c r="C361" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="362" spans="1:3">
@@ -4383,7 +4372,7 @@
         <v>36</v>
       </c>
       <c r="C362" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="363" spans="1:3">
@@ -4394,7 +4383,7 @@
         <v>22</v>
       </c>
       <c r="C363" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="364" spans="1:3">
@@ -4405,7 +4394,7 @@
         <v>47</v>
       </c>
       <c r="C364" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="365" spans="1:3">
@@ -4416,7 +4405,7 @@
         <v>63</v>
       </c>
       <c r="C365" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="366" spans="1:3">
@@ -4438,7 +4427,7 @@
         <v>45</v>
       </c>
       <c r="C367" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="368" spans="1:3">
@@ -4449,7 +4438,7 @@
         <v>19</v>
       </c>
       <c r="C368" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="369" spans="1:3">
@@ -4460,7 +4449,7 @@
         <v>26</v>
       </c>
       <c r="C369" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="370" spans="1:3">
@@ -4471,7 +4460,7 @@
         <v>58</v>
       </c>
       <c r="C370" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="371" spans="1:3">
@@ -4482,7 +4471,7 @@
         <v>21</v>
       </c>
       <c r="C371" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="372" spans="1:3">
@@ -4493,7 +4482,7 @@
         <v>57</v>
       </c>
       <c r="C372" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="373" spans="1:3">
@@ -4504,7 +4493,7 @@
         <v>29</v>
       </c>
       <c r="C373" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="374" spans="1:3">
@@ -4515,7 +4504,7 @@
         <v>33</v>
       </c>
       <c r="C374" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="375" spans="1:3">
@@ -4537,7 +4526,7 @@
         <v>47</v>
       </c>
       <c r="C376" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="377" spans="1:3">
@@ -4548,7 +4537,7 @@
         <v>56</v>
       </c>
       <c r="C377" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="378" spans="1:3">
@@ -4559,7 +4548,7 @@
         <v>28</v>
       </c>
       <c r="C378" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="379" spans="1:3">
@@ -4570,7 +4559,7 @@
         <v>40</v>
       </c>
       <c r="C379" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="380" spans="1:3">
@@ -4581,7 +4570,7 @@
         <v>61</v>
       </c>
       <c r="C380" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="381" spans="1:3">
@@ -4592,7 +4581,7 @@
         <v>62</v>
       </c>
       <c r="C381" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="382" spans="1:3">
@@ -4603,7 +4592,7 @@
         <v>32</v>
       </c>
       <c r="C382" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="383" spans="1:3">
@@ -4614,7 +4603,7 @@
         <v>65</v>
       </c>
       <c r="C383" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="384" spans="1:3">
@@ -4625,7 +4614,7 @@
         <v>22</v>
       </c>
       <c r="C384" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="385" spans="1:3">
@@ -4636,7 +4625,7 @@
         <v>44</v>
       </c>
       <c r="C385" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="386" spans="1:3">
@@ -4647,7 +4636,7 @@
         <v>50</v>
       </c>
       <c r="C386" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="387" spans="1:3">
@@ -4658,7 +4647,7 @@
         <v>53</v>
       </c>
       <c r="C387" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="388" spans="1:3">
@@ -4669,7 +4658,7 @@
         <v>50</v>
       </c>
       <c r="C388" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="389" spans="1:3">
@@ -4680,7 +4669,7 @@
         <v>44</v>
       </c>
       <c r="C389" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="390" spans="1:3">
@@ -4691,7 +4680,7 @@
         <v>27</v>
       </c>
       <c r="C390" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="391" spans="1:3">
@@ -4702,7 +4691,7 @@
         <v>29</v>
       </c>
       <c r="C391" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="392" spans="1:3">
@@ -4713,7 +4702,7 @@
         <v>47</v>
       </c>
       <c r="C392" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="393" spans="1:3">
@@ -4724,7 +4713,7 @@
         <v>38</v>
       </c>
       <c r="C393" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="394" spans="1:3">
@@ -4735,7 +4724,7 @@
         <v>41</v>
       </c>
       <c r="C394" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="395" spans="1:3">
@@ -4746,7 +4735,7 @@
         <v>36</v>
       </c>
       <c r="C395" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="396" spans="1:3">
@@ -4757,7 +4746,7 @@
         <v>65</v>
       </c>
       <c r="C396" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="397" spans="1:3">
@@ -4768,7 +4757,7 @@
         <v>51</v>
       </c>
       <c r="C397" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="398" spans="1:3">
@@ -4779,7 +4768,7 @@
         <v>50</v>
       </c>
       <c r="C398" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="399" spans="1:3">
@@ -4790,7 +4779,7 @@
         <v>62</v>
       </c>
       <c r="C399" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="400" spans="1:3">
@@ -4812,7 +4801,7 @@
         <v>28</v>
       </c>
       <c r="C401" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="402" spans="1:3">
@@ -4823,7 +4812,7 @@
         <v>53</v>
       </c>
       <c r="C402" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="403" spans="1:3">
@@ -4834,7 +4823,7 @@
         <v>19</v>
       </c>
       <c r="C403" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="404" spans="1:3">
@@ -4845,7 +4834,7 @@
         <v>49</v>
       </c>
       <c r="C404" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="405" spans="1:3">
@@ -4856,7 +4845,7 @@
         <v>31</v>
       </c>
       <c r="C405" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="406" spans="1:3">
@@ -4867,7 +4856,7 @@
         <v>51</v>
       </c>
       <c r="C406" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="407" spans="1:3">
@@ -4878,7 +4867,7 @@
         <v>32</v>
       </c>
       <c r="C407" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="408" spans="1:3">
@@ -4889,7 +4878,7 @@
         <v>46</v>
       </c>
       <c r="C408" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="409" spans="1:3">
@@ -4900,7 +4889,7 @@
         <v>16</v>
       </c>
       <c r="C409" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="410" spans="1:3">
@@ -4911,7 +4900,7 @@
         <v>47</v>
       </c>
       <c r="C410" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="411" spans="1:3">
@@ -4922,7 +4911,7 @@
         <v>44</v>
       </c>
       <c r="C411" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="412" spans="1:3">
@@ -4933,7 +4922,7 @@
         <v>57</v>
       </c>
       <c r="C412" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="413" spans="1:3">
@@ -4944,7 +4933,7 @@
         <v>65</v>
       </c>
       <c r="C413" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="414" spans="1:3">
@@ -4955,7 +4944,7 @@
         <v>23</v>
       </c>
       <c r="C414" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="415" spans="1:3">
@@ -4977,7 +4966,7 @@
         <v>47</v>
       </c>
       <c r="C416" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="417" spans="1:3">
@@ -4988,7 +4977,7 @@
         <v>52</v>
       </c>
       <c r="C417" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="418" spans="1:3">
@@ -4999,7 +4988,7 @@
         <v>27</v>
       </c>
       <c r="C418" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="419" spans="1:3">
@@ -5010,7 +4999,7 @@
         <v>39</v>
       </c>
       <c r="C419" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="420" spans="1:3">
@@ -5021,7 +5010,7 @@
         <v>61</v>
       </c>
       <c r="C420" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="421" spans="1:3">
@@ -5032,7 +5021,7 @@
         <v>60</v>
       </c>
       <c r="C421" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="422" spans="1:3">
@@ -5043,7 +5032,7 @@
         <v>59</v>
       </c>
       <c r="C422" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="423" spans="1:3">
@@ -5054,7 +5043,7 @@
         <v>42</v>
       </c>
       <c r="C423" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="424" spans="1:3">
@@ -5065,7 +5054,7 @@
         <v>40</v>
       </c>
       <c r="C424" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="425" spans="1:3">
@@ -5076,7 +5065,7 @@
         <v>59</v>
       </c>
       <c r="C425" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="426" spans="1:3">
@@ -5087,7 +5076,7 @@
         <v>63</v>
       </c>
       <c r="C426" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="427" spans="1:3">
@@ -5098,7 +5087,7 @@
         <v>59</v>
       </c>
       <c r="C427" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="428" spans="1:3">
@@ -5120,7 +5109,7 @@
         <v>41</v>
       </c>
       <c r="C429" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="430" spans="1:3">
@@ -5131,7 +5120,7 @@
         <v>19</v>
       </c>
       <c r="C430" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="431" spans="1:3">
@@ -5142,7 +5131,7 @@
         <v>60</v>
       </c>
       <c r="C431" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="432" spans="1:3">
@@ -5153,7 +5142,7 @@
         <v>54</v>
       </c>
       <c r="C432" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="433" spans="1:3">
@@ -5164,7 +5153,7 @@
         <v>31</v>
       </c>
       <c r="C433" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="434" spans="1:3">
@@ -5175,7 +5164,7 @@
         <v>53</v>
       </c>
       <c r="C434" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="435" spans="1:3">
@@ -5186,7 +5175,7 @@
         <v>22</v>
       </c>
       <c r="C435" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="436" spans="1:3">
@@ -5197,7 +5186,7 @@
         <v>47</v>
       </c>
       <c r="C436" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="437" spans="1:3">
@@ -5208,7 +5197,7 @@
         <v>60</v>
       </c>
       <c r="C437" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="438" spans="1:3">
@@ -5219,7 +5208,7 @@
         <v>55</v>
       </c>
       <c r="C438" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="439" spans="1:3">
@@ -5230,7 +5219,7 @@
         <v>19</v>
       </c>
       <c r="C439" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="440" spans="1:3">
@@ -5241,7 +5230,7 @@
         <v>22</v>
       </c>
       <c r="C440" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="441" spans="1:3">
@@ -5263,7 +5252,7 @@
         <v>30</v>
       </c>
       <c r="C442" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="443" spans="1:3">
@@ -5274,7 +5263,7 @@
         <v>30</v>
       </c>
       <c r="C443" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="444" spans="1:3">
@@ -5285,7 +5274,7 @@
         <v>52</v>
       </c>
       <c r="C444" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="445" spans="1:3">
@@ -5318,7 +5307,7 @@
         <v>16</v>
       </c>
       <c r="C447" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="448" spans="1:3">
@@ -5329,7 +5318,7 @@
         <v>20</v>
       </c>
       <c r="C448" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="449" spans="1:3">
@@ -5340,7 +5329,7 @@
         <v>32</v>
       </c>
       <c r="C449" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="450" spans="1:3">
@@ -5351,7 +5340,7 @@
         <v>22</v>
       </c>
       <c r="C450" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="451" spans="1:3">
@@ -5362,7 +5351,7 @@
         <v>27</v>
       </c>
       <c r="C451" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="452" spans="1:3">
@@ -5373,7 +5362,7 @@
         <v>28</v>
       </c>
       <c r="C452" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="453" spans="1:3">
@@ -5384,7 +5373,7 @@
         <v>51</v>
       </c>
       <c r="C453" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="454" spans="1:3">
@@ -5395,7 +5384,7 @@
         <v>54</v>
       </c>
       <c r="C454" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="455" spans="1:3">
@@ -5406,7 +5395,7 @@
         <v>59</v>
       </c>
       <c r="C455" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="456" spans="1:3">
@@ -5417,7 +5406,7 @@
         <v>30</v>
       </c>
       <c r="C456" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="457" spans="1:3">
@@ -5428,7 +5417,7 @@
         <v>55</v>
       </c>
       <c r="C457" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="458" spans="1:3">
@@ -5439,7 +5428,7 @@
         <v>47</v>
       </c>
       <c r="C458" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="459" spans="1:3">
@@ -5461,7 +5450,7 @@
         <v>48</v>
       </c>
       <c r="C460" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="461" spans="1:3">
@@ -5472,7 +5461,7 @@
         <v>51</v>
       </c>
       <c r="C461" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="462" spans="1:3">
@@ -5483,7 +5472,7 @@
         <v>61</v>
       </c>
       <c r="C462" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="463" spans="1:3">
@@ -5494,7 +5483,7 @@
         <v>45</v>
       </c>
       <c r="C463" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="464" spans="1:3">
@@ -5505,7 +5494,7 @@
         <v>57</v>
       </c>
       <c r="C464" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="465" spans="1:3">
@@ -5516,7 +5505,7 @@
         <v>36</v>
       </c>
       <c r="C465" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="466" spans="1:3">
@@ -5527,7 +5516,7 @@
         <v>42</v>
       </c>
       <c r="C466" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="467" spans="1:3">
@@ -5538,7 +5527,7 @@
         <v>18</v>
       </c>
       <c r="C467" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="468" spans="1:3">
@@ -5549,7 +5538,7 @@
         <v>65</v>
       </c>
       <c r="C468" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="469" spans="1:3">
@@ -5560,7 +5549,7 @@
         <v>58</v>
       </c>
       <c r="C469" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="470" spans="1:3">
@@ -5571,7 +5560,7 @@
         <v>49</v>
       </c>
       <c r="C470" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="471" spans="1:3">
@@ -5582,7 +5571,7 @@
         <v>44</v>
       </c>
       <c r="C471" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="472" spans="1:3">
@@ -5593,7 +5582,7 @@
         <v>25</v>
       </c>
       <c r="C472" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="473" spans="1:3">
@@ -5604,7 +5593,7 @@
         <v>50</v>
       </c>
       <c r="C473" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="474" spans="1:3">
@@ -5615,7 +5604,7 @@
         <v>37</v>
       </c>
       <c r="C474" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="475" spans="1:3">
@@ -5626,7 +5615,7 @@
         <v>63</v>
       </c>
       <c r="C475" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="476" spans="1:3">
@@ -5637,7 +5626,7 @@
         <v>29</v>
       </c>
       <c r="C476" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="477" spans="1:3">
@@ -5648,7 +5637,7 @@
         <v>46</v>
       </c>
       <c r="C477" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="478" spans="1:3">
@@ -5670,7 +5659,7 @@
         <v>47</v>
       </c>
       <c r="C479" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="480" spans="1:3">
@@ -5681,7 +5670,7 @@
         <v>31</v>
       </c>
       <c r="C480" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="481" spans="1:3">
@@ -5692,7 +5681,7 @@
         <v>33</v>
       </c>
       <c r="C481" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="482" spans="1:3">
@@ -5703,7 +5692,7 @@
         <v>55</v>
       </c>
       <c r="C482" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="483" spans="1:3">
@@ -5714,7 +5703,7 @@
         <v>45</v>
       </c>
       <c r="C483" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="484" spans="1:3">
@@ -5725,7 +5714,7 @@
         <v>59</v>
       </c>
       <c r="C484" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="485" spans="1:3">
@@ -5747,7 +5736,7 @@
         <v>37</v>
       </c>
       <c r="C486" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="487" spans="1:3">
@@ -5758,7 +5747,7 @@
         <v>50</v>
       </c>
       <c r="C487" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="488" spans="1:3">
@@ -5791,7 +5780,7 @@
         <v>19</v>
       </c>
       <c r="C490" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="491" spans="1:3">
@@ -5802,7 +5791,7 @@
         <v>34</v>
       </c>
       <c r="C491" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="492" spans="1:3">
@@ -5813,7 +5802,7 @@
         <v>26</v>
       </c>
       <c r="C492" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="493" spans="1:3">
@@ -5824,7 +5813,7 @@
         <v>48</v>
       </c>
       <c r="C493" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="494" spans="1:3">
@@ -5835,7 +5824,7 @@
         <v>54</v>
       </c>
       <c r="C494" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="495" spans="1:3">
@@ -5846,7 +5835,7 @@
         <v>46</v>
       </c>
       <c r="C495" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="496" spans="1:3">
@@ -5857,7 +5846,7 @@
         <v>33</v>
       </c>
       <c r="C496" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="497" spans="1:3">
@@ -5868,7 +5857,7 @@
         <v>38</v>
       </c>
       <c r="C497" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="498" spans="1:3">
@@ -5879,7 +5868,7 @@
         <v>22</v>
       </c>
       <c r="C498" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="499" spans="1:3">
@@ -5890,7 +5879,7 @@
         <v>23</v>
       </c>
       <c r="C499" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="500" spans="1:3">
@@ -5912,7 +5901,7 @@
         <v>62</v>
       </c>
       <c r="C501" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="502" spans="1:3">
@@ -5923,7 +5912,7 @@
         <v>40</v>
       </c>
       <c r="C502" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="503" spans="1:3">
@@ -5934,7 +5923,7 @@
         <v>26</v>
       </c>
       <c r="C503" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="504" spans="1:3">
@@ -5945,7 +5934,7 @@
         <v>48</v>
       </c>
       <c r="C504" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="505" spans="1:3">
@@ -5956,7 +5945,7 @@
         <v>22</v>
       </c>
       <c r="C505" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="506" spans="1:3">
@@ -5967,7 +5956,7 @@
         <v>63</v>
       </c>
       <c r="C506" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="507" spans="1:3">
@@ -5978,7 +5967,7 @@
         <v>26</v>
       </c>
       <c r="C507" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="508" spans="1:3">
@@ -5989,7 +5978,7 @@
         <v>54</v>
       </c>
       <c r="C508" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="509" spans="1:3">
@@ -6000,7 +5989,7 @@
         <v>33</v>
       </c>
       <c r="C509" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="510" spans="1:3">
@@ -6011,7 +6000,7 @@
         <v>64</v>
       </c>
       <c r="C510" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="511" spans="1:3">
@@ -6033,7 +6022,7 @@
         <v>57</v>
       </c>
       <c r="C512" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="513" spans="1:3">
@@ -6055,7 +6044,7 @@
         <v>16</v>
       </c>
       <c r="C514" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="515" spans="1:3">
@@ -6066,7 +6055,7 @@
         <v>60</v>
       </c>
       <c r="C515" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="516" spans="1:3">
@@ -6077,7 +6066,7 @@
         <v>45</v>
       </c>
       <c r="C516" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="517" spans="1:3">
@@ -6088,7 +6077,7 @@
         <v>60</v>
       </c>
       <c r="C517" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="518" spans="1:3">
@@ -6099,7 +6088,7 @@
         <v>30</v>
       </c>
       <c r="C518" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="519" spans="1:3">
@@ -6110,7 +6099,7 @@
         <v>55</v>
       </c>
       <c r="C519" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="520" spans="1:3">
@@ -6121,7 +6110,7 @@
         <v>63</v>
       </c>
       <c r="C520" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="521" spans="1:3">
@@ -6132,7 +6121,7 @@
         <v>63</v>
       </c>
       <c r="C521" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="522" spans="1:3">
@@ -6143,7 +6132,7 @@
         <v>57</v>
       </c>
       <c r="C522" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="523" spans="1:3">
@@ -6154,7 +6143,7 @@
         <v>17</v>
       </c>
       <c r="C523" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="524" spans="1:3">
@@ -6165,7 +6154,7 @@
         <v>62</v>
       </c>
       <c r="C524" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="525" spans="1:3">
@@ -6176,7 +6165,7 @@
         <v>47</v>
       </c>
       <c r="C525" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="526" spans="1:3">
@@ -6187,7 +6176,7 @@
         <v>60</v>
       </c>
       <c r="C526" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="527" spans="1:3">
@@ -6198,7 +6187,7 @@
         <v>29</v>
       </c>
       <c r="C527" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="528" spans="1:3">
@@ -6209,7 +6198,7 @@
         <v>39</v>
       </c>
       <c r="C528" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="529" spans="1:3">
@@ -6220,7 +6209,7 @@
         <v>55</v>
       </c>
       <c r="C529" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="530" spans="1:3">
@@ -6231,7 +6220,7 @@
         <v>34</v>
       </c>
       <c r="C530" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="531" spans="1:3">
@@ -6253,7 +6242,7 @@
         <v>56</v>
       </c>
       <c r="C532" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="533" spans="1:3">
@@ -6264,7 +6253,7 @@
         <v>23</v>
       </c>
       <c r="C533" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="534" spans="1:3">
@@ -6275,7 +6264,7 @@
         <v>55</v>
       </c>
       <c r="C534" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="535" spans="1:3">
@@ -6297,7 +6286,7 @@
         <v>47</v>
       </c>
       <c r="C536" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="537" spans="1:3">
@@ -6308,7 +6297,7 @@
         <v>21</v>
       </c>
       <c r="C537" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="538" spans="1:3">
@@ -6319,7 +6308,7 @@
         <v>18</v>
       </c>
       <c r="C538" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="539" spans="1:3">
@@ -6330,7 +6319,7 @@
         <v>54</v>
       </c>
       <c r="C539" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="540" spans="1:3">
@@ -6341,7 +6330,7 @@
         <v>29</v>
       </c>
       <c r="C540" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="541" spans="1:3">
@@ -6352,7 +6341,7 @@
         <v>54</v>
       </c>
       <c r="C541" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="542" spans="1:3">
@@ -6363,7 +6352,7 @@
         <v>20</v>
       </c>
       <c r="C542" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="543" spans="1:3">
@@ -6374,7 +6363,7 @@
         <v>57</v>
       </c>
       <c r="C543" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="544" spans="1:3">
@@ -6396,7 +6385,7 @@
         <v>51</v>
       </c>
       <c r="C545" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="546" spans="1:3">
@@ -6407,7 +6396,7 @@
         <v>27</v>
       </c>
       <c r="C546" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="547" spans="1:3">
@@ -6429,7 +6418,7 @@
         <v>49</v>
       </c>
       <c r="C548" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="549" spans="1:3">
@@ -6440,7 +6429,7 @@
         <v>57</v>
       </c>
       <c r="C549" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="550" spans="1:3">
@@ -6462,7 +6451,7 @@
         <v>58</v>
       </c>
       <c r="C551" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="552" spans="1:3">
@@ -6473,7 +6462,7 @@
         <v>38</v>
       </c>
       <c r="C552" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="553" spans="1:3">
@@ -6484,7 +6473,7 @@
         <v>45</v>
       </c>
       <c r="C553" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="554" spans="1:3">
@@ -6495,7 +6484,7 @@
         <v>36</v>
       </c>
       <c r="C554" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="555" spans="1:3">
@@ -6517,7 +6506,7 @@
         <v>44</v>
       </c>
       <c r="C556" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="557" spans="1:3">
@@ -6528,7 +6517,7 @@
         <v>41</v>
       </c>
       <c r="C557" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="558" spans="1:3">
@@ -6539,7 +6528,7 @@
         <v>49</v>
       </c>
       <c r="C558" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="559" spans="1:3">
@@ -6550,7 +6539,7 @@
         <v>21</v>
       </c>
       <c r="C559" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="560" spans="1:3">
@@ -6561,7 +6550,7 @@
         <v>28</v>
       </c>
       <c r="C560" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="561" spans="1:3">
@@ -6572,7 +6561,7 @@
         <v>50</v>
       </c>
       <c r="C561" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="562" spans="1:3">
@@ -6583,7 +6572,7 @@
         <v>25</v>
       </c>
       <c r="C562" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="563" spans="1:3">
@@ -6594,7 +6583,7 @@
         <v>34</v>
       </c>
       <c r="C563" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="564" spans="1:3">
@@ -6605,7 +6594,7 @@
         <v>59</v>
       </c>
       <c r="C564" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="565" spans="1:3">
@@ -6616,7 +6605,7 @@
         <v>20</v>
       </c>
       <c r="C565" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="566" spans="1:3">
@@ -6627,7 +6616,7 @@
         <v>44</v>
       </c>
       <c r="C566" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="567" spans="1:3">
@@ -6638,7 +6627,7 @@
         <v>57</v>
       </c>
       <c r="C567" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="568" spans="1:3">
@@ -6649,7 +6638,7 @@
         <v>38</v>
       </c>
       <c r="C568" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="569" spans="1:3">
@@ -6660,7 +6649,7 @@
         <v>23</v>
       </c>
       <c r="C569" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="570" spans="1:3">
@@ -6671,7 +6660,7 @@
         <v>42</v>
       </c>
       <c r="C570" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="571" spans="1:3">
@@ -6682,7 +6671,7 @@
         <v>23</v>
       </c>
       <c r="C571" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="572" spans="1:3">
@@ -6693,7 +6682,7 @@
         <v>40</v>
       </c>
       <c r="C572" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="573" spans="1:3">
@@ -6704,7 +6693,7 @@
         <v>17</v>
       </c>
       <c r="C573" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="574" spans="1:3">
@@ -6715,7 +6704,7 @@
         <v>64</v>
       </c>
       <c r="C574" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="575" spans="1:3">
@@ -6726,7 +6715,7 @@
         <v>61</v>
       </c>
       <c r="C575" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="576" spans="1:3">
@@ -6737,7 +6726,7 @@
         <v>29</v>
       </c>
       <c r="C576" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="577" spans="1:3">
@@ -6748,7 +6737,7 @@
         <v>45</v>
       </c>
       <c r="C577" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="578" spans="1:3">
@@ -6781,7 +6770,7 @@
         <v>46</v>
       </c>
       <c r="C580" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="581" spans="1:3">
@@ -6792,7 +6781,7 @@
         <v>21</v>
       </c>
       <c r="C581" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="582" spans="1:3">
@@ -6803,7 +6792,7 @@
         <v>32</v>
       </c>
       <c r="C582" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="583" spans="1:3">
@@ -6814,7 +6803,7 @@
         <v>52</v>
       </c>
       <c r="C583" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="584" spans="1:3">
@@ -6825,7 +6814,7 @@
         <v>17</v>
       </c>
       <c r="C584" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="585" spans="1:3">
@@ -6836,7 +6825,7 @@
         <v>58</v>
       </c>
       <c r="C585" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="586" spans="1:3">
@@ -6847,7 +6836,7 @@
         <v>23</v>
       </c>
       <c r="C586" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="587" spans="1:3">
@@ -6858,7 +6847,7 @@
         <v>45</v>
       </c>
       <c r="C587" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="588" spans="1:3">
@@ -6869,7 +6858,7 @@
         <v>65</v>
       </c>
       <c r="C588" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="589" spans="1:3">
@@ -6880,7 +6869,7 @@
         <v>24</v>
       </c>
       <c r="C589" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="590" spans="1:3">
@@ -6891,7 +6880,7 @@
         <v>54</v>
       </c>
       <c r="C590" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="591" spans="1:3">
@@ -6913,7 +6902,7 @@
         <v>61</v>
       </c>
       <c r="C592" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="593" spans="1:3">
@@ -6924,7 +6913,7 @@
         <v>60</v>
       </c>
       <c r="C593" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="594" spans="1:3">
@@ -6935,7 +6924,7 @@
         <v>44</v>
       </c>
       <c r="C594" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="595" spans="1:3">
@@ -6946,7 +6935,7 @@
         <v>16</v>
       </c>
       <c r="C595" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="596" spans="1:3">
@@ -6957,7 +6946,7 @@
         <v>17</v>
       </c>
       <c r="C596" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="597" spans="1:3">
@@ -6968,7 +6957,7 @@
         <v>60</v>
       </c>
       <c r="C597" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="598" spans="1:3">
@@ -6979,7 +6968,7 @@
         <v>26</v>
       </c>
       <c r="C598" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="599" spans="1:3">
@@ -6990,7 +6979,7 @@
         <v>32</v>
       </c>
       <c r="C599" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="600" spans="1:3">
@@ -7001,7 +6990,7 @@
         <v>42</v>
       </c>
       <c r="C600" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="601" spans="1:3">
@@ -7012,7 +7001,7 @@
         <v>37</v>
       </c>
       <c r="C601" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="602" spans="1:3">
@@ -7023,7 +7012,7 @@
         <v>57</v>
       </c>
       <c r="C602" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="603" spans="1:3">
@@ -7034,7 +7023,7 @@
         <v>53</v>
       </c>
       <c r="C603" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="604" spans="1:3">
@@ -7045,7 +7034,7 @@
         <v>56</v>
       </c>
       <c r="C604" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="605" spans="1:3">
@@ -7056,7 +7045,7 @@
         <v>63</v>
       </c>
       <c r="C605" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="606" spans="1:3">
@@ -7067,7 +7056,7 @@
         <v>21</v>
       </c>
       <c r="C606" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="607" spans="1:3">
@@ -7078,7 +7067,7 @@
         <v>25</v>
       </c>
       <c r="C607" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="608" spans="1:3">
@@ -7089,7 +7078,7 @@
         <v>30</v>
       </c>
       <c r="C608" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="609" spans="1:3">
@@ -7100,7 +7089,7 @@
         <v>22</v>
       </c>
       <c r="C609" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="610" spans="1:3">
@@ -7122,7 +7111,7 @@
         <v>63</v>
       </c>
       <c r="C611" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="612" spans="1:3">
@@ -7144,7 +7133,7 @@
         <v>23</v>
       </c>
       <c r="C613" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="614" spans="1:3">
@@ -7155,7 +7144,7 @@
         <v>27</v>
       </c>
       <c r="C614" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="615" spans="1:3">
@@ -7166,7 +7155,7 @@
         <v>42</v>
       </c>
       <c r="C615" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="616" spans="1:3">
@@ -7177,7 +7166,7 @@
         <v>48</v>
       </c>
       <c r="C616" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="617" spans="1:3">
@@ -7188,7 +7177,7 @@
         <v>18</v>
       </c>
       <c r="C617" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="618" spans="1:3">
@@ -7199,7 +7188,7 @@
         <v>28</v>
       </c>
       <c r="C618" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="619" spans="1:3">
@@ -7210,7 +7199,7 @@
         <v>29</v>
       </c>
       <c r="C619" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="620" spans="1:3">
@@ -7221,7 +7210,7 @@
         <v>35</v>
       </c>
       <c r="C620" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="621" spans="1:3">
@@ -7232,7 +7221,7 @@
         <v>19</v>
       </c>
       <c r="C621" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="622" spans="1:3">
@@ -7243,7 +7232,7 @@
         <v>31</v>
       </c>
       <c r="C622" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="623" spans="1:3">
@@ -7265,7 +7254,7 @@
         <v>48</v>
       </c>
       <c r="C624" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="625" spans="1:3">
@@ -7276,7 +7265,7 @@
         <v>19</v>
       </c>
       <c r="C625" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="626" spans="1:3">
@@ -7287,7 +7276,7 @@
         <v>42</v>
       </c>
       <c r="C626" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="627" spans="1:3">
@@ -7298,7 +7287,7 @@
         <v>33</v>
       </c>
       <c r="C627" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="628" spans="1:3">
@@ -7309,7 +7298,7 @@
         <v>34</v>
       </c>
       <c r="C628" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="629" spans="1:3">
@@ -7320,7 +7309,7 @@
         <v>53</v>
       </c>
       <c r="C629" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="630" spans="1:3">
@@ -7331,7 +7320,7 @@
         <v>54</v>
       </c>
       <c r="C630" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="631" spans="1:3">
@@ -7342,7 +7331,7 @@
         <v>41</v>
       </c>
       <c r="C631" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="632" spans="1:3">
@@ -7353,7 +7342,7 @@
         <v>52</v>
       </c>
       <c r="C632" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="633" spans="1:3">
@@ -7364,7 +7353,7 @@
         <v>19</v>
       </c>
       <c r="C633" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="634" spans="1:3">
@@ -7375,7 +7364,7 @@
         <v>35</v>
       </c>
       <c r="C634" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="635" spans="1:3">
@@ -7386,7 +7375,7 @@
         <v>45</v>
       </c>
       <c r="C635" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="636" spans="1:3">
@@ -7397,7 +7386,7 @@
         <v>45</v>
       </c>
       <c r="C636" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="637" spans="1:3">
@@ -7408,7 +7397,7 @@
         <v>35</v>
       </c>
       <c r="C637" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="638" spans="1:3">
@@ -7419,7 +7408,7 @@
         <v>46</v>
       </c>
       <c r="C638" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="639" spans="1:3">
@@ -7430,7 +7419,7 @@
         <v>46</v>
       </c>
       <c r="C639" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="640" spans="1:3">
@@ -7441,7 +7430,7 @@
         <v>57</v>
       </c>
       <c r="C640" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="641" spans="1:3">
@@ -7452,7 +7441,7 @@
         <v>35</v>
       </c>
       <c r="C641" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="642" spans="1:3">
@@ -7463,7 +7452,7 @@
         <v>24</v>
       </c>
       <c r="C642" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="643" spans="1:3">
@@ -7474,7 +7463,7 @@
         <v>32</v>
       </c>
       <c r="C643" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="644" spans="1:3">
@@ -7485,7 +7474,7 @@
         <v>61</v>
       </c>
       <c r="C644" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="645" spans="1:3">
@@ -7496,7 +7485,7 @@
         <v>25</v>
       </c>
       <c r="C645" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="646" spans="1:3">
@@ -7507,7 +7496,7 @@
         <v>49</v>
       </c>
       <c r="C646" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="647" spans="1:3">
@@ -7518,7 +7507,7 @@
         <v>38</v>
       </c>
       <c r="C647" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="648" spans="1:3">
@@ -7529,7 +7518,7 @@
         <v>17</v>
       </c>
       <c r="C648" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="649" spans="1:3">
@@ -7540,7 +7529,7 @@
         <v>55</v>
       </c>
       <c r="C649" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="650" spans="1:3">
@@ -7562,7 +7551,7 @@
         <v>34</v>
       </c>
       <c r="C651" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="652" spans="1:3">
@@ -7584,7 +7573,7 @@
         <v>32</v>
       </c>
       <c r="C653" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="654" spans="1:3">
@@ -7595,7 +7584,7 @@
         <v>55</v>
       </c>
       <c r="C654" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="655" spans="1:3">
@@ -7606,7 +7595,7 @@
         <v>37</v>
       </c>
       <c r="C655" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="656" spans="1:3">
@@ -7617,7 +7606,7 @@
         <v>51</v>
       </c>
       <c r="C656" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="657" spans="1:3">
@@ -7628,7 +7617,7 @@
         <v>38</v>
       </c>
       <c r="C657" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="658" spans="1:3">
@@ -7639,7 +7628,7 @@
         <v>48</v>
       </c>
       <c r="C658" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="659" spans="1:3">
@@ -7650,7 +7639,7 @@
         <v>25</v>
       </c>
       <c r="C659" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="660" spans="1:3">
@@ -7661,7 +7650,7 @@
         <v>50</v>
       </c>
       <c r="C660" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="661" spans="1:3">
@@ -7672,7 +7661,7 @@
         <v>21</v>
       </c>
       <c r="C661" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="662" spans="1:3">
@@ -7683,7 +7672,7 @@
         <v>55</v>
       </c>
       <c r="C662" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="663" spans="1:3">
@@ -7694,7 +7683,7 @@
         <v>35</v>
       </c>
       <c r="C663" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="664" spans="1:3">
@@ -7705,7 +7694,7 @@
         <v>57</v>
       </c>
       <c r="C664" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="665" spans="1:3">
@@ -7716,7 +7705,7 @@
         <v>29</v>
       </c>
       <c r="C665" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="666" spans="1:3">
@@ -7727,7 +7716,7 @@
         <v>31</v>
       </c>
       <c r="C666" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="667" spans="1:3">
@@ -7738,7 +7727,7 @@
         <v>16</v>
       </c>
       <c r="C667" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="668" spans="1:3">
@@ -7749,7 +7738,7 @@
         <v>63</v>
       </c>
       <c r="C668" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="669" spans="1:3">
@@ -7760,7 +7749,7 @@
         <v>32</v>
       </c>
       <c r="C669" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="670" spans="1:3">
@@ -7771,7 +7760,7 @@
         <v>63</v>
       </c>
       <c r="C670" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="671" spans="1:3">
@@ -7782,7 +7771,7 @@
         <v>31</v>
       </c>
       <c r="C671" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="672" spans="1:3">
@@ -7793,7 +7782,7 @@
         <v>29</v>
       </c>
       <c r="C672" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="673" spans="1:3">
@@ -7804,7 +7793,7 @@
         <v>49</v>
       </c>
       <c r="C673" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="674" spans="1:3">
@@ -7815,7 +7804,7 @@
         <v>50</v>
       </c>
       <c r="C674" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="675" spans="1:3">
@@ -7826,7 +7815,7 @@
         <v>40</v>
       </c>
       <c r="C675" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="676" spans="1:3">
@@ -7837,7 +7826,7 @@
         <v>43</v>
       </c>
       <c r="C676" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="677" spans="1:3">
@@ -7848,7 +7837,7 @@
         <v>46</v>
       </c>
       <c r="C677" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="678" spans="1:3">
@@ -7870,7 +7859,7 @@
         <v>45</v>
       </c>
       <c r="C679" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="680" spans="1:3">
@@ -7881,7 +7870,7 @@
         <v>52</v>
       </c>
       <c r="C680" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="681" spans="1:3">
@@ -7892,7 +7881,7 @@
         <v>18</v>
       </c>
       <c r="C681" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="682" spans="1:3">
@@ -7903,7 +7892,7 @@
         <v>43</v>
       </c>
       <c r="C682" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="683" spans="1:3">
@@ -7914,7 +7903,7 @@
         <v>60</v>
       </c>
       <c r="C683" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="684" spans="1:3">
@@ -7925,7 +7914,7 @@
         <v>30</v>
       </c>
       <c r="C684" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="685" spans="1:3">
@@ -7936,7 +7925,7 @@
         <v>54</v>
       </c>
       <c r="C685" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="686" spans="1:3">
@@ -7958,7 +7947,7 @@
         <v>36</v>
       </c>
       <c r="C687" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="688" spans="1:3">
@@ -7980,7 +7969,7 @@
         <v>61</v>
       </c>
       <c r="C689" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="690" spans="1:3">
@@ -7991,7 +7980,7 @@
         <v>28</v>
       </c>
       <c r="C690" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="691" spans="1:3">
@@ -8002,7 +7991,7 @@
         <v>23</v>
       </c>
       <c r="C691" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="692" spans="1:3">
@@ -8013,7 +8002,7 @@
         <v>43</v>
       </c>
       <c r="C692" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="693" spans="1:3">
@@ -8024,7 +8013,7 @@
         <v>57</v>
       </c>
       <c r="C693" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="694" spans="1:3">
@@ -8035,7 +8024,7 @@
         <v>35</v>
       </c>
       <c r="C694" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="695" spans="1:3">
@@ -8046,7 +8035,7 @@
         <v>53</v>
       </c>
       <c r="C695" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="696" spans="1:3">
@@ -8057,7 +8046,7 @@
         <v>28</v>
       </c>
       <c r="C696" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="697" spans="1:3">
@@ -8068,7 +8057,7 @@
         <v>65</v>
       </c>
       <c r="C697" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="698" spans="1:3">
@@ -8079,7 +8068,7 @@
         <v>53</v>
       </c>
       <c r="C698" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="699" spans="1:3">
@@ -8090,7 +8079,7 @@
         <v>53</v>
       </c>
       <c r="C699" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="700" spans="1:3">
@@ -8101,7 +8090,7 @@
         <v>36</v>
       </c>
       <c r="C700" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="701" spans="1:3">
@@ -8112,7 +8101,7 @@
         <v>53</v>
       </c>
       <c r="C701" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="702" spans="1:3">
@@ -8123,7 +8112,7 @@
         <v>45</v>
       </c>
       <c r="C702" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="703" spans="1:3">
@@ -8134,7 +8123,7 @@
         <v>39</v>
       </c>
       <c r="C703" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="704" spans="1:3">
@@ -8145,7 +8134,7 @@
         <v>27</v>
       </c>
       <c r="C704" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="705" spans="1:3">
@@ -8156,7 +8145,7 @@
         <v>43</v>
       </c>
       <c r="C705" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="706" spans="1:3">
@@ -8167,7 +8156,7 @@
         <v>60</v>
       </c>
       <c r="C706" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="707" spans="1:3">
@@ -8178,7 +8167,7 @@
         <v>17</v>
       </c>
       <c r="C707" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="708" spans="1:3">
@@ -8189,7 +8178,7 @@
         <v>32</v>
       </c>
       <c r="C708" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="709" spans="1:3">
@@ -8200,7 +8189,7 @@
         <v>30</v>
       </c>
       <c r="C709" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="710" spans="1:3">
@@ -8211,7 +8200,7 @@
         <v>29</v>
       </c>
       <c r="C710" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="711" spans="1:3">
@@ -8222,7 +8211,7 @@
         <v>41</v>
       </c>
       <c r="C711" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="712" spans="1:3">
@@ -8233,7 +8222,7 @@
         <v>36</v>
       </c>
       <c r="C712" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="713" spans="1:3">
@@ -8255,7 +8244,7 @@
         <v>43</v>
       </c>
       <c r="C714" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="715" spans="1:3">
@@ -8266,7 +8255,7 @@
         <v>59</v>
       </c>
       <c r="C715" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="716" spans="1:3">
@@ -8277,7 +8266,7 @@
         <v>26</v>
       </c>
       <c r="C716" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="717" spans="1:3">
@@ -8288,7 +8277,7 @@
         <v>22</v>
       </c>
       <c r="C717" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="718" spans="1:3">
@@ -8299,7 +8288,7 @@
         <v>28</v>
       </c>
       <c r="C718" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="719" spans="1:3">
@@ -8310,7 +8299,7 @@
         <v>57</v>
       </c>
       <c r="C719" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="720" spans="1:3">
@@ -8321,7 +8310,7 @@
         <v>56</v>
       </c>
       <c r="C720" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="721" spans="1:3">
@@ -8332,7 +8321,7 @@
         <v>57</v>
       </c>
       <c r="C721" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="722" spans="1:3">
@@ -8343,7 +8332,7 @@
         <v>54</v>
       </c>
       <c r="C722" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="723" spans="1:3">
@@ -8354,7 +8343,7 @@
         <v>57</v>
       </c>
       <c r="C723" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="724" spans="1:3">
@@ -8376,7 +8365,7 @@
         <v>65</v>
       </c>
       <c r="C725" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="726" spans="1:3">
@@ -8387,7 +8376,7 @@
         <v>45</v>
       </c>
       <c r="C726" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="727" spans="1:3">
@@ -8398,7 +8387,7 @@
         <v>35</v>
       </c>
       <c r="C727" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="728" spans="1:3">
@@ -8409,7 +8398,7 @@
         <v>63</v>
       </c>
       <c r="C728" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="729" spans="1:3">
@@ -8420,7 +8409,7 @@
         <v>58</v>
       </c>
       <c r="C729" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="730" spans="1:3">
@@ -8431,7 +8420,7 @@
         <v>47</v>
       </c>
       <c r="C730" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="731" spans="1:3">
@@ -8442,7 +8431,7 @@
         <v>24</v>
       </c>
       <c r="C731" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="732" spans="1:3">
@@ -8453,7 +8442,7 @@
         <v>26</v>
       </c>
       <c r="C732" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="733" spans="1:3">
@@ -8464,7 +8453,7 @@
         <v>19</v>
       </c>
       <c r="C733" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="734" spans="1:3">
@@ -8497,7 +8486,7 @@
         <v>34</v>
       </c>
       <c r="C736" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="737" spans="1:3">
@@ -8508,7 +8497,7 @@
         <v>28</v>
       </c>
       <c r="C737" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="738" spans="1:3">
@@ -8519,7 +8508,7 @@
         <v>53</v>
       </c>
       <c r="C738" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="739" spans="1:3">
@@ -8530,7 +8519,7 @@
         <v>33</v>
       </c>
       <c r="C739" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="740" spans="1:3">
@@ -8541,7 +8530,7 @@
         <v>19</v>
       </c>
       <c r="C740" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="741" spans="1:3">
@@ -8552,7 +8541,7 @@
         <v>46</v>
       </c>
       <c r="C741" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="742" spans="1:3">
@@ -8563,7 +8552,7 @@
         <v>20</v>
       </c>
       <c r="C742" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="743" spans="1:3">
@@ -8574,7 +8563,7 @@
         <v>54</v>
       </c>
       <c r="C743" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="744" spans="1:3">
@@ -8585,7 +8574,7 @@
         <v>21</v>
       </c>
       <c r="C744" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="745" spans="1:3">
@@ -8596,7 +8585,7 @@
         <v>44</v>
       </c>
       <c r="C745" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="746" spans="1:3">
@@ -8607,7 +8596,7 @@
         <v>27</v>
       </c>
       <c r="C746" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="747" spans="1:3">
@@ -8618,7 +8607,7 @@
         <v>48</v>
       </c>
       <c r="C747" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="748" spans="1:3">
@@ -8629,7 +8618,7 @@
         <v>58</v>
       </c>
       <c r="C748" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="749" spans="1:3">
@@ -8640,7 +8629,7 @@
         <v>31</v>
       </c>
       <c r="C749" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="750" spans="1:3">
@@ -8651,7 +8640,7 @@
         <v>42</v>
       </c>
       <c r="C750" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="751" spans="1:3">
@@ -8662,7 +8651,7 @@
         <v>21</v>
       </c>
       <c r="C751" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="752" spans="1:3">
@@ -8673,7 +8662,7 @@
         <v>60</v>
       </c>
       <c r="C752" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="753" spans="1:3">
@@ -8684,7 +8673,7 @@
         <v>63</v>
       </c>
       <c r="C753" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="754" spans="1:3">
@@ -8695,7 +8684,7 @@
         <v>52</v>
       </c>
       <c r="C754" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="755" spans="1:3">
@@ -8706,7 +8695,7 @@
         <v>30</v>
       </c>
       <c r="C755" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="756" spans="1:3">
@@ -8717,7 +8706,7 @@
         <v>54</v>
       </c>
       <c r="C756" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="757" spans="1:3">
@@ -8728,7 +8717,7 @@
         <v>32</v>
       </c>
       <c r="C757" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="758" spans="1:3">
@@ -8739,7 +8728,7 @@
         <v>18</v>
       </c>
       <c r="C758" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="759" spans="1:3">
@@ -8750,7 +8739,7 @@
         <v>26</v>
       </c>
       <c r="C759" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="760" spans="1:3">
@@ -8761,7 +8750,7 @@
         <v>16</v>
       </c>
       <c r="C760" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="761" spans="1:3">
@@ -8772,7 +8761,7 @@
         <v>57</v>
       </c>
       <c r="C761" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="762" spans="1:3">
@@ -8783,7 +8772,7 @@
         <v>42</v>
       </c>
       <c r="C762" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="763" spans="1:3">
@@ -8805,7 +8794,7 @@
         <v>45</v>
       </c>
       <c r="C764" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="765" spans="1:3">
@@ -8816,7 +8805,7 @@
         <v>47</v>
       </c>
       <c r="C765" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="766" spans="1:3">
@@ -8827,7 +8816,7 @@
         <v>45</v>
       </c>
       <c r="C766" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="767" spans="1:3">
@@ -8838,7 +8827,7 @@
         <v>26</v>
       </c>
       <c r="C767" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="768" spans="1:3">
@@ -8849,7 +8838,7 @@
         <v>58</v>
       </c>
       <c r="C768" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="769" spans="1:3">
@@ -8860,7 +8849,7 @@
         <v>41</v>
       </c>
       <c r="C769" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="770" spans="1:3">
@@ -8871,7 +8860,7 @@
         <v>32</v>
       </c>
       <c r="C770" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="771" spans="1:3">
@@ -8893,7 +8882,7 @@
         <v>39</v>
       </c>
       <c r="C772" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="773" spans="1:3">
@@ -8904,7 +8893,7 @@
         <v>18</v>
       </c>
       <c r="C773" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="774" spans="1:3">
@@ -8915,7 +8904,7 @@
         <v>29</v>
       </c>
       <c r="C774" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="775" spans="1:3">
@@ -8926,7 +8915,7 @@
         <v>25</v>
       </c>
       <c r="C775" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="776" spans="1:3">
@@ -8937,7 +8926,7 @@
         <v>29</v>
       </c>
       <c r="C776" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="777" spans="1:3">
@@ -8959,7 +8948,7 @@
         <v>44</v>
       </c>
       <c r="C778" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="779" spans="1:3">
@@ -8970,7 +8959,7 @@
         <v>18</v>
       </c>
       <c r="C779" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="780" spans="1:3">
@@ -8981,7 +8970,7 @@
         <v>35</v>
       </c>
       <c r="C780" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="781" spans="1:3">
@@ -8992,7 +8981,7 @@
         <v>31</v>
       </c>
       <c r="C781" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="782" spans="1:3">
@@ -9025,7 +9014,7 @@
         <v>18</v>
       </c>
       <c r="C784" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="785" spans="1:3">
@@ -9036,7 +9025,7 @@
         <v>52</v>
       </c>
       <c r="C785" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="786" spans="1:3">
@@ -9047,7 +9036,7 @@
         <v>65</v>
       </c>
       <c r="C786" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="787" spans="1:3">
@@ -9058,7 +9047,7 @@
         <v>17</v>
       </c>
       <c r="C787" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="788" spans="1:3">
@@ -9069,7 +9058,7 @@
         <v>30</v>
       </c>
       <c r="C788" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="789" spans="1:3">
@@ -9080,7 +9069,7 @@
         <v>23</v>
       </c>
       <c r="C789" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="790" spans="1:3">
@@ -9091,7 +9080,7 @@
         <v>53</v>
       </c>
       <c r="C790" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="791" spans="1:3">
@@ -9102,7 +9091,7 @@
         <v>50</v>
       </c>
       <c r="C791" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="792" spans="1:3">
@@ -9113,7 +9102,7 @@
         <v>64</v>
       </c>
       <c r="C792" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="793" spans="1:3">
@@ -9124,7 +9113,7 @@
         <v>53</v>
       </c>
       <c r="C793" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="794" spans="1:3">
@@ -9135,7 +9124,7 @@
         <v>43</v>
       </c>
       <c r="C794" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="795" spans="1:3">
@@ -9146,7 +9135,7 @@
         <v>38</v>
       </c>
       <c r="C795" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="796" spans="1:3">
@@ -9157,7 +9146,7 @@
         <v>51</v>
       </c>
       <c r="C796" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="797" spans="1:3">
@@ -9168,7 +9157,7 @@
         <v>64</v>
       </c>
       <c r="C797" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="798" spans="1:3">
@@ -9179,7 +9168,7 @@
         <v>27</v>
       </c>
       <c r="C798" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="799" spans="1:3">
@@ -9190,7 +9179,7 @@
         <v>62</v>
       </c>
       <c r="C799" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="800" spans="1:3">
@@ -9201,7 +9190,7 @@
         <v>26</v>
       </c>
       <c r="C800" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="801" spans="1:3">
@@ -9223,7 +9212,7 @@
         <v>38</v>
       </c>
       <c r="C802" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="803" spans="1:3">
@@ -9234,7 +9223,7 @@
         <v>59</v>
       </c>
       <c r="C803" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="804" spans="1:3">
@@ -9245,7 +9234,7 @@
         <v>24</v>
       </c>
       <c r="C804" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="805" spans="1:3">
@@ -9256,7 +9245,7 @@
         <v>20</v>
       </c>
       <c r="C805" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="806" spans="1:3">
@@ -9267,7 +9256,7 @@
         <v>55</v>
       </c>
       <c r="C806" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="807" spans="1:3">
@@ -9278,7 +9267,7 @@
         <v>26</v>
       </c>
       <c r="C807" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="808" spans="1:3">
@@ -9289,7 +9278,7 @@
         <v>36</v>
       </c>
       <c r="C808" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="809" spans="1:3">
@@ -9300,7 +9289,7 @@
         <v>22</v>
       </c>
       <c r="C809" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="810" spans="1:3">
@@ -9311,7 +9300,7 @@
         <v>33</v>
       </c>
       <c r="C810" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="811" spans="1:3">
@@ -9333,7 +9322,7 @@
         <v>51</v>
       </c>
       <c r="C812" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="813" spans="1:3">
@@ -9344,7 +9333,7 @@
         <v>53</v>
       </c>
       <c r="C813" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="814" spans="1:3">
@@ -9355,7 +9344,7 @@
         <v>46</v>
       </c>
       <c r="C814" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="815" spans="1:3">
@@ -9366,7 +9355,7 @@
         <v>43</v>
       </c>
       <c r="C815" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="816" spans="1:3">
@@ -9377,7 +9366,7 @@
         <v>51</v>
       </c>
       <c r="C816" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="817" spans="1:3">
@@ -9388,7 +9377,7 @@
         <v>23</v>
       </c>
       <c r="C817" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="818" spans="1:3">
@@ -9399,7 +9388,7 @@
         <v>60</v>
       </c>
       <c r="C818" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="819" spans="1:3">
@@ -9410,7 +9399,7 @@
         <v>48</v>
       </c>
       <c r="C819" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="820" spans="1:3">
@@ -9432,7 +9421,7 @@
         <v>37</v>
       </c>
       <c r="C821" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="822" spans="1:3">
@@ -9443,7 +9432,7 @@
         <v>45</v>
       </c>
       <c r="C822" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="823" spans="1:3">
@@ -9454,7 +9443,7 @@
         <v>22</v>
       </c>
       <c r="C823" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="824" spans="1:3">
@@ -9465,7 +9454,7 @@
         <v>33</v>
       </c>
       <c r="C824" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="825" spans="1:3">
@@ -9476,7 +9465,7 @@
         <v>30</v>
       </c>
       <c r="C825" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="826" spans="1:3">
@@ -9487,7 +9476,7 @@
         <v>23</v>
       </c>
       <c r="C826" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="827" spans="1:3">
@@ -9498,7 +9487,7 @@
         <v>22</v>
       </c>
       <c r="C827" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="828" spans="1:3">
@@ -9520,7 +9509,7 @@
         <v>55</v>
       </c>
       <c r="C829" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="830" spans="1:3">
@@ -9531,7 +9520,7 @@
         <v>24</v>
       </c>
       <c r="C830" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="831" spans="1:3">
@@ -9542,7 +9531,7 @@
         <v>39</v>
       </c>
       <c r="C831" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="832" spans="1:3">
@@ -9553,7 +9542,7 @@
         <v>28</v>
       </c>
       <c r="C832" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="833" spans="1:3">
@@ -9564,7 +9553,7 @@
         <v>59</v>
       </c>
       <c r="C833" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="834" spans="1:3">
@@ -9575,7 +9564,7 @@
         <v>21</v>
       </c>
       <c r="C834" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="835" spans="1:3">
@@ -9586,7 +9575,7 @@
         <v>64</v>
       </c>
       <c r="C835" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="836" spans="1:3">
@@ -9597,7 +9586,7 @@
         <v>16</v>
       </c>
       <c r="C836" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="837" spans="1:3">
@@ -9608,7 +9597,7 @@
         <v>59</v>
       </c>
       <c r="C837" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="838" spans="1:3">
@@ -9619,7 +9608,7 @@
         <v>55</v>
       </c>
       <c r="C838" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="839" spans="1:3">
@@ -9630,7 +9619,7 @@
         <v>40</v>
       </c>
       <c r="C839" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="840" spans="1:3">
@@ -9641,7 +9630,7 @@
         <v>27</v>
       </c>
       <c r="C840" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="841" spans="1:3">
@@ -9652,7 +9641,7 @@
         <v>23</v>
       </c>
       <c r="C841" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="842" spans="1:3">
@@ -9663,7 +9652,7 @@
         <v>24</v>
       </c>
       <c r="C842" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="843" spans="1:3">
@@ -9674,7 +9663,7 @@
         <v>60</v>
       </c>
       <c r="C843" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="844" spans="1:3">
@@ -9685,7 +9674,7 @@
         <v>46</v>
       </c>
       <c r="C844" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="845" spans="1:3">
@@ -9696,7 +9685,7 @@
         <v>42</v>
       </c>
       <c r="C845" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="846" spans="1:3">
@@ -9707,7 +9696,7 @@
         <v>40</v>
       </c>
       <c r="C846" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="847" spans="1:3">
@@ -9718,7 +9707,7 @@
         <v>44</v>
       </c>
       <c r="C847" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="848" spans="1:3">
@@ -9729,7 +9718,7 @@
         <v>64</v>
       </c>
       <c r="C848" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="849" spans="1:3">
@@ -9740,7 +9729,7 @@
         <v>19</v>
       </c>
       <c r="C849" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="850" spans="1:3">
@@ -9751,7 +9740,7 @@
         <v>49</v>
       </c>
       <c r="C850" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="851" spans="1:3">
@@ -9762,7 +9751,7 @@
         <v>65</v>
       </c>
       <c r="C851" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="852" spans="1:3">
@@ -9784,7 +9773,7 @@
         <v>32</v>
       </c>
       <c r="C853" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="854" spans="1:3">
@@ -9795,7 +9784,7 @@
         <v>62</v>
       </c>
       <c r="C854" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="855" spans="1:3">
@@ -9806,7 +9795,7 @@
         <v>27</v>
       </c>
       <c r="C855" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="856" spans="1:3">
@@ -9817,7 +9806,7 @@
         <v>50</v>
       </c>
       <c r="C856" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="857" spans="1:3">
@@ -9828,7 +9817,7 @@
         <v>45</v>
       </c>
       <c r="C857" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="858" spans="1:3">
@@ -9839,7 +9828,7 @@
         <v>55</v>
       </c>
       <c r="C858" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="859" spans="1:3">
@@ -9850,7 +9839,7 @@
         <v>50</v>
       </c>
       <c r="C859" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="860" spans="1:3">
@@ -9861,7 +9850,7 @@
         <v>32</v>
       </c>
       <c r="C860" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="861" spans="1:3">
@@ -9872,7 +9861,7 @@
         <v>42</v>
       </c>
       <c r="C861" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="862" spans="1:3">
@@ -9883,7 +9872,7 @@
         <v>52</v>
       </c>
       <c r="C862" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="863" spans="1:3">
@@ -9894,7 +9883,7 @@
         <v>51</v>
       </c>
       <c r="C863" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="864" spans="1:3">
@@ -9905,7 +9894,7 @@
         <v>50</v>
       </c>
       <c r="C864" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="865" spans="1:3">
@@ -9916,7 +9905,7 @@
         <v>36</v>
       </c>
       <c r="C865" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="866" spans="1:3">
@@ -9938,7 +9927,7 @@
         <v>57</v>
       </c>
       <c r="C867" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="868" spans="1:3">
@@ -9949,7 +9938,7 @@
         <v>40</v>
       </c>
       <c r="C868" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="869" spans="1:3">
@@ -9960,7 +9949,7 @@
         <v>18</v>
       </c>
       <c r="C869" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="870" spans="1:3">
@@ -9971,7 +9960,7 @@
         <v>46</v>
       </c>
       <c r="C870" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="871" spans="1:3">
@@ -9982,7 +9971,7 @@
         <v>26</v>
       </c>
       <c r="C871" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="872" spans="1:3">
@@ -9993,7 +9982,7 @@
         <v>34</v>
       </c>
       <c r="C872" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="873" spans="1:3">
@@ -10004,7 +9993,7 @@
         <v>18</v>
       </c>
       <c r="C873" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="874" spans="1:3">
@@ -10015,7 +10004,7 @@
         <v>26</v>
       </c>
       <c r="C874" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="875" spans="1:3">
@@ -10026,7 +10015,7 @@
         <v>29</v>
       </c>
       <c r="C875" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="876" spans="1:3">
@@ -10037,7 +10026,7 @@
         <v>29</v>
       </c>
       <c r="C876" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="877" spans="1:3">
@@ -10048,7 +10037,7 @@
         <v>41</v>
       </c>
       <c r="C877" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="878" spans="1:3">
@@ -10059,7 +10048,7 @@
         <v>40</v>
       </c>
       <c r="C878" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="879" spans="1:3">
@@ -10070,7 +10059,7 @@
         <v>30</v>
       </c>
       <c r="C879" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="880" spans="1:3">
@@ -10081,7 +10070,7 @@
         <v>27</v>
       </c>
       <c r="C880" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="881" spans="1:3">
@@ -10092,7 +10081,7 @@
         <v>18</v>
       </c>
       <c r="C881" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="882" spans="1:3">
@@ -10114,7 +10103,7 @@
         <v>32</v>
       </c>
       <c r="C883" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="884" spans="1:3">
@@ -10125,7 +10114,7 @@
         <v>27</v>
       </c>
       <c r="C884" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="885" spans="1:3">
@@ -10136,7 +10125,7 @@
         <v>49</v>
       </c>
       <c r="C885" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="886" spans="1:3">
@@ -10147,7 +10136,7 @@
         <v>33</v>
       </c>
       <c r="C886" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="887" spans="1:3">
@@ -10158,7 +10147,7 @@
         <v>26</v>
       </c>
       <c r="C887" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="888" spans="1:3">
@@ -10169,7 +10158,7 @@
         <v>27</v>
       </c>
       <c r="C888" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="889" spans="1:3">
@@ -10180,7 +10169,7 @@
         <v>58</v>
       </c>
       <c r="C889" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="890" spans="1:3">
@@ -10191,7 +10180,7 @@
         <v>50</v>
       </c>
       <c r="C890" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="891" spans="1:3">
@@ -10202,7 +10191,7 @@
         <v>35</v>
       </c>
       <c r="C891" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="892" spans="1:3">
@@ -10213,7 +10202,7 @@
         <v>19</v>
       </c>
       <c r="C892" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="893" spans="1:3">
@@ -10224,7 +10213,7 @@
         <v>62</v>
       </c>
       <c r="C893" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="894" spans="1:3">
@@ -10235,7 +10224,7 @@
         <v>63</v>
       </c>
       <c r="C894" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="895" spans="1:3">
@@ -10246,7 +10235,7 @@
         <v>64</v>
       </c>
       <c r="C895" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="896" spans="1:3">
@@ -10257,7 +10246,7 @@
         <v>42</v>
       </c>
       <c r="C896" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="897" spans="1:3">
@@ -10268,7 +10257,7 @@
         <v>24</v>
       </c>
       <c r="C897" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="898" spans="1:3">
@@ -10279,7 +10268,7 @@
         <v>23</v>
       </c>
       <c r="C898" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="899" spans="1:3">
@@ -10290,7 +10279,7 @@
         <v>45</v>
       </c>
       <c r="C899" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="900" spans="1:3">
@@ -10301,7 +10290,7 @@
         <v>25</v>
       </c>
       <c r="C900" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="901" spans="1:3">
@@ -10312,7 +10301,7 @@
         <v>28</v>
       </c>
       <c r="C901" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="902" spans="1:3">
@@ -10323,7 +10312,7 @@
         <v>17</v>
       </c>
       <c r="C902" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="903" spans="1:3">
@@ -10345,7 +10334,7 @@
         <v>33</v>
       </c>
       <c r="C904" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="905" spans="1:3">
@@ -10356,7 +10345,7 @@
         <v>38</v>
       </c>
       <c r="C905" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="906" spans="1:3">
@@ -10378,7 +10367,7 @@
         <v>65</v>
       </c>
       <c r="C907" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="908" spans="1:3">
@@ -10389,7 +10378,7 @@
         <v>37</v>
       </c>
       <c r="C908" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="909" spans="1:3">
@@ -10400,7 +10389,7 @@
         <v>59</v>
       </c>
       <c r="C909" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="910" spans="1:3">
@@ -10411,7 +10400,7 @@
         <v>43</v>
       </c>
       <c r="C910" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="911" spans="1:3">
@@ -10422,7 +10411,7 @@
         <v>39</v>
       </c>
       <c r="C911" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="912" spans="1:3">
@@ -10433,7 +10422,7 @@
         <v>21</v>
       </c>
       <c r="C912" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="913" spans="1:3">
@@ -10444,7 +10433,7 @@
         <v>50</v>
       </c>
       <c r="C913" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="914" spans="1:3">
@@ -10455,7 +10444,7 @@
         <v>42</v>
       </c>
       <c r="C914" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="915" spans="1:3">
@@ -10466,7 +10455,7 @@
         <v>62</v>
       </c>
       <c r="C915" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="916" spans="1:3">
@@ -10477,7 +10466,7 @@
         <v>56</v>
       </c>
       <c r="C916" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="917" spans="1:3">
@@ -10488,7 +10477,7 @@
         <v>36</v>
       </c>
       <c r="C917" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="918" spans="1:3">
@@ -10499,7 +10488,7 @@
         <v>17</v>
       </c>
       <c r="C918" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="919" spans="1:3">
@@ -10510,7 +10499,7 @@
         <v>39</v>
       </c>
       <c r="C919" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="920" spans="1:3">
@@ -10521,7 +10510,7 @@
         <v>57</v>
       </c>
       <c r="C920" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="921" spans="1:3">
@@ -10532,7 +10521,7 @@
         <v>55</v>
       </c>
       <c r="C921" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="922" spans="1:3">
@@ -10543,7 +10532,7 @@
         <v>20</v>
       </c>
       <c r="C922" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="923" spans="1:3">
@@ -10554,7 +10543,7 @@
         <v>55</v>
       </c>
       <c r="C923" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="924" spans="1:3">
@@ -10565,7 +10554,7 @@
         <v>40</v>
       </c>
       <c r="C924" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="925" spans="1:3">
@@ -10576,7 +10565,7 @@
         <v>18</v>
       </c>
       <c r="C925" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="926" spans="1:3">
@@ -10587,7 +10576,7 @@
         <v>42</v>
       </c>
       <c r="C926" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="927" spans="1:3">
@@ -10598,7 +10587,7 @@
         <v>54</v>
       </c>
       <c r="C927" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="928" spans="1:3">
@@ -10609,7 +10598,7 @@
         <v>41</v>
       </c>
       <c r="C928" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="929" spans="1:3">
@@ -10631,7 +10620,7 @@
         <v>29</v>
       </c>
       <c r="C930" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="931" spans="1:3">
@@ -10653,7 +10642,7 @@
         <v>21</v>
       </c>
       <c r="C932" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="933" spans="1:3">
@@ -10664,7 +10653,7 @@
         <v>38</v>
       </c>
       <c r="C933" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="934" spans="1:3">
@@ -10675,7 +10664,7 @@
         <v>46</v>
       </c>
       <c r="C934" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="935" spans="1:3">
@@ -10686,7 +10675,7 @@
         <v>49</v>
       </c>
       <c r="C935" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="936" spans="1:3">
@@ -10708,7 +10697,7 @@
         <v>59</v>
       </c>
       <c r="C937" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="938" spans="1:3">
@@ -10719,7 +10708,7 @@
         <v>17</v>
       </c>
       <c r="C938" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="939" spans="1:3">
@@ -10730,7 +10719,7 @@
         <v>23</v>
       </c>
       <c r="C939" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="940" spans="1:3">
@@ -10741,7 +10730,7 @@
         <v>52</v>
       </c>
       <c r="C940" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="941" spans="1:3">
@@ -10752,7 +10741,7 @@
         <v>37</v>
       </c>
       <c r="C941" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="942" spans="1:3">
@@ -10763,7 +10752,7 @@
         <v>34</v>
       </c>
       <c r="C942" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="943" spans="1:3">
@@ -10774,7 +10763,7 @@
         <v>56</v>
       </c>
       <c r="C943" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="944" spans="1:3">
@@ -10785,7 +10774,7 @@
         <v>40</v>
       </c>
       <c r="C944" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="945" spans="1:3">
@@ -10818,7 +10807,7 @@
         <v>38</v>
       </c>
       <c r="C947" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="948" spans="1:3">
@@ -10829,7 +10818,7 @@
         <v>59</v>
       </c>
       <c r="C948" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="949" spans="1:3">
@@ -10851,7 +10840,7 @@
         <v>31</v>
       </c>
       <c r="C950" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="951" spans="1:3">
@@ -10862,7 +10851,7 @@
         <v>23</v>
       </c>
       <c r="C951" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="952" spans="1:3">
@@ -10873,7 +10862,7 @@
         <v>28</v>
       </c>
       <c r="C952" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="953" spans="1:3">
@@ -10895,7 +10884,7 @@
         <v>54</v>
       </c>
       <c r="C954" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="955" spans="1:3">
@@ -10906,7 +10895,7 @@
         <v>55</v>
       </c>
       <c r="C955" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="956" spans="1:3">
@@ -10917,7 +10906,7 @@
         <v>62</v>
       </c>
       <c r="C956" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="957" spans="1:3">
@@ -10928,7 +10917,7 @@
         <v>44</v>
       </c>
       <c r="C957" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="958" spans="1:3">
@@ -10939,7 +10928,7 @@
         <v>63</v>
       </c>
       <c r="C958" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="959" spans="1:3">
@@ -10950,7 +10939,7 @@
         <v>24</v>
       </c>
       <c r="C959" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="960" spans="1:3">
@@ -10961,7 +10950,7 @@
         <v>24</v>
       </c>
       <c r="C960" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="961" spans="1:3">
@@ -10972,7 +10961,7 @@
         <v>33</v>
       </c>
       <c r="C961" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="962" spans="1:3">
@@ -10983,7 +10972,7 @@
         <v>62</v>
       </c>
       <c r="C962" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="963" spans="1:3">
@@ -10994,7 +10983,7 @@
         <v>58</v>
       </c>
       <c r="C963" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="964" spans="1:3">
@@ -11016,7 +11005,7 @@
         <v>61</v>
       </c>
       <c r="C965" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="966" spans="1:3">
@@ -11027,7 +11016,7 @@
         <v>21</v>
       </c>
       <c r="C966" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="967" spans="1:3">
@@ -11049,7 +11038,7 @@
         <v>24</v>
       </c>
       <c r="C968" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="969" spans="1:3">
@@ -11071,7 +11060,7 @@
         <v>62</v>
       </c>
       <c r="C970" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="971" spans="1:3">
@@ -11082,7 +11071,7 @@
         <v>36</v>
       </c>
       <c r="C971" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="972" spans="1:3">
@@ -11093,7 +11082,7 @@
         <v>41</v>
       </c>
       <c r="C972" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="973" spans="1:3">
@@ -11104,7 +11093,7 @@
         <v>62</v>
       </c>
       <c r="C973" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="974" spans="1:3">
@@ -11126,7 +11115,7 @@
         <v>23</v>
       </c>
       <c r="C975" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="976" spans="1:3">
@@ -11137,7 +11126,7 @@
         <v>18</v>
       </c>
       <c r="C976" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="977" spans="1:3">
@@ -11148,7 +11137,7 @@
         <v>30</v>
       </c>
       <c r="C977" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="978" spans="1:3">
@@ -11159,7 +11148,7 @@
         <v>58</v>
       </c>
       <c r="C978" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="979" spans="1:3">
@@ -11170,7 +11159,7 @@
         <v>31</v>
       </c>
       <c r="C979" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="980" spans="1:3">
@@ -11181,7 +11170,7 @@
         <v>26</v>
       </c>
       <c r="C980" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="981" spans="1:3">
@@ -11192,7 +11181,7 @@
         <v>61</v>
       </c>
       <c r="C981" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="982" spans="1:3">
@@ -11203,7 +11192,7 @@
         <v>28</v>
       </c>
       <c r="C982" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="983" spans="1:3">
@@ -11214,7 +11203,7 @@
         <v>48</v>
       </c>
       <c r="C983" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="984" spans="1:3">
@@ -11225,7 +11214,7 @@
         <v>36</v>
       </c>
       <c r="C984" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="985" spans="1:3">
@@ -11236,7 +11225,7 @@
         <v>29</v>
       </c>
       <c r="C985" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="986" spans="1:3">
@@ -11247,7 +11236,7 @@
         <v>35</v>
       </c>
       <c r="C986" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="987" spans="1:3">
@@ -11258,7 +11247,7 @@
         <v>32</v>
       </c>
       <c r="C987" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="988" spans="1:3">
@@ -11269,7 +11258,7 @@
         <v>47</v>
       </c>
       <c r="C988" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="989" spans="1:3">
@@ -11280,7 +11269,7 @@
         <v>27</v>
       </c>
       <c r="C989" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="990" spans="1:3">
@@ -11302,7 +11291,7 @@
         <v>47</v>
       </c>
       <c r="C991" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="992" spans="1:3">
@@ -11324,7 +11313,7 @@
         <v>24</v>
       </c>
       <c r="C993" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="994" spans="1:3">
@@ -11335,7 +11324,7 @@
         <v>43</v>
       </c>
       <c r="C994" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="995" spans="1:3">
@@ -11346,7 +11335,7 @@
         <v>58</v>
       </c>
       <c r="C995" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="996" spans="1:3">
@@ -11357,7 +11346,7 @@
         <v>22</v>
       </c>
       <c r="C996" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="997" spans="1:3">
@@ -11368,7 +11357,7 @@
         <v>25</v>
       </c>
       <c r="C997" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="998" spans="1:3">
@@ -11379,7 +11368,7 @@
         <v>44</v>
       </c>
       <c r="C998" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="999" spans="1:3">
@@ -11401,7 +11390,7 @@
         <v>58</v>
       </c>
       <c r="C1000" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1001" spans="1:3">
@@ -11412,7 +11401,7 @@
         <v>63</v>
       </c>
       <c r="C1001" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="10">
   <si>
     <t>user_id</t>
   </si>
@@ -25,48 +25,41 @@
     <t>country</t>
   </si>
   <si>
-    <t>درعا</t>
+    <t>Qatar</t>
   </si>
   <si>
-    <t>حلب</t>
+    <t>Jordan</t>
   </si>
   <si>
-    <t>دمشق</t>
+    <t>Morocco</t>
   </si>
   <si>
-    <t>القنيطرة</t>
+    <t>Egypt</t>
   </si>
   <si>
-    <t>اللاذقية</t>
+    <t>UAE</t>
   </si>
   <si>
-    <t>حماة</t>
+    <t>Kuwait</t>
   </si>
   <si>
-    <t>حمص</t>
-  </si>
-  <si>
-    <t>إدلب</t>
-  </si>
-  <si>
-    <t>السويداء</t>
-  </si>
-  <si>
-    <t>دير الزور</t>
-  </si>
-  <si>
-    <t>الرقة</t>
-  </si>
-  <si>
-    <t>طرطوس</t>
+    <t>Saudi Arabia</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -82,7 +75,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -90,12 +83,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -394,13 +405,13 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -478,7 +489,7 @@
         <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -489,7 +500,7 @@
         <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -500,7 +511,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -511,7 +522,7 @@
         <v>54</v>
       </c>
       <c r="C11" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -522,7 +533,7 @@
         <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -544,7 +555,7 @@
         <v>51</v>
       </c>
       <c r="C14" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -555,7 +566,7 @@
         <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -566,7 +577,7 @@
         <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -577,7 +588,7 @@
         <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -588,7 +599,7 @@
         <v>40</v>
       </c>
       <c r="C18" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -599,7 +610,7 @@
         <v>49</v>
       </c>
       <c r="C19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -610,7 +621,7 @@
         <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -621,7 +632,7 @@
         <v>53</v>
       </c>
       <c r="C21" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -632,7 +643,7 @@
         <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -643,7 +654,7 @@
         <v>30</v>
       </c>
       <c r="C23" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -654,7 +665,7 @@
         <v>50</v>
       </c>
       <c r="C24" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -665,7 +676,7 @@
         <v>63</v>
       </c>
       <c r="C25" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -676,7 +687,7 @@
         <v>53</v>
       </c>
       <c r="C26" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -687,7 +698,7 @@
         <v>18</v>
       </c>
       <c r="C27" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -698,7 +709,7 @@
         <v>51</v>
       </c>
       <c r="C28" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -709,7 +720,7 @@
         <v>42</v>
       </c>
       <c r="C29" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -720,7 +731,7 @@
         <v>59</v>
       </c>
       <c r="C30" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -731,7 +742,7 @@
         <v>24</v>
       </c>
       <c r="C31" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -742,7 +753,7 @@
         <v>43</v>
       </c>
       <c r="C32" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -753,7 +764,7 @@
         <v>65</v>
       </c>
       <c r="C33" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -764,7 +775,7 @@
         <v>41</v>
       </c>
       <c r="C34" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -775,7 +786,7 @@
         <v>31</v>
       </c>
       <c r="C35" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -786,7 +797,7 @@
         <v>33</v>
       </c>
       <c r="C36" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -797,7 +808,7 @@
         <v>25</v>
       </c>
       <c r="C37" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -819,7 +830,7 @@
         <v>29</v>
       </c>
       <c r="C39" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -830,7 +841,7 @@
         <v>47</v>
       </c>
       <c r="C40" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -841,7 +852,7 @@
         <v>32</v>
       </c>
       <c r="C41" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -852,7 +863,7 @@
         <v>54</v>
       </c>
       <c r="C42" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -885,7 +896,7 @@
         <v>56</v>
       </c>
       <c r="C45" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -896,7 +907,7 @@
         <v>57</v>
       </c>
       <c r="C46" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -907,7 +918,7 @@
         <v>31</v>
       </c>
       <c r="C47" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -918,7 +929,7 @@
         <v>25</v>
       </c>
       <c r="C48" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -929,7 +940,7 @@
         <v>32</v>
       </c>
       <c r="C49" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -940,7 +951,7 @@
         <v>55</v>
       </c>
       <c r="C50" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -951,7 +962,7 @@
         <v>49</v>
       </c>
       <c r="C51" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -962,7 +973,7 @@
         <v>23</v>
       </c>
       <c r="C52" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -973,7 +984,7 @@
         <v>24</v>
       </c>
       <c r="C53" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -984,7 +995,7 @@
         <v>39</v>
       </c>
       <c r="C54" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1006,7 +1017,7 @@
         <v>19</v>
       </c>
       <c r="C56" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1017,7 +1028,7 @@
         <v>50</v>
       </c>
       <c r="C57" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1028,7 +1039,7 @@
         <v>40</v>
       </c>
       <c r="C58" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1039,7 +1050,7 @@
         <v>54</v>
       </c>
       <c r="C59" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1050,7 +1061,7 @@
         <v>21</v>
       </c>
       <c r="C60" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1061,7 +1072,7 @@
         <v>24</v>
       </c>
       <c r="C61" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1083,7 +1094,7 @@
         <v>23</v>
       </c>
       <c r="C63" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1094,7 +1105,7 @@
         <v>64</v>
       </c>
       <c r="C64" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1105,7 +1116,7 @@
         <v>20</v>
       </c>
       <c r="C65" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1116,7 +1127,7 @@
         <v>63</v>
       </c>
       <c r="C66" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1127,7 +1138,7 @@
         <v>50</v>
       </c>
       <c r="C67" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1149,7 +1160,7 @@
         <v>18</v>
       </c>
       <c r="C69" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1182,7 +1193,7 @@
         <v>28</v>
       </c>
       <c r="C72" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1193,7 +1204,7 @@
         <v>23</v>
       </c>
       <c r="C73" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1226,7 +1237,7 @@
         <v>58</v>
       </c>
       <c r="C76" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1237,7 +1248,7 @@
         <v>27</v>
       </c>
       <c r="C77" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1248,7 +1259,7 @@
         <v>52</v>
       </c>
       <c r="C78" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1259,7 +1270,7 @@
         <v>51</v>
       </c>
       <c r="C79" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1270,7 +1281,7 @@
         <v>54</v>
       </c>
       <c r="C80" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1281,7 +1292,7 @@
         <v>29</v>
       </c>
       <c r="C81" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1292,7 +1303,7 @@
         <v>57</v>
       </c>
       <c r="C82" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1303,7 +1314,7 @@
         <v>21</v>
       </c>
       <c r="C83" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1314,7 +1325,7 @@
         <v>54</v>
       </c>
       <c r="C84" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1325,7 +1336,7 @@
         <v>40</v>
       </c>
       <c r="C85" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1336,7 +1347,7 @@
         <v>31</v>
       </c>
       <c r="C86" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1347,7 +1358,7 @@
         <v>64</v>
       </c>
       <c r="C87" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1358,7 +1369,7 @@
         <v>47</v>
       </c>
       <c r="C88" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1380,7 +1391,7 @@
         <v>28</v>
       </c>
       <c r="C90" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1402,7 +1413,7 @@
         <v>64</v>
       </c>
       <c r="C92" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1413,7 +1424,7 @@
         <v>42</v>
       </c>
       <c r="C93" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1424,7 +1435,7 @@
         <v>53</v>
       </c>
       <c r="C94" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1435,7 +1446,7 @@
         <v>23</v>
       </c>
       <c r="C95" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1446,7 +1457,7 @@
         <v>63</v>
       </c>
       <c r="C96" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1457,7 +1468,7 @@
         <v>52</v>
       </c>
       <c r="C97" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1468,7 +1479,7 @@
         <v>63</v>
       </c>
       <c r="C98" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -1479,7 +1490,7 @@
         <v>35</v>
       </c>
       <c r="C99" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -1490,7 +1501,7 @@
         <v>52</v>
       </c>
       <c r="C100" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -1501,7 +1512,7 @@
         <v>37</v>
       </c>
       <c r="C101" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -1512,7 +1523,7 @@
         <v>46</v>
       </c>
       <c r="C102" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -1523,7 +1534,7 @@
         <v>20</v>
       </c>
       <c r="C103" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -1534,7 +1545,7 @@
         <v>20</v>
       </c>
       <c r="C104" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -1545,7 +1556,7 @@
         <v>61</v>
       </c>
       <c r="C105" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -1556,7 +1567,7 @@
         <v>40</v>
       </c>
       <c r="C106" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -1567,7 +1578,7 @@
         <v>31</v>
       </c>
       <c r="C107" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -1578,7 +1589,7 @@
         <v>56</v>
       </c>
       <c r="C108" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -1589,7 +1600,7 @@
         <v>57</v>
       </c>
       <c r="C109" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -1600,7 +1611,7 @@
         <v>24</v>
       </c>
       <c r="C110" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -1611,7 +1622,7 @@
         <v>26</v>
       </c>
       <c r="C111" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -1622,7 +1633,7 @@
         <v>64</v>
       </c>
       <c r="C112" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -1633,7 +1644,7 @@
         <v>62</v>
       </c>
       <c r="C113" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -1644,7 +1655,7 @@
         <v>29</v>
       </c>
       <c r="C114" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -1655,7 +1666,7 @@
         <v>18</v>
       </c>
       <c r="C115" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -1666,7 +1677,7 @@
         <v>42</v>
       </c>
       <c r="C116" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -1677,7 +1688,7 @@
         <v>23</v>
       </c>
       <c r="C117" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -1688,7 +1699,7 @@
         <v>45</v>
       </c>
       <c r="C118" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -1699,7 +1710,7 @@
         <v>62</v>
       </c>
       <c r="C119" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -1710,7 +1721,7 @@
         <v>26</v>
       </c>
       <c r="C120" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -1721,7 +1732,7 @@
         <v>33</v>
       </c>
       <c r="C121" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -1732,7 +1743,7 @@
         <v>58</v>
       </c>
       <c r="C122" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -1743,7 +1754,7 @@
         <v>44</v>
       </c>
       <c r="C123" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -1754,7 +1765,7 @@
         <v>33</v>
       </c>
       <c r="C124" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -1776,7 +1787,7 @@
         <v>32</v>
       </c>
       <c r="C126" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -1787,7 +1798,7 @@
         <v>51</v>
       </c>
       <c r="C127" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -1798,7 +1809,7 @@
         <v>45</v>
       </c>
       <c r="C128" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -1809,7 +1820,7 @@
         <v>65</v>
       </c>
       <c r="C129" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -1820,7 +1831,7 @@
         <v>18</v>
       </c>
       <c r="C130" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -1831,7 +1842,7 @@
         <v>36</v>
       </c>
       <c r="C131" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -1842,7 +1853,7 @@
         <v>62</v>
       </c>
       <c r="C132" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -1853,7 +1864,7 @@
         <v>18</v>
       </c>
       <c r="C133" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -1864,7 +1875,7 @@
         <v>23</v>
       </c>
       <c r="C134" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -1875,7 +1886,7 @@
         <v>19</v>
       </c>
       <c r="C135" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -1886,7 +1897,7 @@
         <v>39</v>
       </c>
       <c r="C136" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -1897,7 +1908,7 @@
         <v>18</v>
       </c>
       <c r="C137" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -1908,7 +1919,7 @@
         <v>22</v>
       </c>
       <c r="C138" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -1919,7 +1930,7 @@
         <v>28</v>
       </c>
       <c r="C139" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -1930,7 +1941,7 @@
         <v>27</v>
       </c>
       <c r="C140" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -1941,7 +1952,7 @@
         <v>42</v>
       </c>
       <c r="C141" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -1952,7 +1963,7 @@
         <v>26</v>
       </c>
       <c r="C142" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -1963,7 +1974,7 @@
         <v>46</v>
       </c>
       <c r="C143" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -1974,7 +1985,7 @@
         <v>46</v>
       </c>
       <c r="C144" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -1985,7 +1996,7 @@
         <v>58</v>
       </c>
       <c r="C145" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -1996,7 +2007,7 @@
         <v>22</v>
       </c>
       <c r="C146" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -2007,7 +2018,7 @@
         <v>43</v>
       </c>
       <c r="C147" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -2018,7 +2029,7 @@
         <v>54</v>
       </c>
       <c r="C148" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -2029,7 +2040,7 @@
         <v>37</v>
       </c>
       <c r="C149" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -2040,7 +2051,7 @@
         <v>37</v>
       </c>
       <c r="C150" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -2051,7 +2062,7 @@
         <v>61</v>
       </c>
       <c r="C151" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -2062,7 +2073,7 @@
         <v>18</v>
       </c>
       <c r="C152" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -2073,7 +2084,7 @@
         <v>37</v>
       </c>
       <c r="C153" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -2084,7 +2095,7 @@
         <v>40</v>
       </c>
       <c r="C154" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -2095,7 +2106,7 @@
         <v>56</v>
       </c>
       <c r="C155" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -2106,7 +2117,7 @@
         <v>63</v>
       </c>
       <c r="C156" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -2117,7 +2128,7 @@
         <v>18</v>
       </c>
       <c r="C157" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -2128,7 +2139,7 @@
         <v>17</v>
       </c>
       <c r="C158" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -2139,7 +2150,7 @@
         <v>59</v>
       </c>
       <c r="C159" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -2150,7 +2161,7 @@
         <v>60</v>
       </c>
       <c r="C160" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -2161,7 +2172,7 @@
         <v>62</v>
       </c>
       <c r="C161" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -2172,7 +2183,7 @@
         <v>28</v>
       </c>
       <c r="C162" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -2183,7 +2194,7 @@
         <v>62</v>
       </c>
       <c r="C163" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -2194,7 +2205,7 @@
         <v>55</v>
       </c>
       <c r="C164" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -2205,7 +2216,7 @@
         <v>49</v>
       </c>
       <c r="C165" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -2227,7 +2238,7 @@
         <v>54</v>
       </c>
       <c r="C167" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -2238,7 +2249,7 @@
         <v>19</v>
       </c>
       <c r="C168" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="169" spans="1:3">
@@ -2249,7 +2260,7 @@
         <v>46</v>
       </c>
       <c r="C169" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="170" spans="1:3">
@@ -2271,7 +2282,7 @@
         <v>23</v>
       </c>
       <c r="C171" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -2282,7 +2293,7 @@
         <v>16</v>
       </c>
       <c r="C172" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="173" spans="1:3">
@@ -2293,7 +2304,7 @@
         <v>54</v>
       </c>
       <c r="C173" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -2304,7 +2315,7 @@
         <v>64</v>
       </c>
       <c r="C174" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="175" spans="1:3">
@@ -2315,7 +2326,7 @@
         <v>39</v>
       </c>
       <c r="C175" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="176" spans="1:3">
@@ -2326,7 +2337,7 @@
         <v>38</v>
       </c>
       <c r="C176" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="177" spans="1:3">
@@ -2337,7 +2348,7 @@
         <v>23</v>
       </c>
       <c r="C177" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -2348,7 +2359,7 @@
         <v>20</v>
       </c>
       <c r="C178" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -2359,7 +2370,7 @@
         <v>38</v>
       </c>
       <c r="C179" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -2370,7 +2381,7 @@
         <v>31</v>
       </c>
       <c r="C180" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -2381,7 +2392,7 @@
         <v>65</v>
       </c>
       <c r="C181" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -2392,7 +2403,7 @@
         <v>50</v>
       </c>
       <c r="C182" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -2414,7 +2425,7 @@
         <v>27</v>
       </c>
       <c r="C184" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -2425,7 +2436,7 @@
         <v>49</v>
       </c>
       <c r="C185" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -2436,7 +2447,7 @@
         <v>16</v>
       </c>
       <c r="C186" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -2447,7 +2458,7 @@
         <v>20</v>
       </c>
       <c r="C187" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -2469,7 +2480,7 @@
         <v>41</v>
       </c>
       <c r="C189" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -2480,7 +2491,7 @@
         <v>45</v>
       </c>
       <c r="C190" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -2491,7 +2502,7 @@
         <v>48</v>
       </c>
       <c r="C191" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="192" spans="1:3">
@@ -2502,7 +2513,7 @@
         <v>41</v>
       </c>
       <c r="C192" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -2513,7 +2524,7 @@
         <v>31</v>
       </c>
       <c r="C193" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -2524,7 +2535,7 @@
         <v>28</v>
       </c>
       <c r="C194" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -2535,7 +2546,7 @@
         <v>31</v>
       </c>
       <c r="C195" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -2546,7 +2557,7 @@
         <v>57</v>
       </c>
       <c r="C196" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -2557,7 +2568,7 @@
         <v>44</v>
       </c>
       <c r="C197" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -2568,7 +2579,7 @@
         <v>28</v>
       </c>
       <c r="C198" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -2579,7 +2590,7 @@
         <v>55</v>
       </c>
       <c r="C199" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -2601,7 +2612,7 @@
         <v>47</v>
       </c>
       <c r="C201" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -2612,7 +2623,7 @@
         <v>59</v>
       </c>
       <c r="C202" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -2634,7 +2645,7 @@
         <v>23</v>
       </c>
       <c r="C204" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -2645,7 +2656,7 @@
         <v>40</v>
       </c>
       <c r="C205" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="206" spans="1:3">
@@ -2656,7 +2667,7 @@
         <v>47</v>
       </c>
       <c r="C206" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -2667,7 +2678,7 @@
         <v>48</v>
       </c>
       <c r="C207" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -2678,7 +2689,7 @@
         <v>61</v>
       </c>
       <c r="C208" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -2689,7 +2700,7 @@
         <v>41</v>
       </c>
       <c r="C209" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="210" spans="1:3">
@@ -2700,7 +2711,7 @@
         <v>56</v>
       </c>
       <c r="C210" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -2711,7 +2722,7 @@
         <v>63</v>
       </c>
       <c r="C211" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -2722,7 +2733,7 @@
         <v>50</v>
       </c>
       <c r="C212" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -2733,7 +2744,7 @@
         <v>28</v>
       </c>
       <c r="C213" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -2744,7 +2755,7 @@
         <v>32</v>
       </c>
       <c r="C214" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -2755,7 +2766,7 @@
         <v>52</v>
       </c>
       <c r="C215" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -2766,7 +2777,7 @@
         <v>32</v>
       </c>
       <c r="C216" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -2777,7 +2788,7 @@
         <v>20</v>
       </c>
       <c r="C217" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -2788,7 +2799,7 @@
         <v>58</v>
       </c>
       <c r="C218" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -2799,7 +2810,7 @@
         <v>62</v>
       </c>
       <c r="C219" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -2810,7 +2821,7 @@
         <v>45</v>
       </c>
       <c r="C220" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -2821,7 +2832,7 @@
         <v>37</v>
       </c>
       <c r="C221" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -2832,7 +2843,7 @@
         <v>27</v>
       </c>
       <c r="C222" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -2843,7 +2854,7 @@
         <v>50</v>
       </c>
       <c r="C223" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -2854,7 +2865,7 @@
         <v>21</v>
       </c>
       <c r="C224" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -2865,7 +2876,7 @@
         <v>20</v>
       </c>
       <c r="C225" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -2887,7 +2898,7 @@
         <v>19</v>
       </c>
       <c r="C227" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="228" spans="1:3">
@@ -2898,7 +2909,7 @@
         <v>64</v>
       </c>
       <c r="C228" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -2909,7 +2920,7 @@
         <v>20</v>
       </c>
       <c r="C229" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="230" spans="1:3">
@@ -2920,7 +2931,7 @@
         <v>26</v>
       </c>
       <c r="C230" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -2931,7 +2942,7 @@
         <v>56</v>
       </c>
       <c r="C231" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="232" spans="1:3">
@@ -2942,7 +2953,7 @@
         <v>58</v>
       </c>
       <c r="C232" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -2953,7 +2964,7 @@
         <v>42</v>
       </c>
       <c r="C233" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -2964,7 +2975,7 @@
         <v>59</v>
       </c>
       <c r="C234" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -2975,7 +2986,7 @@
         <v>17</v>
       </c>
       <c r="C235" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -2986,7 +2997,7 @@
         <v>29</v>
       </c>
       <c r="C236" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -2997,7 +3008,7 @@
         <v>37</v>
       </c>
       <c r="C237" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -3008,7 +3019,7 @@
         <v>18</v>
       </c>
       <c r="C238" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="239" spans="1:3">
@@ -3019,7 +3030,7 @@
         <v>58</v>
       </c>
       <c r="C239" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -3041,7 +3052,7 @@
         <v>53</v>
       </c>
       <c r="C241" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -3052,7 +3063,7 @@
         <v>31</v>
       </c>
       <c r="C242" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -3063,7 +3074,7 @@
         <v>28</v>
       </c>
       <c r="C243" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -3074,7 +3085,7 @@
         <v>55</v>
       </c>
       <c r="C244" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="245" spans="1:3">
@@ -3085,7 +3096,7 @@
         <v>52</v>
       </c>
       <c r="C245" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="246" spans="1:3">
@@ -3096,7 +3107,7 @@
         <v>65</v>
       </c>
       <c r="C246" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="247" spans="1:3">
@@ -3107,7 +3118,7 @@
         <v>55</v>
       </c>
       <c r="C247" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="248" spans="1:3">
@@ -3118,7 +3129,7 @@
         <v>23</v>
       </c>
       <c r="C248" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="249" spans="1:3">
@@ -3129,7 +3140,7 @@
         <v>22</v>
       </c>
       <c r="C249" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="250" spans="1:3">
@@ -3140,7 +3151,7 @@
         <v>34</v>
       </c>
       <c r="C250" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="251" spans="1:3">
@@ -3151,7 +3162,7 @@
         <v>52</v>
       </c>
       <c r="C251" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="252" spans="1:3">
@@ -3162,7 +3173,7 @@
         <v>60</v>
       </c>
       <c r="C252" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="253" spans="1:3">
@@ -3173,7 +3184,7 @@
         <v>42</v>
       </c>
       <c r="C253" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="254" spans="1:3">
@@ -3184,7 +3195,7 @@
         <v>20</v>
       </c>
       <c r="C254" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="255" spans="1:3">
@@ -3195,7 +3206,7 @@
         <v>45</v>
       </c>
       <c r="C255" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="256" spans="1:3">
@@ -3206,7 +3217,7 @@
         <v>51</v>
       </c>
       <c r="C256" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="257" spans="1:3">
@@ -3217,7 +3228,7 @@
         <v>19</v>
       </c>
       <c r="C257" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -3228,7 +3239,7 @@
         <v>34</v>
       </c>
       <c r="C258" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="259" spans="1:3">
@@ -3239,7 +3250,7 @@
         <v>65</v>
       </c>
       <c r="C259" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="260" spans="1:3">
@@ -3250,7 +3261,7 @@
         <v>28</v>
       </c>
       <c r="C260" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="261" spans="1:3">
@@ -3261,7 +3272,7 @@
         <v>44</v>
       </c>
       <c r="C261" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="262" spans="1:3">
@@ -3272,7 +3283,7 @@
         <v>19</v>
       </c>
       <c r="C262" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="263" spans="1:3">
@@ -3294,7 +3305,7 @@
         <v>18</v>
       </c>
       <c r="C264" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="265" spans="1:3">
@@ -3305,7 +3316,7 @@
         <v>52</v>
       </c>
       <c r="C265" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="266" spans="1:3">
@@ -3316,7 +3327,7 @@
         <v>55</v>
       </c>
       <c r="C266" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="267" spans="1:3">
@@ -3327,7 +3338,7 @@
         <v>55</v>
       </c>
       <c r="C267" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="268" spans="1:3">
@@ -3338,7 +3349,7 @@
         <v>20</v>
       </c>
       <c r="C268" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="269" spans="1:3">
@@ -3349,7 +3360,7 @@
         <v>54</v>
       </c>
       <c r="C269" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="270" spans="1:3">
@@ -3360,7 +3371,7 @@
         <v>55</v>
       </c>
       <c r="C270" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="271" spans="1:3">
@@ -3371,7 +3382,7 @@
         <v>24</v>
       </c>
       <c r="C271" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="272" spans="1:3">
@@ -3382,7 +3393,7 @@
         <v>62</v>
       </c>
       <c r="C272" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="273" spans="1:3">
@@ -3404,7 +3415,7 @@
         <v>53</v>
       </c>
       <c r="C274" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="275" spans="1:3">
@@ -3415,7 +3426,7 @@
         <v>32</v>
       </c>
       <c r="C275" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="276" spans="1:3">
@@ -3426,7 +3437,7 @@
         <v>21</v>
       </c>
       <c r="C276" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="277" spans="1:3">
@@ -3437,7 +3448,7 @@
         <v>25</v>
       </c>
       <c r="C277" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="278" spans="1:3">
@@ -3448,7 +3459,7 @@
         <v>47</v>
       </c>
       <c r="C278" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="279" spans="1:3">
@@ -3459,7 +3470,7 @@
         <v>42</v>
       </c>
       <c r="C279" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="280" spans="1:3">
@@ -3470,7 +3481,7 @@
         <v>55</v>
       </c>
       <c r="C280" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="281" spans="1:3">
@@ -3481,7 +3492,7 @@
         <v>21</v>
       </c>
       <c r="C281" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="282" spans="1:3">
@@ -3492,7 +3503,7 @@
         <v>32</v>
       </c>
       <c r="C282" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="283" spans="1:3">
@@ -3514,7 +3525,7 @@
         <v>40</v>
       </c>
       <c r="C284" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="285" spans="1:3">
@@ -3525,7 +3536,7 @@
         <v>35</v>
       </c>
       <c r="C285" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="286" spans="1:3">
@@ -3536,7 +3547,7 @@
         <v>52</v>
       </c>
       <c r="C286" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="287" spans="1:3">
@@ -3547,7 +3558,7 @@
         <v>57</v>
       </c>
       <c r="C287" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="288" spans="1:3">
@@ -3558,7 +3569,7 @@
         <v>16</v>
       </c>
       <c r="C288" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="289" spans="1:3">
@@ -3569,7 +3580,7 @@
         <v>41</v>
       </c>
       <c r="C289" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="290" spans="1:3">
@@ -3580,7 +3591,7 @@
         <v>38</v>
       </c>
       <c r="C290" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="291" spans="1:3">
@@ -3591,7 +3602,7 @@
         <v>56</v>
       </c>
       <c r="C291" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="292" spans="1:3">
@@ -3602,7 +3613,7 @@
         <v>36</v>
       </c>
       <c r="C292" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="293" spans="1:3">
@@ -3613,7 +3624,7 @@
         <v>39</v>
       </c>
       <c r="C293" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="294" spans="1:3">
@@ -3624,7 +3635,7 @@
         <v>56</v>
       </c>
       <c r="C294" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="295" spans="1:3">
@@ -3635,7 +3646,7 @@
         <v>37</v>
       </c>
       <c r="C295" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="296" spans="1:3">
@@ -3646,7 +3657,7 @@
         <v>33</v>
       </c>
       <c r="C296" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="297" spans="1:3">
@@ -3657,7 +3668,7 @@
         <v>16</v>
       </c>
       <c r="C297" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="298" spans="1:3">
@@ -3679,7 +3690,7 @@
         <v>41</v>
       </c>
       <c r="C299" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="300" spans="1:3">
@@ -3690,7 +3701,7 @@
         <v>45</v>
       </c>
       <c r="C300" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="301" spans="1:3">
@@ -3701,7 +3712,7 @@
         <v>51</v>
       </c>
       <c r="C301" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="302" spans="1:3">
@@ -3712,7 +3723,7 @@
         <v>19</v>
       </c>
       <c r="C302" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="303" spans="1:3">
@@ -3723,7 +3734,7 @@
         <v>47</v>
       </c>
       <c r="C303" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="304" spans="1:3">
@@ -3734,7 +3745,7 @@
         <v>27</v>
       </c>
       <c r="C304" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="305" spans="1:3">
@@ -3745,7 +3756,7 @@
         <v>59</v>
       </c>
       <c r="C305" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="306" spans="1:3">
@@ -3756,7 +3767,7 @@
         <v>17</v>
       </c>
       <c r="C306" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="307" spans="1:3">
@@ -3767,7 +3778,7 @@
         <v>45</v>
       </c>
       <c r="C307" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="308" spans="1:3">
@@ -3778,7 +3789,7 @@
         <v>30</v>
       </c>
       <c r="C308" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="309" spans="1:3">
@@ -3789,7 +3800,7 @@
         <v>26</v>
       </c>
       <c r="C309" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="310" spans="1:3">
@@ -3800,7 +3811,7 @@
         <v>20</v>
       </c>
       <c r="C310" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="311" spans="1:3">
@@ -3811,7 +3822,7 @@
         <v>58</v>
       </c>
       <c r="C311" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="312" spans="1:3">
@@ -3822,7 +3833,7 @@
         <v>30</v>
       </c>
       <c r="C312" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="313" spans="1:3">
@@ -3833,7 +3844,7 @@
         <v>54</v>
       </c>
       <c r="C313" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="314" spans="1:3">
@@ -3844,7 +3855,7 @@
         <v>36</v>
       </c>
       <c r="C314" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="315" spans="1:3">
@@ -3855,7 +3866,7 @@
         <v>64</v>
       </c>
       <c r="C315" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="316" spans="1:3">
@@ -3877,7 +3888,7 @@
         <v>58</v>
       </c>
       <c r="C317" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="318" spans="1:3">
@@ -3888,7 +3899,7 @@
         <v>63</v>
       </c>
       <c r="C318" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="319" spans="1:3">
@@ -3899,7 +3910,7 @@
         <v>22</v>
       </c>
       <c r="C319" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="320" spans="1:3">
@@ -3910,7 +3921,7 @@
         <v>52</v>
       </c>
       <c r="C320" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="321" spans="1:3">
@@ -3921,7 +3932,7 @@
         <v>19</v>
       </c>
       <c r="C321" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="322" spans="1:3">
@@ -3932,7 +3943,7 @@
         <v>42</v>
       </c>
       <c r="C322" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="323" spans="1:3">
@@ -3943,7 +3954,7 @@
         <v>20</v>
       </c>
       <c r="C323" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="324" spans="1:3">
@@ -3954,7 +3965,7 @@
         <v>63</v>
       </c>
       <c r="C324" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="325" spans="1:3">
@@ -3976,7 +3987,7 @@
         <v>34</v>
       </c>
       <c r="C326" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="327" spans="1:3">
@@ -3998,7 +4009,7 @@
         <v>64</v>
       </c>
       <c r="C328" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="329" spans="1:3">
@@ -4009,7 +4020,7 @@
         <v>63</v>
       </c>
       <c r="C329" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="330" spans="1:3">
@@ -4020,7 +4031,7 @@
         <v>53</v>
       </c>
       <c r="C330" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="331" spans="1:3">
@@ -4031,7 +4042,7 @@
         <v>21</v>
       </c>
       <c r="C331" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="332" spans="1:3">
@@ -4042,7 +4053,7 @@
         <v>62</v>
       </c>
       <c r="C332" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="333" spans="1:3">
@@ -4053,7 +4064,7 @@
         <v>36</v>
       </c>
       <c r="C333" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="334" spans="1:3">
@@ -4064,7 +4075,7 @@
         <v>53</v>
       </c>
       <c r="C334" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="335" spans="1:3">
@@ -4075,7 +4086,7 @@
         <v>64</v>
       </c>
       <c r="C335" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="336" spans="1:3">
@@ -4086,7 +4097,7 @@
         <v>38</v>
       </c>
       <c r="C336" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="337" spans="1:3">
@@ -4097,7 +4108,7 @@
         <v>22</v>
       </c>
       <c r="C337" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="338" spans="1:3">
@@ -4108,7 +4119,7 @@
         <v>21</v>
       </c>
       <c r="C338" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="339" spans="1:3">
@@ -4119,7 +4130,7 @@
         <v>52</v>
       </c>
       <c r="C339" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="340" spans="1:3">
@@ -4130,7 +4141,7 @@
         <v>30</v>
       </c>
       <c r="C340" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="341" spans="1:3">
@@ -4141,7 +4152,7 @@
         <v>37</v>
       </c>
       <c r="C341" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="342" spans="1:3">
@@ -4152,7 +4163,7 @@
         <v>55</v>
       </c>
       <c r="C342" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343" spans="1:3">
@@ -4163,7 +4174,7 @@
         <v>23</v>
       </c>
       <c r="C343" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="344" spans="1:3">
@@ -4174,7 +4185,7 @@
         <v>30</v>
       </c>
       <c r="C344" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="345" spans="1:3">
@@ -4185,7 +4196,7 @@
         <v>60</v>
       </c>
       <c r="C345" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="346" spans="1:3">
@@ -4196,7 +4207,7 @@
         <v>48</v>
       </c>
       <c r="C346" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="347" spans="1:3">
@@ -4207,7 +4218,7 @@
         <v>24</v>
       </c>
       <c r="C347" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="348" spans="1:3">
@@ -4218,7 +4229,7 @@
         <v>22</v>
       </c>
       <c r="C348" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="349" spans="1:3">
@@ -4229,7 +4240,7 @@
         <v>39</v>
       </c>
       <c r="C349" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="350" spans="1:3">
@@ -4240,7 +4251,7 @@
         <v>57</v>
       </c>
       <c r="C350" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="351" spans="1:3">
@@ -4251,7 +4262,7 @@
         <v>58</v>
       </c>
       <c r="C351" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="352" spans="1:3">
@@ -4262,7 +4273,7 @@
         <v>26</v>
       </c>
       <c r="C352" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="353" spans="1:3">
@@ -4273,7 +4284,7 @@
         <v>34</v>
       </c>
       <c r="C353" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="354" spans="1:3">
@@ -4284,7 +4295,7 @@
         <v>57</v>
       </c>
       <c r="C354" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="355" spans="1:3">
@@ -4295,7 +4306,7 @@
         <v>57</v>
       </c>
       <c r="C355" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="356" spans="1:3">
@@ -4306,7 +4317,7 @@
         <v>16</v>
       </c>
       <c r="C356" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="357" spans="1:3">
@@ -4317,7 +4328,7 @@
         <v>60</v>
       </c>
       <c r="C357" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="358" spans="1:3">
@@ -4328,7 +4339,7 @@
         <v>56</v>
       </c>
       <c r="C358" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="359" spans="1:3">
@@ -4339,7 +4350,7 @@
         <v>32</v>
       </c>
       <c r="C359" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="360" spans="1:3">
@@ -4350,7 +4361,7 @@
         <v>38</v>
       </c>
       <c r="C360" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="361" spans="1:3">
@@ -4361,7 +4372,7 @@
         <v>25</v>
       </c>
       <c r="C361" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="362" spans="1:3">
@@ -4372,7 +4383,7 @@
         <v>36</v>
       </c>
       <c r="C362" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="363" spans="1:3">
@@ -4383,7 +4394,7 @@
         <v>22</v>
       </c>
       <c r="C363" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="364" spans="1:3">
@@ -4394,7 +4405,7 @@
         <v>47</v>
       </c>
       <c r="C364" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="365" spans="1:3">
@@ -4405,7 +4416,7 @@
         <v>63</v>
       </c>
       <c r="C365" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="366" spans="1:3">
@@ -4427,7 +4438,7 @@
         <v>45</v>
       </c>
       <c r="C367" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="368" spans="1:3">
@@ -4438,7 +4449,7 @@
         <v>19</v>
       </c>
       <c r="C368" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="369" spans="1:3">
@@ -4449,7 +4460,7 @@
         <v>26</v>
       </c>
       <c r="C369" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="370" spans="1:3">
@@ -4460,7 +4471,7 @@
         <v>58</v>
       </c>
       <c r="C370" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="371" spans="1:3">
@@ -4471,7 +4482,7 @@
         <v>21</v>
       </c>
       <c r="C371" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="372" spans="1:3">
@@ -4482,7 +4493,7 @@
         <v>57</v>
       </c>
       <c r="C372" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="373" spans="1:3">
@@ -4493,7 +4504,7 @@
         <v>29</v>
       </c>
       <c r="C373" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="374" spans="1:3">
@@ -4504,7 +4515,7 @@
         <v>33</v>
       </c>
       <c r="C374" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="375" spans="1:3">
@@ -4526,7 +4537,7 @@
         <v>47</v>
       </c>
       <c r="C376" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="377" spans="1:3">
@@ -4537,7 +4548,7 @@
         <v>56</v>
       </c>
       <c r="C377" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="378" spans="1:3">
@@ -4548,7 +4559,7 @@
         <v>28</v>
       </c>
       <c r="C378" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="379" spans="1:3">
@@ -4559,7 +4570,7 @@
         <v>40</v>
       </c>
       <c r="C379" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="380" spans="1:3">
@@ -4570,7 +4581,7 @@
         <v>61</v>
       </c>
       <c r="C380" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="381" spans="1:3">
@@ -4581,7 +4592,7 @@
         <v>62</v>
       </c>
       <c r="C381" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="382" spans="1:3">
@@ -4592,7 +4603,7 @@
         <v>32</v>
       </c>
       <c r="C382" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="383" spans="1:3">
@@ -4603,7 +4614,7 @@
         <v>65</v>
       </c>
       <c r="C383" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="384" spans="1:3">
@@ -4614,7 +4625,7 @@
         <v>22</v>
       </c>
       <c r="C384" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="385" spans="1:3">
@@ -4625,7 +4636,7 @@
         <v>44</v>
       </c>
       <c r="C385" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="386" spans="1:3">
@@ -4636,7 +4647,7 @@
         <v>50</v>
       </c>
       <c r="C386" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="387" spans="1:3">
@@ -4647,7 +4658,7 @@
         <v>53</v>
       </c>
       <c r="C387" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="388" spans="1:3">
@@ -4658,7 +4669,7 @@
         <v>50</v>
       </c>
       <c r="C388" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="389" spans="1:3">
@@ -4669,7 +4680,7 @@
         <v>44</v>
       </c>
       <c r="C389" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="390" spans="1:3">
@@ -4680,7 +4691,7 @@
         <v>27</v>
       </c>
       <c r="C390" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="391" spans="1:3">
@@ -4691,7 +4702,7 @@
         <v>29</v>
       </c>
       <c r="C391" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="392" spans="1:3">
@@ -4702,7 +4713,7 @@
         <v>47</v>
       </c>
       <c r="C392" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="393" spans="1:3">
@@ -4713,7 +4724,7 @@
         <v>38</v>
       </c>
       <c r="C393" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="394" spans="1:3">
@@ -4724,7 +4735,7 @@
         <v>41</v>
       </c>
       <c r="C394" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="395" spans="1:3">
@@ -4735,7 +4746,7 @@
         <v>36</v>
       </c>
       <c r="C395" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="396" spans="1:3">
@@ -4746,7 +4757,7 @@
         <v>65</v>
       </c>
       <c r="C396" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="397" spans="1:3">
@@ -4757,7 +4768,7 @@
         <v>51</v>
       </c>
       <c r="C397" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="398" spans="1:3">
@@ -4768,7 +4779,7 @@
         <v>50</v>
       </c>
       <c r="C398" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="399" spans="1:3">
@@ -4779,7 +4790,7 @@
         <v>62</v>
       </c>
       <c r="C399" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="400" spans="1:3">
@@ -4801,7 +4812,7 @@
         <v>28</v>
       </c>
       <c r="C401" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="402" spans="1:3">
@@ -4812,7 +4823,7 @@
         <v>53</v>
       </c>
       <c r="C402" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="403" spans="1:3">
@@ -4823,7 +4834,7 @@
         <v>19</v>
       </c>
       <c r="C403" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="404" spans="1:3">
@@ -4834,7 +4845,7 @@
         <v>49</v>
       </c>
       <c r="C404" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="405" spans="1:3">
@@ -4845,7 +4856,7 @@
         <v>31</v>
       </c>
       <c r="C405" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="406" spans="1:3">
@@ -4856,7 +4867,7 @@
         <v>51</v>
       </c>
       <c r="C406" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="407" spans="1:3">
@@ -4867,7 +4878,7 @@
         <v>32</v>
       </c>
       <c r="C407" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="408" spans="1:3">
@@ -4878,7 +4889,7 @@
         <v>46</v>
       </c>
       <c r="C408" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="409" spans="1:3">
@@ -4889,7 +4900,7 @@
         <v>16</v>
       </c>
       <c r="C409" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="410" spans="1:3">
@@ -4900,7 +4911,7 @@
         <v>47</v>
       </c>
       <c r="C410" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="411" spans="1:3">
@@ -4911,7 +4922,7 @@
         <v>44</v>
       </c>
       <c r="C411" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="412" spans="1:3">
@@ -4922,7 +4933,7 @@
         <v>57</v>
       </c>
       <c r="C412" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="413" spans="1:3">
@@ -4933,7 +4944,7 @@
         <v>65</v>
       </c>
       <c r="C413" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="414" spans="1:3">
@@ -4944,7 +4955,7 @@
         <v>23</v>
       </c>
       <c r="C414" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="415" spans="1:3">
@@ -4966,7 +4977,7 @@
         <v>47</v>
       </c>
       <c r="C416" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="417" spans="1:3">
@@ -4977,7 +4988,7 @@
         <v>52</v>
       </c>
       <c r="C417" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="418" spans="1:3">
@@ -4988,7 +4999,7 @@
         <v>27</v>
       </c>
       <c r="C418" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="419" spans="1:3">
@@ -4999,7 +5010,7 @@
         <v>39</v>
       </c>
       <c r="C419" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="420" spans="1:3">
@@ -5010,7 +5021,7 @@
         <v>61</v>
       </c>
       <c r="C420" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="421" spans="1:3">
@@ -5021,7 +5032,7 @@
         <v>60</v>
       </c>
       <c r="C421" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="422" spans="1:3">
@@ -5032,7 +5043,7 @@
         <v>59</v>
       </c>
       <c r="C422" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="423" spans="1:3">
@@ -5043,7 +5054,7 @@
         <v>42</v>
       </c>
       <c r="C423" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="424" spans="1:3">
@@ -5054,7 +5065,7 @@
         <v>40</v>
       </c>
       <c r="C424" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="425" spans="1:3">
@@ -5065,7 +5076,7 @@
         <v>59</v>
       </c>
       <c r="C425" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="426" spans="1:3">
@@ -5076,7 +5087,7 @@
         <v>63</v>
       </c>
       <c r="C426" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="427" spans="1:3">
@@ -5087,7 +5098,7 @@
         <v>59</v>
       </c>
       <c r="C427" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="428" spans="1:3">
@@ -5109,7 +5120,7 @@
         <v>41</v>
       </c>
       <c r="C429" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="430" spans="1:3">
@@ -5120,7 +5131,7 @@
         <v>19</v>
       </c>
       <c r="C430" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="431" spans="1:3">
@@ -5131,7 +5142,7 @@
         <v>60</v>
       </c>
       <c r="C431" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="432" spans="1:3">
@@ -5142,7 +5153,7 @@
         <v>54</v>
       </c>
       <c r="C432" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="433" spans="1:3">
@@ -5153,7 +5164,7 @@
         <v>31</v>
       </c>
       <c r="C433" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="434" spans="1:3">
@@ -5164,7 +5175,7 @@
         <v>53</v>
       </c>
       <c r="C434" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="435" spans="1:3">
@@ -5175,7 +5186,7 @@
         <v>22</v>
       </c>
       <c r="C435" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="436" spans="1:3">
@@ -5186,7 +5197,7 @@
         <v>47</v>
       </c>
       <c r="C436" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="437" spans="1:3">
@@ -5197,7 +5208,7 @@
         <v>60</v>
       </c>
       <c r="C437" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="438" spans="1:3">
@@ -5208,7 +5219,7 @@
         <v>55</v>
       </c>
       <c r="C438" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="439" spans="1:3">
@@ -5219,7 +5230,7 @@
         <v>19</v>
       </c>
       <c r="C439" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="440" spans="1:3">
@@ -5230,7 +5241,7 @@
         <v>22</v>
       </c>
       <c r="C440" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="441" spans="1:3">
@@ -5252,7 +5263,7 @@
         <v>30</v>
       </c>
       <c r="C442" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="443" spans="1:3">
@@ -5263,7 +5274,7 @@
         <v>30</v>
       </c>
       <c r="C443" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="444" spans="1:3">
@@ -5274,7 +5285,7 @@
         <v>52</v>
       </c>
       <c r="C444" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="445" spans="1:3">
@@ -5307,7 +5318,7 @@
         <v>16</v>
       </c>
       <c r="C447" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="448" spans="1:3">
@@ -5318,7 +5329,7 @@
         <v>20</v>
       </c>
       <c r="C448" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="449" spans="1:3">
@@ -5329,7 +5340,7 @@
         <v>32</v>
       </c>
       <c r="C449" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="450" spans="1:3">
@@ -5340,7 +5351,7 @@
         <v>22</v>
       </c>
       <c r="C450" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="451" spans="1:3">
@@ -5351,7 +5362,7 @@
         <v>27</v>
       </c>
       <c r="C451" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="452" spans="1:3">
@@ -5362,7 +5373,7 @@
         <v>28</v>
       </c>
       <c r="C452" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="453" spans="1:3">
@@ -5373,7 +5384,7 @@
         <v>51</v>
       </c>
       <c r="C453" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="454" spans="1:3">
@@ -5384,7 +5395,7 @@
         <v>54</v>
       </c>
       <c r="C454" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="455" spans="1:3">
@@ -5395,7 +5406,7 @@
         <v>59</v>
       </c>
       <c r="C455" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="456" spans="1:3">
@@ -5406,7 +5417,7 @@
         <v>30</v>
       </c>
       <c r="C456" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="457" spans="1:3">
@@ -5417,7 +5428,7 @@
         <v>55</v>
       </c>
       <c r="C457" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="458" spans="1:3">
@@ -5428,7 +5439,7 @@
         <v>47</v>
       </c>
       <c r="C458" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="459" spans="1:3">
@@ -5450,7 +5461,7 @@
         <v>48</v>
       </c>
       <c r="C460" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="461" spans="1:3">
@@ -5461,7 +5472,7 @@
         <v>51</v>
       </c>
       <c r="C461" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="462" spans="1:3">
@@ -5472,7 +5483,7 @@
         <v>61</v>
       </c>
       <c r="C462" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="463" spans="1:3">
@@ -5483,7 +5494,7 @@
         <v>45</v>
       </c>
       <c r="C463" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="464" spans="1:3">
@@ -5494,7 +5505,7 @@
         <v>57</v>
       </c>
       <c r="C464" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="465" spans="1:3">
@@ -5505,7 +5516,7 @@
         <v>36</v>
       </c>
       <c r="C465" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="466" spans="1:3">
@@ -5516,7 +5527,7 @@
         <v>42</v>
       </c>
       <c r="C466" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="467" spans="1:3">
@@ -5527,7 +5538,7 @@
         <v>18</v>
       </c>
       <c r="C467" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="468" spans="1:3">
@@ -5538,7 +5549,7 @@
         <v>65</v>
       </c>
       <c r="C468" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="469" spans="1:3">
@@ -5549,7 +5560,7 @@
         <v>58</v>
       </c>
       <c r="C469" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="470" spans="1:3">
@@ -5560,7 +5571,7 @@
         <v>49</v>
       </c>
       <c r="C470" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="471" spans="1:3">
@@ -5571,7 +5582,7 @@
         <v>44</v>
       </c>
       <c r="C471" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="472" spans="1:3">
@@ -5582,7 +5593,7 @@
         <v>25</v>
       </c>
       <c r="C472" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="473" spans="1:3">
@@ -5593,7 +5604,7 @@
         <v>50</v>
       </c>
       <c r="C473" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="474" spans="1:3">
@@ -5604,7 +5615,7 @@
         <v>37</v>
       </c>
       <c r="C474" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="475" spans="1:3">
@@ -5615,7 +5626,7 @@
         <v>63</v>
       </c>
       <c r="C475" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="476" spans="1:3">
@@ -5626,7 +5637,7 @@
         <v>29</v>
       </c>
       <c r="C476" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="477" spans="1:3">
@@ -5637,7 +5648,7 @@
         <v>46</v>
       </c>
       <c r="C477" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="478" spans="1:3">
@@ -5659,7 +5670,7 @@
         <v>47</v>
       </c>
       <c r="C479" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="480" spans="1:3">
@@ -5670,7 +5681,7 @@
         <v>31</v>
       </c>
       <c r="C480" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="481" spans="1:3">
@@ -5681,7 +5692,7 @@
         <v>33</v>
       </c>
       <c r="C481" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="482" spans="1:3">
@@ -5692,7 +5703,7 @@
         <v>55</v>
       </c>
       <c r="C482" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="483" spans="1:3">
@@ -5703,7 +5714,7 @@
         <v>45</v>
       </c>
       <c r="C483" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="484" spans="1:3">
@@ -5714,7 +5725,7 @@
         <v>59</v>
       </c>
       <c r="C484" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="485" spans="1:3">
@@ -5736,7 +5747,7 @@
         <v>37</v>
       </c>
       <c r="C486" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="487" spans="1:3">
@@ -5747,7 +5758,7 @@
         <v>50</v>
       </c>
       <c r="C487" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="488" spans="1:3">
@@ -5780,7 +5791,7 @@
         <v>19</v>
       </c>
       <c r="C490" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="491" spans="1:3">
@@ -5791,7 +5802,7 @@
         <v>34</v>
       </c>
       <c r="C491" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="492" spans="1:3">
@@ -5802,7 +5813,7 @@
         <v>26</v>
       </c>
       <c r="C492" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="493" spans="1:3">
@@ -5813,7 +5824,7 @@
         <v>48</v>
       </c>
       <c r="C493" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="494" spans="1:3">
@@ -5824,7 +5835,7 @@
         <v>54</v>
       </c>
       <c r="C494" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="495" spans="1:3">
@@ -5835,7 +5846,7 @@
         <v>46</v>
       </c>
       <c r="C495" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="496" spans="1:3">
@@ -5846,7 +5857,7 @@
         <v>33</v>
       </c>
       <c r="C496" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="497" spans="1:3">
@@ -5857,7 +5868,7 @@
         <v>38</v>
       </c>
       <c r="C497" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="498" spans="1:3">
@@ -5868,7 +5879,7 @@
         <v>22</v>
       </c>
       <c r="C498" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="499" spans="1:3">
@@ -5879,7 +5890,7 @@
         <v>23</v>
       </c>
       <c r="C499" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="500" spans="1:3">
@@ -5901,7 +5912,7 @@
         <v>62</v>
       </c>
       <c r="C501" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="502" spans="1:3">
@@ -5912,7 +5923,7 @@
         <v>40</v>
       </c>
       <c r="C502" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="503" spans="1:3">
@@ -5923,7 +5934,7 @@
         <v>26</v>
       </c>
       <c r="C503" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="504" spans="1:3">
@@ -5934,7 +5945,7 @@
         <v>48</v>
       </c>
       <c r="C504" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="505" spans="1:3">
@@ -5945,7 +5956,7 @@
         <v>22</v>
       </c>
       <c r="C505" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="506" spans="1:3">
@@ -5956,7 +5967,7 @@
         <v>63</v>
       </c>
       <c r="C506" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="507" spans="1:3">
@@ -5967,7 +5978,7 @@
         <v>26</v>
       </c>
       <c r="C507" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="508" spans="1:3">
@@ -5978,7 +5989,7 @@
         <v>54</v>
       </c>
       <c r="C508" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="509" spans="1:3">
@@ -5989,7 +6000,7 @@
         <v>33</v>
       </c>
       <c r="C509" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="510" spans="1:3">
@@ -6000,7 +6011,7 @@
         <v>64</v>
       </c>
       <c r="C510" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="511" spans="1:3">
@@ -6022,7 +6033,7 @@
         <v>57</v>
       </c>
       <c r="C512" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="513" spans="1:3">
@@ -6044,7 +6055,7 @@
         <v>16</v>
       </c>
       <c r="C514" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="515" spans="1:3">
@@ -6055,7 +6066,7 @@
         <v>60</v>
       </c>
       <c r="C515" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="516" spans="1:3">
@@ -6066,7 +6077,7 @@
         <v>45</v>
       </c>
       <c r="C516" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="517" spans="1:3">
@@ -6077,7 +6088,7 @@
         <v>60</v>
       </c>
       <c r="C517" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="518" spans="1:3">
@@ -6088,7 +6099,7 @@
         <v>30</v>
       </c>
       <c r="C518" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="519" spans="1:3">
@@ -6099,7 +6110,7 @@
         <v>55</v>
       </c>
       <c r="C519" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="520" spans="1:3">
@@ -6110,7 +6121,7 @@
         <v>63</v>
       </c>
       <c r="C520" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="521" spans="1:3">
@@ -6121,7 +6132,7 @@
         <v>63</v>
       </c>
       <c r="C521" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="522" spans="1:3">
@@ -6132,7 +6143,7 @@
         <v>57</v>
       </c>
       <c r="C522" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="523" spans="1:3">
@@ -6143,7 +6154,7 @@
         <v>17</v>
       </c>
       <c r="C523" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="524" spans="1:3">
@@ -6154,7 +6165,7 @@
         <v>62</v>
       </c>
       <c r="C524" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="525" spans="1:3">
@@ -6165,7 +6176,7 @@
         <v>47</v>
       </c>
       <c r="C525" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="526" spans="1:3">
@@ -6176,7 +6187,7 @@
         <v>60</v>
       </c>
       <c r="C526" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="527" spans="1:3">
@@ -6187,7 +6198,7 @@
         <v>29</v>
       </c>
       <c r="C527" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="528" spans="1:3">
@@ -6198,7 +6209,7 @@
         <v>39</v>
       </c>
       <c r="C528" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="529" spans="1:3">
@@ -6209,7 +6220,7 @@
         <v>55</v>
       </c>
       <c r="C529" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="530" spans="1:3">
@@ -6220,7 +6231,7 @@
         <v>34</v>
       </c>
       <c r="C530" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="531" spans="1:3">
@@ -6242,7 +6253,7 @@
         <v>56</v>
       </c>
       <c r="C532" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="533" spans="1:3">
@@ -6253,7 +6264,7 @@
         <v>23</v>
       </c>
       <c r="C533" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="534" spans="1:3">
@@ -6264,7 +6275,7 @@
         <v>55</v>
       </c>
       <c r="C534" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="535" spans="1:3">
@@ -6286,7 +6297,7 @@
         <v>47</v>
       </c>
       <c r="C536" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="537" spans="1:3">
@@ -6297,7 +6308,7 @@
         <v>21</v>
       </c>
       <c r="C537" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="538" spans="1:3">
@@ -6308,7 +6319,7 @@
         <v>18</v>
       </c>
       <c r="C538" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="539" spans="1:3">
@@ -6319,7 +6330,7 @@
         <v>54</v>
       </c>
       <c r="C539" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="540" spans="1:3">
@@ -6330,7 +6341,7 @@
         <v>29</v>
       </c>
       <c r="C540" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="541" spans="1:3">
@@ -6341,7 +6352,7 @@
         <v>54</v>
       </c>
       <c r="C541" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="542" spans="1:3">
@@ -6352,7 +6363,7 @@
         <v>20</v>
       </c>
       <c r="C542" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="543" spans="1:3">
@@ -6363,7 +6374,7 @@
         <v>57</v>
       </c>
       <c r="C543" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="544" spans="1:3">
@@ -6385,7 +6396,7 @@
         <v>51</v>
       </c>
       <c r="C545" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="546" spans="1:3">
@@ -6396,7 +6407,7 @@
         <v>27</v>
       </c>
       <c r="C546" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="547" spans="1:3">
@@ -6418,7 +6429,7 @@
         <v>49</v>
       </c>
       <c r="C548" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="549" spans="1:3">
@@ -6429,7 +6440,7 @@
         <v>57</v>
       </c>
       <c r="C549" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="550" spans="1:3">
@@ -6451,7 +6462,7 @@
         <v>58</v>
       </c>
       <c r="C551" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="552" spans="1:3">
@@ -6462,7 +6473,7 @@
         <v>38</v>
       </c>
       <c r="C552" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="553" spans="1:3">
@@ -6473,7 +6484,7 @@
         <v>45</v>
       </c>
       <c r="C553" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="554" spans="1:3">
@@ -6484,7 +6495,7 @@
         <v>36</v>
       </c>
       <c r="C554" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="555" spans="1:3">
@@ -6506,7 +6517,7 @@
         <v>44</v>
       </c>
       <c r="C556" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="557" spans="1:3">
@@ -6517,7 +6528,7 @@
         <v>41</v>
       </c>
       <c r="C557" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="558" spans="1:3">
@@ -6528,7 +6539,7 @@
         <v>49</v>
       </c>
       <c r="C558" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="559" spans="1:3">
@@ -6539,7 +6550,7 @@
         <v>21</v>
       </c>
       <c r="C559" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="560" spans="1:3">
@@ -6550,7 +6561,7 @@
         <v>28</v>
       </c>
       <c r="C560" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="561" spans="1:3">
@@ -6561,7 +6572,7 @@
         <v>50</v>
       </c>
       <c r="C561" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="562" spans="1:3">
@@ -6572,7 +6583,7 @@
         <v>25</v>
       </c>
       <c r="C562" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="563" spans="1:3">
@@ -6583,7 +6594,7 @@
         <v>34</v>
       </c>
       <c r="C563" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="564" spans="1:3">
@@ -6594,7 +6605,7 @@
         <v>59</v>
       </c>
       <c r="C564" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="565" spans="1:3">
@@ -6605,7 +6616,7 @@
         <v>20</v>
       </c>
       <c r="C565" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="566" spans="1:3">
@@ -6616,7 +6627,7 @@
         <v>44</v>
       </c>
       <c r="C566" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="567" spans="1:3">
@@ -6627,7 +6638,7 @@
         <v>57</v>
       </c>
       <c r="C567" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="568" spans="1:3">
@@ -6638,7 +6649,7 @@
         <v>38</v>
       </c>
       <c r="C568" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="569" spans="1:3">
@@ -6649,7 +6660,7 @@
         <v>23</v>
       </c>
       <c r="C569" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="570" spans="1:3">
@@ -6660,7 +6671,7 @@
         <v>42</v>
       </c>
       <c r="C570" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="571" spans="1:3">
@@ -6671,7 +6682,7 @@
         <v>23</v>
       </c>
       <c r="C571" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="572" spans="1:3">
@@ -6682,7 +6693,7 @@
         <v>40</v>
       </c>
       <c r="C572" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="573" spans="1:3">
@@ -6693,7 +6704,7 @@
         <v>17</v>
       </c>
       <c r="C573" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="574" spans="1:3">
@@ -6704,7 +6715,7 @@
         <v>64</v>
       </c>
       <c r="C574" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="575" spans="1:3">
@@ -6715,7 +6726,7 @@
         <v>61</v>
       </c>
       <c r="C575" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="576" spans="1:3">
@@ -6726,7 +6737,7 @@
         <v>29</v>
       </c>
       <c r="C576" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="577" spans="1:3">
@@ -6737,7 +6748,7 @@
         <v>45</v>
       </c>
       <c r="C577" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="578" spans="1:3">
@@ -6770,7 +6781,7 @@
         <v>46</v>
       </c>
       <c r="C580" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="581" spans="1:3">
@@ -6781,7 +6792,7 @@
         <v>21</v>
       </c>
       <c r="C581" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="582" spans="1:3">
@@ -6792,7 +6803,7 @@
         <v>32</v>
       </c>
       <c r="C582" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="583" spans="1:3">
@@ -6803,7 +6814,7 @@
         <v>52</v>
       </c>
       <c r="C583" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="584" spans="1:3">
@@ -6814,7 +6825,7 @@
         <v>17</v>
       </c>
       <c r="C584" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="585" spans="1:3">
@@ -6825,7 +6836,7 @@
         <v>58</v>
       </c>
       <c r="C585" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="586" spans="1:3">
@@ -6836,7 +6847,7 @@
         <v>23</v>
       </c>
       <c r="C586" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="587" spans="1:3">
@@ -6847,7 +6858,7 @@
         <v>45</v>
       </c>
       <c r="C587" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="588" spans="1:3">
@@ -6858,7 +6869,7 @@
         <v>65</v>
       </c>
       <c r="C588" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="589" spans="1:3">
@@ -6869,7 +6880,7 @@
         <v>24</v>
       </c>
       <c r="C589" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="590" spans="1:3">
@@ -6880,7 +6891,7 @@
         <v>54</v>
       </c>
       <c r="C590" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="591" spans="1:3">
@@ -6902,7 +6913,7 @@
         <v>61</v>
       </c>
       <c r="C592" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="593" spans="1:3">
@@ -6913,7 +6924,7 @@
         <v>60</v>
       </c>
       <c r="C593" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="594" spans="1:3">
@@ -6924,7 +6935,7 @@
         <v>44</v>
       </c>
       <c r="C594" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="595" spans="1:3">
@@ -6935,7 +6946,7 @@
         <v>16</v>
       </c>
       <c r="C595" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="596" spans="1:3">
@@ -6946,7 +6957,7 @@
         <v>17</v>
       </c>
       <c r="C596" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="597" spans="1:3">
@@ -6957,7 +6968,7 @@
         <v>60</v>
       </c>
       <c r="C597" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="598" spans="1:3">
@@ -6968,7 +6979,7 @@
         <v>26</v>
       </c>
       <c r="C598" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="599" spans="1:3">
@@ -6979,7 +6990,7 @@
         <v>32</v>
       </c>
       <c r="C599" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="600" spans="1:3">
@@ -6990,7 +7001,7 @@
         <v>42</v>
       </c>
       <c r="C600" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="601" spans="1:3">
@@ -7001,7 +7012,7 @@
         <v>37</v>
       </c>
       <c r="C601" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="602" spans="1:3">
@@ -7012,7 +7023,7 @@
         <v>57</v>
       </c>
       <c r="C602" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="603" spans="1:3">
@@ -7023,7 +7034,7 @@
         <v>53</v>
       </c>
       <c r="C603" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="604" spans="1:3">
@@ -7034,7 +7045,7 @@
         <v>56</v>
       </c>
       <c r="C604" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="605" spans="1:3">
@@ -7045,7 +7056,7 @@
         <v>63</v>
       </c>
       <c r="C605" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="606" spans="1:3">
@@ -7056,7 +7067,7 @@
         <v>21</v>
       </c>
       <c r="C606" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="607" spans="1:3">
@@ -7067,7 +7078,7 @@
         <v>25</v>
       </c>
       <c r="C607" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="608" spans="1:3">
@@ -7078,7 +7089,7 @@
         <v>30</v>
       </c>
       <c r="C608" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="609" spans="1:3">
@@ -7089,7 +7100,7 @@
         <v>22</v>
       </c>
       <c r="C609" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="610" spans="1:3">
@@ -7111,7 +7122,7 @@
         <v>63</v>
       </c>
       <c r="C611" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="612" spans="1:3">
@@ -7133,7 +7144,7 @@
         <v>23</v>
       </c>
       <c r="C613" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="614" spans="1:3">
@@ -7144,7 +7155,7 @@
         <v>27</v>
       </c>
       <c r="C614" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="615" spans="1:3">
@@ -7155,7 +7166,7 @@
         <v>42</v>
       </c>
       <c r="C615" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="616" spans="1:3">
@@ -7166,7 +7177,7 @@
         <v>48</v>
       </c>
       <c r="C616" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="617" spans="1:3">
@@ -7177,7 +7188,7 @@
         <v>18</v>
       </c>
       <c r="C617" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="618" spans="1:3">
@@ -7188,7 +7199,7 @@
         <v>28</v>
       </c>
       <c r="C618" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="619" spans="1:3">
@@ -7199,7 +7210,7 @@
         <v>29</v>
       </c>
       <c r="C619" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="620" spans="1:3">
@@ -7210,7 +7221,7 @@
         <v>35</v>
       </c>
       <c r="C620" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="621" spans="1:3">
@@ -7221,7 +7232,7 @@
         <v>19</v>
       </c>
       <c r="C621" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="622" spans="1:3">
@@ -7232,7 +7243,7 @@
         <v>31</v>
       </c>
       <c r="C622" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="623" spans="1:3">
@@ -7254,7 +7265,7 @@
         <v>48</v>
       </c>
       <c r="C624" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="625" spans="1:3">
@@ -7265,7 +7276,7 @@
         <v>19</v>
       </c>
       <c r="C625" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="626" spans="1:3">
@@ -7276,7 +7287,7 @@
         <v>42</v>
       </c>
       <c r="C626" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="627" spans="1:3">
@@ -7287,7 +7298,7 @@
         <v>33</v>
       </c>
       <c r="C627" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="628" spans="1:3">
@@ -7298,7 +7309,7 @@
         <v>34</v>
       </c>
       <c r="C628" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="629" spans="1:3">
@@ -7309,7 +7320,7 @@
         <v>53</v>
       </c>
       <c r="C629" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="630" spans="1:3">
@@ -7320,7 +7331,7 @@
         <v>54</v>
       </c>
       <c r="C630" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="631" spans="1:3">
@@ -7331,7 +7342,7 @@
         <v>41</v>
       </c>
       <c r="C631" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="632" spans="1:3">
@@ -7342,7 +7353,7 @@
         <v>52</v>
       </c>
       <c r="C632" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="633" spans="1:3">
@@ -7353,7 +7364,7 @@
         <v>19</v>
       </c>
       <c r="C633" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="634" spans="1:3">
@@ -7364,7 +7375,7 @@
         <v>35</v>
       </c>
       <c r="C634" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="635" spans="1:3">
@@ -7375,7 +7386,7 @@
         <v>45</v>
       </c>
       <c r="C635" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="636" spans="1:3">
@@ -7386,7 +7397,7 @@
         <v>45</v>
       </c>
       <c r="C636" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="637" spans="1:3">
@@ -7397,7 +7408,7 @@
         <v>35</v>
       </c>
       <c r="C637" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="638" spans="1:3">
@@ -7408,7 +7419,7 @@
         <v>46</v>
       </c>
       <c r="C638" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="639" spans="1:3">
@@ -7419,7 +7430,7 @@
         <v>46</v>
       </c>
       <c r="C639" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="640" spans="1:3">
@@ -7430,7 +7441,7 @@
         <v>57</v>
       </c>
       <c r="C640" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="641" spans="1:3">
@@ -7441,7 +7452,7 @@
         <v>35</v>
       </c>
       <c r="C641" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="642" spans="1:3">
@@ -7452,7 +7463,7 @@
         <v>24</v>
       </c>
       <c r="C642" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="643" spans="1:3">
@@ -7463,7 +7474,7 @@
         <v>32</v>
       </c>
       <c r="C643" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="644" spans="1:3">
@@ -7474,7 +7485,7 @@
         <v>61</v>
       </c>
       <c r="C644" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="645" spans="1:3">
@@ -7485,7 +7496,7 @@
         <v>25</v>
       </c>
       <c r="C645" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="646" spans="1:3">
@@ -7496,7 +7507,7 @@
         <v>49</v>
       </c>
       <c r="C646" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="647" spans="1:3">
@@ -7507,7 +7518,7 @@
         <v>38</v>
       </c>
       <c r="C647" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="648" spans="1:3">
@@ -7518,7 +7529,7 @@
         <v>17</v>
       </c>
       <c r="C648" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="649" spans="1:3">
@@ -7529,7 +7540,7 @@
         <v>55</v>
       </c>
       <c r="C649" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="650" spans="1:3">
@@ -7551,7 +7562,7 @@
         <v>34</v>
       </c>
       <c r="C651" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="652" spans="1:3">
@@ -7573,7 +7584,7 @@
         <v>32</v>
       </c>
       <c r="C653" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="654" spans="1:3">
@@ -7584,7 +7595,7 @@
         <v>55</v>
       </c>
       <c r="C654" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="655" spans="1:3">
@@ -7595,7 +7606,7 @@
         <v>37</v>
       </c>
       <c r="C655" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="656" spans="1:3">
@@ -7606,7 +7617,7 @@
         <v>51</v>
       </c>
       <c r="C656" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="657" spans="1:3">
@@ -7617,7 +7628,7 @@
         <v>38</v>
       </c>
       <c r="C657" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="658" spans="1:3">
@@ -7628,7 +7639,7 @@
         <v>48</v>
       </c>
       <c r="C658" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="659" spans="1:3">
@@ -7639,7 +7650,7 @@
         <v>25</v>
       </c>
       <c r="C659" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="660" spans="1:3">
@@ -7650,7 +7661,7 @@
         <v>50</v>
       </c>
       <c r="C660" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="661" spans="1:3">
@@ -7661,7 +7672,7 @@
         <v>21</v>
       </c>
       <c r="C661" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="662" spans="1:3">
@@ -7672,7 +7683,7 @@
         <v>55</v>
       </c>
       <c r="C662" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="663" spans="1:3">
@@ -7683,7 +7694,7 @@
         <v>35</v>
       </c>
       <c r="C663" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="664" spans="1:3">
@@ -7694,7 +7705,7 @@
         <v>57</v>
       </c>
       <c r="C664" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="665" spans="1:3">
@@ -7705,7 +7716,7 @@
         <v>29</v>
       </c>
       <c r="C665" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="666" spans="1:3">
@@ -7716,7 +7727,7 @@
         <v>31</v>
       </c>
       <c r="C666" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="667" spans="1:3">
@@ -7727,7 +7738,7 @@
         <v>16</v>
       </c>
       <c r="C667" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="668" spans="1:3">
@@ -7738,7 +7749,7 @@
         <v>63</v>
       </c>
       <c r="C668" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="669" spans="1:3">
@@ -7749,7 +7760,7 @@
         <v>32</v>
       </c>
       <c r="C669" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="670" spans="1:3">
@@ -7760,7 +7771,7 @@
         <v>63</v>
       </c>
       <c r="C670" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="671" spans="1:3">
@@ -7771,7 +7782,7 @@
         <v>31</v>
       </c>
       <c r="C671" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="672" spans="1:3">
@@ -7782,7 +7793,7 @@
         <v>29</v>
       </c>
       <c r="C672" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="673" spans="1:3">
@@ -7793,7 +7804,7 @@
         <v>49</v>
       </c>
       <c r="C673" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="674" spans="1:3">
@@ -7804,7 +7815,7 @@
         <v>50</v>
       </c>
       <c r="C674" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="675" spans="1:3">
@@ -7815,7 +7826,7 @@
         <v>40</v>
       </c>
       <c r="C675" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="676" spans="1:3">
@@ -7826,7 +7837,7 @@
         <v>43</v>
       </c>
       <c r="C676" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="677" spans="1:3">
@@ -7837,7 +7848,7 @@
         <v>46</v>
       </c>
       <c r="C677" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="678" spans="1:3">
@@ -7859,7 +7870,7 @@
         <v>45</v>
       </c>
       <c r="C679" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="680" spans="1:3">
@@ -7870,7 +7881,7 @@
         <v>52</v>
       </c>
       <c r="C680" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="681" spans="1:3">
@@ -7881,7 +7892,7 @@
         <v>18</v>
       </c>
       <c r="C681" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="682" spans="1:3">
@@ -7892,7 +7903,7 @@
         <v>43</v>
       </c>
       <c r="C682" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="683" spans="1:3">
@@ -7903,7 +7914,7 @@
         <v>60</v>
       </c>
       <c r="C683" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="684" spans="1:3">
@@ -7914,7 +7925,7 @@
         <v>30</v>
       </c>
       <c r="C684" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="685" spans="1:3">
@@ -7925,7 +7936,7 @@
         <v>54</v>
       </c>
       <c r="C685" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="686" spans="1:3">
@@ -7947,7 +7958,7 @@
         <v>36</v>
       </c>
       <c r="C687" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="688" spans="1:3">
@@ -7969,7 +7980,7 @@
         <v>61</v>
       </c>
       <c r="C689" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="690" spans="1:3">
@@ -7980,7 +7991,7 @@
         <v>28</v>
       </c>
       <c r="C690" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="691" spans="1:3">
@@ -7991,7 +8002,7 @@
         <v>23</v>
       </c>
       <c r="C691" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="692" spans="1:3">
@@ -8002,7 +8013,7 @@
         <v>43</v>
       </c>
       <c r="C692" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="693" spans="1:3">
@@ -8013,7 +8024,7 @@
         <v>57</v>
       </c>
       <c r="C693" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="694" spans="1:3">
@@ -8024,7 +8035,7 @@
         <v>35</v>
       </c>
       <c r="C694" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="695" spans="1:3">
@@ -8035,7 +8046,7 @@
         <v>53</v>
       </c>
       <c r="C695" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="696" spans="1:3">
@@ -8046,7 +8057,7 @@
         <v>28</v>
       </c>
       <c r="C696" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="697" spans="1:3">
@@ -8057,7 +8068,7 @@
         <v>65</v>
       </c>
       <c r="C697" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="698" spans="1:3">
@@ -8068,7 +8079,7 @@
         <v>53</v>
       </c>
       <c r="C698" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="699" spans="1:3">
@@ -8079,7 +8090,7 @@
         <v>53</v>
       </c>
       <c r="C699" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="700" spans="1:3">
@@ -8090,7 +8101,7 @@
         <v>36</v>
       </c>
       <c r="C700" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="701" spans="1:3">
@@ -8101,7 +8112,7 @@
         <v>53</v>
       </c>
       <c r="C701" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="702" spans="1:3">
@@ -8112,7 +8123,7 @@
         <v>45</v>
       </c>
       <c r="C702" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="703" spans="1:3">
@@ -8123,7 +8134,7 @@
         <v>39</v>
       </c>
       <c r="C703" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="704" spans="1:3">
@@ -8134,7 +8145,7 @@
         <v>27</v>
       </c>
       <c r="C704" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="705" spans="1:3">
@@ -8145,7 +8156,7 @@
         <v>43</v>
       </c>
       <c r="C705" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="706" spans="1:3">
@@ -8156,7 +8167,7 @@
         <v>60</v>
       </c>
       <c r="C706" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="707" spans="1:3">
@@ -8167,7 +8178,7 @@
         <v>17</v>
       </c>
       <c r="C707" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="708" spans="1:3">
@@ -8178,7 +8189,7 @@
         <v>32</v>
       </c>
       <c r="C708" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="709" spans="1:3">
@@ -8189,7 +8200,7 @@
         <v>30</v>
       </c>
       <c r="C709" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="710" spans="1:3">
@@ -8200,7 +8211,7 @@
         <v>29</v>
       </c>
       <c r="C710" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="711" spans="1:3">
@@ -8211,7 +8222,7 @@
         <v>41</v>
       </c>
       <c r="C711" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="712" spans="1:3">
@@ -8222,7 +8233,7 @@
         <v>36</v>
       </c>
       <c r="C712" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="713" spans="1:3">
@@ -8244,7 +8255,7 @@
         <v>43</v>
       </c>
       <c r="C714" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="715" spans="1:3">
@@ -8255,7 +8266,7 @@
         <v>59</v>
       </c>
       <c r="C715" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="716" spans="1:3">
@@ -8266,7 +8277,7 @@
         <v>26</v>
       </c>
       <c r="C716" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="717" spans="1:3">
@@ -8277,7 +8288,7 @@
         <v>22</v>
       </c>
       <c r="C717" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="718" spans="1:3">
@@ -8288,7 +8299,7 @@
         <v>28</v>
       </c>
       <c r="C718" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="719" spans="1:3">
@@ -8299,7 +8310,7 @@
         <v>57</v>
       </c>
       <c r="C719" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="720" spans="1:3">
@@ -8310,7 +8321,7 @@
         <v>56</v>
       </c>
       <c r="C720" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="721" spans="1:3">
@@ -8321,7 +8332,7 @@
         <v>57</v>
       </c>
       <c r="C721" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="722" spans="1:3">
@@ -8332,7 +8343,7 @@
         <v>54</v>
       </c>
       <c r="C722" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="723" spans="1:3">
@@ -8343,7 +8354,7 @@
         <v>57</v>
       </c>
       <c r="C723" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="724" spans="1:3">
@@ -8365,7 +8376,7 @@
         <v>65</v>
       </c>
       <c r="C725" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="726" spans="1:3">
@@ -8376,7 +8387,7 @@
         <v>45</v>
       </c>
       <c r="C726" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="727" spans="1:3">
@@ -8387,7 +8398,7 @@
         <v>35</v>
       </c>
       <c r="C727" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="728" spans="1:3">
@@ -8398,7 +8409,7 @@
         <v>63</v>
       </c>
       <c r="C728" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="729" spans="1:3">
@@ -8409,7 +8420,7 @@
         <v>58</v>
       </c>
       <c r="C729" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="730" spans="1:3">
@@ -8420,7 +8431,7 @@
         <v>47</v>
       </c>
       <c r="C730" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="731" spans="1:3">
@@ -8431,7 +8442,7 @@
         <v>24</v>
       </c>
       <c r="C731" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="732" spans="1:3">
@@ -8442,7 +8453,7 @@
         <v>26</v>
       </c>
       <c r="C732" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="733" spans="1:3">
@@ -8453,7 +8464,7 @@
         <v>19</v>
       </c>
       <c r="C733" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="734" spans="1:3">
@@ -8486,7 +8497,7 @@
         <v>34</v>
       </c>
       <c r="C736" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="737" spans="1:3">
@@ -8497,7 +8508,7 @@
         <v>28</v>
       </c>
       <c r="C737" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="738" spans="1:3">
@@ -8508,7 +8519,7 @@
         <v>53</v>
       </c>
       <c r="C738" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="739" spans="1:3">
@@ -8519,7 +8530,7 @@
         <v>33</v>
       </c>
       <c r="C739" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="740" spans="1:3">
@@ -8530,7 +8541,7 @@
         <v>19</v>
       </c>
       <c r="C740" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="741" spans="1:3">
@@ -8541,7 +8552,7 @@
         <v>46</v>
       </c>
       <c r="C741" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="742" spans="1:3">
@@ -8552,7 +8563,7 @@
         <v>20</v>
       </c>
       <c r="C742" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="743" spans="1:3">
@@ -8563,7 +8574,7 @@
         <v>54</v>
       </c>
       <c r="C743" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="744" spans="1:3">
@@ -8574,7 +8585,7 @@
         <v>21</v>
       </c>
       <c r="C744" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="745" spans="1:3">
@@ -8585,7 +8596,7 @@
         <v>44</v>
       </c>
       <c r="C745" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="746" spans="1:3">
@@ -8596,7 +8607,7 @@
         <v>27</v>
       </c>
       <c r="C746" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="747" spans="1:3">
@@ -8607,7 +8618,7 @@
         <v>48</v>
       </c>
       <c r="C747" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="748" spans="1:3">
@@ -8618,7 +8629,7 @@
         <v>58</v>
       </c>
       <c r="C748" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="749" spans="1:3">
@@ -8629,7 +8640,7 @@
         <v>31</v>
       </c>
       <c r="C749" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="750" spans="1:3">
@@ -8640,7 +8651,7 @@
         <v>42</v>
       </c>
       <c r="C750" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="751" spans="1:3">
@@ -8651,7 +8662,7 @@
         <v>21</v>
       </c>
       <c r="C751" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="752" spans="1:3">
@@ -8662,7 +8673,7 @@
         <v>60</v>
       </c>
       <c r="C752" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="753" spans="1:3">
@@ -8673,7 +8684,7 @@
         <v>63</v>
       </c>
       <c r="C753" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="754" spans="1:3">
@@ -8684,7 +8695,7 @@
         <v>52</v>
       </c>
       <c r="C754" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="755" spans="1:3">
@@ -8695,7 +8706,7 @@
         <v>30</v>
       </c>
       <c r="C755" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="756" spans="1:3">
@@ -8706,7 +8717,7 @@
         <v>54</v>
       </c>
       <c r="C756" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="757" spans="1:3">
@@ -8717,7 +8728,7 @@
         <v>32</v>
       </c>
       <c r="C757" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="758" spans="1:3">
@@ -8728,7 +8739,7 @@
         <v>18</v>
       </c>
       <c r="C758" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="759" spans="1:3">
@@ -8739,7 +8750,7 @@
         <v>26</v>
       </c>
       <c r="C759" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="760" spans="1:3">
@@ -8750,7 +8761,7 @@
         <v>16</v>
       </c>
       <c r="C760" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="761" spans="1:3">
@@ -8761,7 +8772,7 @@
         <v>57</v>
       </c>
       <c r="C761" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="762" spans="1:3">
@@ -8772,7 +8783,7 @@
         <v>42</v>
       </c>
       <c r="C762" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="763" spans="1:3">
@@ -8794,7 +8805,7 @@
         <v>45</v>
       </c>
       <c r="C764" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="765" spans="1:3">
@@ -8805,7 +8816,7 @@
         <v>47</v>
       </c>
       <c r="C765" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="766" spans="1:3">
@@ -8816,7 +8827,7 @@
         <v>45</v>
       </c>
       <c r="C766" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="767" spans="1:3">
@@ -8827,7 +8838,7 @@
         <v>26</v>
       </c>
       <c r="C767" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="768" spans="1:3">
@@ -8838,7 +8849,7 @@
         <v>58</v>
       </c>
       <c r="C768" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="769" spans="1:3">
@@ -8849,7 +8860,7 @@
         <v>41</v>
       </c>
       <c r="C769" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="770" spans="1:3">
@@ -8860,7 +8871,7 @@
         <v>32</v>
       </c>
       <c r="C770" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="771" spans="1:3">
@@ -8882,7 +8893,7 @@
         <v>39</v>
       </c>
       <c r="C772" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="773" spans="1:3">
@@ -8893,7 +8904,7 @@
         <v>18</v>
       </c>
       <c r="C773" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="774" spans="1:3">
@@ -8904,7 +8915,7 @@
         <v>29</v>
       </c>
       <c r="C774" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="775" spans="1:3">
@@ -8915,7 +8926,7 @@
         <v>25</v>
       </c>
       <c r="C775" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="776" spans="1:3">
@@ -8926,7 +8937,7 @@
         <v>29</v>
       </c>
       <c r="C776" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="777" spans="1:3">
@@ -8948,7 +8959,7 @@
         <v>44</v>
       </c>
       <c r="C778" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="779" spans="1:3">
@@ -8959,7 +8970,7 @@
         <v>18</v>
       </c>
       <c r="C779" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="780" spans="1:3">
@@ -8970,7 +8981,7 @@
         <v>35</v>
       </c>
       <c r="C780" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="781" spans="1:3">
@@ -8981,7 +8992,7 @@
         <v>31</v>
       </c>
       <c r="C781" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="782" spans="1:3">
@@ -9014,7 +9025,7 @@
         <v>18</v>
       </c>
       <c r="C784" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="785" spans="1:3">
@@ -9025,7 +9036,7 @@
         <v>52</v>
       </c>
       <c r="C785" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="786" spans="1:3">
@@ -9036,7 +9047,7 @@
         <v>65</v>
       </c>
       <c r="C786" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="787" spans="1:3">
@@ -9047,7 +9058,7 @@
         <v>17</v>
       </c>
       <c r="C787" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="788" spans="1:3">
@@ -9058,7 +9069,7 @@
         <v>30</v>
       </c>
       <c r="C788" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="789" spans="1:3">
@@ -9069,7 +9080,7 @@
         <v>23</v>
       </c>
       <c r="C789" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="790" spans="1:3">
@@ -9080,7 +9091,7 @@
         <v>53</v>
       </c>
       <c r="C790" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="791" spans="1:3">
@@ -9091,7 +9102,7 @@
         <v>50</v>
       </c>
       <c r="C791" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="792" spans="1:3">
@@ -9102,7 +9113,7 @@
         <v>64</v>
       </c>
       <c r="C792" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="793" spans="1:3">
@@ -9113,7 +9124,7 @@
         <v>53</v>
       </c>
       <c r="C793" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="794" spans="1:3">
@@ -9124,7 +9135,7 @@
         <v>43</v>
       </c>
       <c r="C794" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="795" spans="1:3">
@@ -9135,7 +9146,7 @@
         <v>38</v>
       </c>
       <c r="C795" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="796" spans="1:3">
@@ -9146,7 +9157,7 @@
         <v>51</v>
       </c>
       <c r="C796" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="797" spans="1:3">
@@ -9157,7 +9168,7 @@
         <v>64</v>
       </c>
       <c r="C797" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="798" spans="1:3">
@@ -9168,7 +9179,7 @@
         <v>27</v>
       </c>
       <c r="C798" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="799" spans="1:3">
@@ -9179,7 +9190,7 @@
         <v>62</v>
       </c>
       <c r="C799" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="800" spans="1:3">
@@ -9190,7 +9201,7 @@
         <v>26</v>
       </c>
       <c r="C800" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="801" spans="1:3">
@@ -9212,7 +9223,7 @@
         <v>38</v>
       </c>
       <c r="C802" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="803" spans="1:3">
@@ -9223,7 +9234,7 @@
         <v>59</v>
       </c>
       <c r="C803" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="804" spans="1:3">
@@ -9234,7 +9245,7 @@
         <v>24</v>
       </c>
       <c r="C804" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="805" spans="1:3">
@@ -9245,7 +9256,7 @@
         <v>20</v>
       </c>
       <c r="C805" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="806" spans="1:3">
@@ -9256,7 +9267,7 @@
         <v>55</v>
       </c>
       <c r="C806" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="807" spans="1:3">
@@ -9267,7 +9278,7 @@
         <v>26</v>
       </c>
       <c r="C807" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="808" spans="1:3">
@@ -9278,7 +9289,7 @@
         <v>36</v>
       </c>
       <c r="C808" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="809" spans="1:3">
@@ -9289,7 +9300,7 @@
         <v>22</v>
       </c>
       <c r="C809" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="810" spans="1:3">
@@ -9300,7 +9311,7 @@
         <v>33</v>
       </c>
       <c r="C810" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="811" spans="1:3">
@@ -9322,7 +9333,7 @@
         <v>51</v>
       </c>
       <c r="C812" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="813" spans="1:3">
@@ -9333,7 +9344,7 @@
         <v>53</v>
       </c>
       <c r="C813" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="814" spans="1:3">
@@ -9344,7 +9355,7 @@
         <v>46</v>
       </c>
       <c r="C814" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="815" spans="1:3">
@@ -9355,7 +9366,7 @@
         <v>43</v>
       </c>
       <c r="C815" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="816" spans="1:3">
@@ -9366,7 +9377,7 @@
         <v>51</v>
       </c>
       <c r="C816" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="817" spans="1:3">
@@ -9377,7 +9388,7 @@
         <v>23</v>
       </c>
       <c r="C817" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="818" spans="1:3">
@@ -9388,7 +9399,7 @@
         <v>60</v>
       </c>
       <c r="C818" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="819" spans="1:3">
@@ -9399,7 +9410,7 @@
         <v>48</v>
       </c>
       <c r="C819" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="820" spans="1:3">
@@ -9421,7 +9432,7 @@
         <v>37</v>
       </c>
       <c r="C821" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="822" spans="1:3">
@@ -9432,7 +9443,7 @@
         <v>45</v>
       </c>
       <c r="C822" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="823" spans="1:3">
@@ -9443,7 +9454,7 @@
         <v>22</v>
       </c>
       <c r="C823" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="824" spans="1:3">
@@ -9454,7 +9465,7 @@
         <v>33</v>
       </c>
       <c r="C824" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="825" spans="1:3">
@@ -9465,7 +9476,7 @@
         <v>30</v>
       </c>
       <c r="C825" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="826" spans="1:3">
@@ -9476,7 +9487,7 @@
         <v>23</v>
       </c>
       <c r="C826" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="827" spans="1:3">
@@ -9487,7 +9498,7 @@
         <v>22</v>
       </c>
       <c r="C827" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="828" spans="1:3">
@@ -9509,7 +9520,7 @@
         <v>55</v>
       </c>
       <c r="C829" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="830" spans="1:3">
@@ -9520,7 +9531,7 @@
         <v>24</v>
       </c>
       <c r="C830" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="831" spans="1:3">
@@ -9531,7 +9542,7 @@
         <v>39</v>
       </c>
       <c r="C831" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="832" spans="1:3">
@@ -9542,7 +9553,7 @@
         <v>28</v>
       </c>
       <c r="C832" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="833" spans="1:3">
@@ -9553,7 +9564,7 @@
         <v>59</v>
       </c>
       <c r="C833" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="834" spans="1:3">
@@ -9564,7 +9575,7 @@
         <v>21</v>
       </c>
       <c r="C834" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="835" spans="1:3">
@@ -9575,7 +9586,7 @@
         <v>64</v>
       </c>
       <c r="C835" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="836" spans="1:3">
@@ -9586,7 +9597,7 @@
         <v>16</v>
       </c>
       <c r="C836" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="837" spans="1:3">
@@ -9597,7 +9608,7 @@
         <v>59</v>
       </c>
       <c r="C837" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="838" spans="1:3">
@@ -9608,7 +9619,7 @@
         <v>55</v>
       </c>
       <c r="C838" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="839" spans="1:3">
@@ -9619,7 +9630,7 @@
         <v>40</v>
       </c>
       <c r="C839" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="840" spans="1:3">
@@ -9630,7 +9641,7 @@
         <v>27</v>
       </c>
       <c r="C840" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="841" spans="1:3">
@@ -9641,7 +9652,7 @@
         <v>23</v>
       </c>
       <c r="C841" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="842" spans="1:3">
@@ -9652,7 +9663,7 @@
         <v>24</v>
       </c>
       <c r="C842" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="843" spans="1:3">
@@ -9663,7 +9674,7 @@
         <v>60</v>
       </c>
       <c r="C843" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="844" spans="1:3">
@@ -9674,7 +9685,7 @@
         <v>46</v>
       </c>
       <c r="C844" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="845" spans="1:3">
@@ -9685,7 +9696,7 @@
         <v>42</v>
       </c>
       <c r="C845" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="846" spans="1:3">
@@ -9696,7 +9707,7 @@
         <v>40</v>
       </c>
       <c r="C846" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="847" spans="1:3">
@@ -9707,7 +9718,7 @@
         <v>44</v>
       </c>
       <c r="C847" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="848" spans="1:3">
@@ -9718,7 +9729,7 @@
         <v>64</v>
       </c>
       <c r="C848" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="849" spans="1:3">
@@ -9729,7 +9740,7 @@
         <v>19</v>
       </c>
       <c r="C849" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="850" spans="1:3">
@@ -9740,7 +9751,7 @@
         <v>49</v>
       </c>
       <c r="C850" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="851" spans="1:3">
@@ -9751,7 +9762,7 @@
         <v>65</v>
       </c>
       <c r="C851" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="852" spans="1:3">
@@ -9773,7 +9784,7 @@
         <v>32</v>
       </c>
       <c r="C853" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="854" spans="1:3">
@@ -9784,7 +9795,7 @@
         <v>62</v>
       </c>
       <c r="C854" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="855" spans="1:3">
@@ -9795,7 +9806,7 @@
         <v>27</v>
       </c>
       <c r="C855" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="856" spans="1:3">
@@ -9806,7 +9817,7 @@
         <v>50</v>
       </c>
       <c r="C856" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="857" spans="1:3">
@@ -9817,7 +9828,7 @@
         <v>45</v>
       </c>
       <c r="C857" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="858" spans="1:3">
@@ -9828,7 +9839,7 @@
         <v>55</v>
       </c>
       <c r="C858" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="859" spans="1:3">
@@ -9839,7 +9850,7 @@
         <v>50</v>
       </c>
       <c r="C859" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="860" spans="1:3">
@@ -9850,7 +9861,7 @@
         <v>32</v>
       </c>
       <c r="C860" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="861" spans="1:3">
@@ -9861,7 +9872,7 @@
         <v>42</v>
       </c>
       <c r="C861" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="862" spans="1:3">
@@ -9872,7 +9883,7 @@
         <v>52</v>
       </c>
       <c r="C862" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="863" spans="1:3">
@@ -9883,7 +9894,7 @@
         <v>51</v>
       </c>
       <c r="C863" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="864" spans="1:3">
@@ -9894,7 +9905,7 @@
         <v>50</v>
       </c>
       <c r="C864" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="865" spans="1:3">
@@ -9905,7 +9916,7 @@
         <v>36</v>
       </c>
       <c r="C865" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="866" spans="1:3">
@@ -9927,7 +9938,7 @@
         <v>57</v>
       </c>
       <c r="C867" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="868" spans="1:3">
@@ -9938,7 +9949,7 @@
         <v>40</v>
       </c>
       <c r="C868" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="869" spans="1:3">
@@ -9949,7 +9960,7 @@
         <v>18</v>
       </c>
       <c r="C869" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="870" spans="1:3">
@@ -9960,7 +9971,7 @@
         <v>46</v>
       </c>
       <c r="C870" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="871" spans="1:3">
@@ -9971,7 +9982,7 @@
         <v>26</v>
       </c>
       <c r="C871" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="872" spans="1:3">
@@ -9982,7 +9993,7 @@
         <v>34</v>
       </c>
       <c r="C872" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="873" spans="1:3">
@@ -9993,7 +10004,7 @@
         <v>18</v>
       </c>
       <c r="C873" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="874" spans="1:3">
@@ -10004,7 +10015,7 @@
         <v>26</v>
       </c>
       <c r="C874" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="875" spans="1:3">
@@ -10015,7 +10026,7 @@
         <v>29</v>
       </c>
       <c r="C875" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="876" spans="1:3">
@@ -10026,7 +10037,7 @@
         <v>29</v>
       </c>
       <c r="C876" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="877" spans="1:3">
@@ -10037,7 +10048,7 @@
         <v>41</v>
       </c>
       <c r="C877" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="878" spans="1:3">
@@ -10048,7 +10059,7 @@
         <v>40</v>
       </c>
       <c r="C878" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="879" spans="1:3">
@@ -10059,7 +10070,7 @@
         <v>30</v>
       </c>
       <c r="C879" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="880" spans="1:3">
@@ -10070,7 +10081,7 @@
         <v>27</v>
       </c>
       <c r="C880" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="881" spans="1:3">
@@ -10081,7 +10092,7 @@
         <v>18</v>
       </c>
       <c r="C881" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="882" spans="1:3">
@@ -10103,7 +10114,7 @@
         <v>32</v>
       </c>
       <c r="C883" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="884" spans="1:3">
@@ -10114,7 +10125,7 @@
         <v>27</v>
       </c>
       <c r="C884" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="885" spans="1:3">
@@ -10125,7 +10136,7 @@
         <v>49</v>
       </c>
       <c r="C885" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="886" spans="1:3">
@@ -10136,7 +10147,7 @@
         <v>33</v>
       </c>
       <c r="C886" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="887" spans="1:3">
@@ -10147,7 +10158,7 @@
         <v>26</v>
       </c>
       <c r="C887" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="888" spans="1:3">
@@ -10158,7 +10169,7 @@
         <v>27</v>
       </c>
       <c r="C888" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="889" spans="1:3">
@@ -10169,7 +10180,7 @@
         <v>58</v>
       </c>
       <c r="C889" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="890" spans="1:3">
@@ -10180,7 +10191,7 @@
         <v>50</v>
       </c>
       <c r="C890" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="891" spans="1:3">
@@ -10191,7 +10202,7 @@
         <v>35</v>
       </c>
       <c r="C891" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="892" spans="1:3">
@@ -10202,7 +10213,7 @@
         <v>19</v>
       </c>
       <c r="C892" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="893" spans="1:3">
@@ -10213,7 +10224,7 @@
         <v>62</v>
       </c>
       <c r="C893" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="894" spans="1:3">
@@ -10224,7 +10235,7 @@
         <v>63</v>
       </c>
       <c r="C894" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="895" spans="1:3">
@@ -10235,7 +10246,7 @@
         <v>64</v>
       </c>
       <c r="C895" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="896" spans="1:3">
@@ -10246,7 +10257,7 @@
         <v>42</v>
       </c>
       <c r="C896" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="897" spans="1:3">
@@ -10257,7 +10268,7 @@
         <v>24</v>
       </c>
       <c r="C897" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="898" spans="1:3">
@@ -10268,7 +10279,7 @@
         <v>23</v>
       </c>
       <c r="C898" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="899" spans="1:3">
@@ -10279,7 +10290,7 @@
         <v>45</v>
       </c>
       <c r="C899" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="900" spans="1:3">
@@ -10290,7 +10301,7 @@
         <v>25</v>
       </c>
       <c r="C900" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="901" spans="1:3">
@@ -10301,7 +10312,7 @@
         <v>28</v>
       </c>
       <c r="C901" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="902" spans="1:3">
@@ -10312,7 +10323,7 @@
         <v>17</v>
       </c>
       <c r="C902" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="903" spans="1:3">
@@ -10334,7 +10345,7 @@
         <v>33</v>
       </c>
       <c r="C904" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="905" spans="1:3">
@@ -10345,7 +10356,7 @@
         <v>38</v>
       </c>
       <c r="C905" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="906" spans="1:3">
@@ -10367,7 +10378,7 @@
         <v>65</v>
       </c>
       <c r="C907" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="908" spans="1:3">
@@ -10378,7 +10389,7 @@
         <v>37</v>
       </c>
       <c r="C908" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="909" spans="1:3">
@@ -10389,7 +10400,7 @@
         <v>59</v>
       </c>
       <c r="C909" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="910" spans="1:3">
@@ -10400,7 +10411,7 @@
         <v>43</v>
       </c>
       <c r="C910" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="911" spans="1:3">
@@ -10411,7 +10422,7 @@
         <v>39</v>
       </c>
       <c r="C911" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="912" spans="1:3">
@@ -10422,7 +10433,7 @@
         <v>21</v>
       </c>
       <c r="C912" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="913" spans="1:3">
@@ -10433,7 +10444,7 @@
         <v>50</v>
       </c>
       <c r="C913" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="914" spans="1:3">
@@ -10444,7 +10455,7 @@
         <v>42</v>
       </c>
       <c r="C914" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="915" spans="1:3">
@@ -10455,7 +10466,7 @@
         <v>62</v>
       </c>
       <c r="C915" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="916" spans="1:3">
@@ -10466,7 +10477,7 @@
         <v>56</v>
       </c>
       <c r="C916" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="917" spans="1:3">
@@ -10477,7 +10488,7 @@
         <v>36</v>
       </c>
       <c r="C917" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="918" spans="1:3">
@@ -10488,7 +10499,7 @@
         <v>17</v>
       </c>
       <c r="C918" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="919" spans="1:3">
@@ -10499,7 +10510,7 @@
         <v>39</v>
       </c>
       <c r="C919" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="920" spans="1:3">
@@ -10510,7 +10521,7 @@
         <v>57</v>
       </c>
       <c r="C920" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="921" spans="1:3">
@@ -10521,7 +10532,7 @@
         <v>55</v>
       </c>
       <c r="C921" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="922" spans="1:3">
@@ -10532,7 +10543,7 @@
         <v>20</v>
       </c>
       <c r="C922" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="923" spans="1:3">
@@ -10543,7 +10554,7 @@
         <v>55</v>
       </c>
       <c r="C923" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="924" spans="1:3">
@@ -10554,7 +10565,7 @@
         <v>40</v>
       </c>
       <c r="C924" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="925" spans="1:3">
@@ -10565,7 +10576,7 @@
         <v>18</v>
       </c>
       <c r="C925" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="926" spans="1:3">
@@ -10576,7 +10587,7 @@
         <v>42</v>
       </c>
       <c r="C926" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="927" spans="1:3">
@@ -10587,7 +10598,7 @@
         <v>54</v>
       </c>
       <c r="C927" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="928" spans="1:3">
@@ -10598,7 +10609,7 @@
         <v>41</v>
       </c>
       <c r="C928" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="929" spans="1:3">
@@ -10620,7 +10631,7 @@
         <v>29</v>
       </c>
       <c r="C930" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="931" spans="1:3">
@@ -10642,7 +10653,7 @@
         <v>21</v>
       </c>
       <c r="C932" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="933" spans="1:3">
@@ -10653,7 +10664,7 @@
         <v>38</v>
       </c>
       <c r="C933" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="934" spans="1:3">
@@ -10664,7 +10675,7 @@
         <v>46</v>
       </c>
       <c r="C934" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="935" spans="1:3">
@@ -10675,7 +10686,7 @@
         <v>49</v>
       </c>
       <c r="C935" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="936" spans="1:3">
@@ -10697,7 +10708,7 @@
         <v>59</v>
       </c>
       <c r="C937" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="938" spans="1:3">
@@ -10708,7 +10719,7 @@
         <v>17</v>
       </c>
       <c r="C938" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="939" spans="1:3">
@@ -10719,7 +10730,7 @@
         <v>23</v>
       </c>
       <c r="C939" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="940" spans="1:3">
@@ -10730,7 +10741,7 @@
         <v>52</v>
       </c>
       <c r="C940" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="941" spans="1:3">
@@ -10741,7 +10752,7 @@
         <v>37</v>
       </c>
       <c r="C941" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="942" spans="1:3">
@@ -10752,7 +10763,7 @@
         <v>34</v>
       </c>
       <c r="C942" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="943" spans="1:3">
@@ -10763,7 +10774,7 @@
         <v>56</v>
       </c>
       <c r="C943" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="944" spans="1:3">
@@ -10774,7 +10785,7 @@
         <v>40</v>
       </c>
       <c r="C944" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="945" spans="1:3">
@@ -10807,7 +10818,7 @@
         <v>38</v>
       </c>
       <c r="C947" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="948" spans="1:3">
@@ -10818,7 +10829,7 @@
         <v>59</v>
       </c>
       <c r="C948" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="949" spans="1:3">
@@ -10840,7 +10851,7 @@
         <v>31</v>
       </c>
       <c r="C950" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="951" spans="1:3">
@@ -10851,7 +10862,7 @@
         <v>23</v>
       </c>
       <c r="C951" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="952" spans="1:3">
@@ -10862,7 +10873,7 @@
         <v>28</v>
       </c>
       <c r="C952" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="953" spans="1:3">
@@ -10884,7 +10895,7 @@
         <v>54</v>
       </c>
       <c r="C954" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="955" spans="1:3">
@@ -10895,7 +10906,7 @@
         <v>55</v>
       </c>
       <c r="C955" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="956" spans="1:3">
@@ -10906,7 +10917,7 @@
         <v>62</v>
       </c>
       <c r="C956" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="957" spans="1:3">
@@ -10917,7 +10928,7 @@
         <v>44</v>
       </c>
       <c r="C957" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="958" spans="1:3">
@@ -10928,7 +10939,7 @@
         <v>63</v>
       </c>
       <c r="C958" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="959" spans="1:3">
@@ -10939,7 +10950,7 @@
         <v>24</v>
       </c>
       <c r="C959" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="960" spans="1:3">
@@ -10950,7 +10961,7 @@
         <v>24</v>
       </c>
       <c r="C960" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="961" spans="1:3">
@@ -10961,7 +10972,7 @@
         <v>33</v>
       </c>
       <c r="C961" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="962" spans="1:3">
@@ -10972,7 +10983,7 @@
         <v>62</v>
       </c>
       <c r="C962" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="963" spans="1:3">
@@ -10983,7 +10994,7 @@
         <v>58</v>
       </c>
       <c r="C963" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="964" spans="1:3">
@@ -11005,7 +11016,7 @@
         <v>61</v>
       </c>
       <c r="C965" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="966" spans="1:3">
@@ -11016,7 +11027,7 @@
         <v>21</v>
       </c>
       <c r="C966" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="967" spans="1:3">
@@ -11038,7 +11049,7 @@
         <v>24</v>
       </c>
       <c r="C968" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="969" spans="1:3">
@@ -11060,7 +11071,7 @@
         <v>62</v>
       </c>
       <c r="C970" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="971" spans="1:3">
@@ -11071,7 +11082,7 @@
         <v>36</v>
       </c>
       <c r="C971" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="972" spans="1:3">
@@ -11082,7 +11093,7 @@
         <v>41</v>
       </c>
       <c r="C972" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="973" spans="1:3">
@@ -11093,7 +11104,7 @@
         <v>62</v>
       </c>
       <c r="C973" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="974" spans="1:3">
@@ -11115,7 +11126,7 @@
         <v>23</v>
       </c>
       <c r="C975" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="976" spans="1:3">
@@ -11126,7 +11137,7 @@
         <v>18</v>
       </c>
       <c r="C976" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="977" spans="1:3">
@@ -11137,7 +11148,7 @@
         <v>30</v>
       </c>
       <c r="C977" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="978" spans="1:3">
@@ -11148,7 +11159,7 @@
         <v>58</v>
       </c>
       <c r="C978" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="979" spans="1:3">
@@ -11159,7 +11170,7 @@
         <v>31</v>
       </c>
       <c r="C979" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="980" spans="1:3">
@@ -11170,7 +11181,7 @@
         <v>26</v>
       </c>
       <c r="C980" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="981" spans="1:3">
@@ -11181,7 +11192,7 @@
         <v>61</v>
       </c>
       <c r="C981" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="982" spans="1:3">
@@ -11192,7 +11203,7 @@
         <v>28</v>
       </c>
       <c r="C982" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="983" spans="1:3">
@@ -11203,7 +11214,7 @@
         <v>48</v>
       </c>
       <c r="C983" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="984" spans="1:3">
@@ -11214,7 +11225,7 @@
         <v>36</v>
       </c>
       <c r="C984" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="985" spans="1:3">
@@ -11225,7 +11236,7 @@
         <v>29</v>
       </c>
       <c r="C985" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="986" spans="1:3">
@@ -11236,7 +11247,7 @@
         <v>35</v>
       </c>
       <c r="C986" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="987" spans="1:3">
@@ -11247,7 +11258,7 @@
         <v>32</v>
       </c>
       <c r="C987" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="988" spans="1:3">
@@ -11258,7 +11269,7 @@
         <v>47</v>
       </c>
       <c r="C988" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="989" spans="1:3">
@@ -11269,7 +11280,7 @@
         <v>27</v>
       </c>
       <c r="C989" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="990" spans="1:3">
@@ -11291,7 +11302,7 @@
         <v>47</v>
       </c>
       <c r="C991" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="992" spans="1:3">
@@ -11313,7 +11324,7 @@
         <v>24</v>
       </c>
       <c r="C993" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="994" spans="1:3">
@@ -11324,7 +11335,7 @@
         <v>43</v>
       </c>
       <c r="C994" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="995" spans="1:3">
@@ -11335,7 +11346,7 @@
         <v>58</v>
       </c>
       <c r="C995" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="996" spans="1:3">
@@ -11346,7 +11357,7 @@
         <v>22</v>
       </c>
       <c r="C996" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="997" spans="1:3">
@@ -11357,7 +11368,7 @@
         <v>25</v>
       </c>
       <c r="C997" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="998" spans="1:3">
@@ -11368,7 +11379,7 @@
         <v>44</v>
       </c>
       <c r="C998" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="999" spans="1:3">
@@ -11390,7 +11401,7 @@
         <v>58</v>
       </c>
       <c r="C1000" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1001" spans="1:3">
@@ -11401,7 +11412,7 @@
         <v>63</v>
       </c>
       <c r="C1001" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
